--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-22.xlsx
@@ -757,25 +757,25 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="G2" t="n">
         <v>3.05</v>
       </c>
       <c r="H2" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="I2" t="n">
         <v>2.58</v>
       </c>
       <c r="J2" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K2" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L2" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
         <v>1.06</v>
@@ -808,7 +808,7 @@
         <v>1.63</v>
       </c>
       <c r="W2" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G3" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="H3" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="I3" t="n">
         <v>3.05</v>
       </c>
       <c r="J3" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="K3" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="L3" t="n">
         <v>1.19</v>
@@ -984,31 +984,31 @@
         <v>3.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="R3" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="S3" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="T3" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="U3" t="n">
         <v>3.4</v>
       </c>
       <c r="V3" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W3" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="X3" t="n">
         <v>40</v>
       </c>
       <c r="Y3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Z3" t="n">
         <v>32</v>
@@ -1020,7 +1020,7 @@
         <v>24</v>
       </c>
       <c r="AC3" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD3" t="n">
         <v>15</v>
@@ -1041,7 +1041,7 @@
         <v>27</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK3" t="n">
         <v>20</v>
@@ -1074,7 +1074,7 @@
         <v>20</v>
       </c>
       <c r="AU3" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AV3" t="n">
         <v>13.5</v>
@@ -1104,7 +1104,7 @@
         <v>20</v>
       </c>
       <c r="BE3" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="BF3" t="n">
         <v>7</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
         <v>3.85</v>
       </c>
       <c r="L6" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
         <v>1.07</v>
@@ -1560,19 +1560,19 @@
         <v>3.95</v>
       </c>
       <c r="O6" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P6" t="n">
         <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R6" t="n">
         <v>1.39</v>
       </c>
       <c r="S6" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T6" t="n">
         <v>1.78</v>
@@ -1674,10 +1674,10 @@
         <v>15.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BB6" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC6" t="n">
         <v>42</v>
@@ -1686,7 +1686,7 @@
         <v>46</v>
       </c>
       <c r="BE6" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BF6" t="n">
         <v>42</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
         <v>1.75</v>
       </c>
       <c r="I8" t="n">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="J8" t="n">
         <v>3.95</v>
@@ -1945,16 +1945,16 @@
         <v>1.04</v>
       </c>
       <c r="N8" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="O8" t="n">
         <v>1.22</v>
       </c>
       <c r="P8" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="R8" t="n">
         <v>1.45</v>
@@ -1969,7 +1969,7 @@
         <v>2.24</v>
       </c>
       <c r="V8" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="W8" t="n">
         <v>1.24</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -2118,13 +2118,13 @@
         <v>2.28</v>
       </c>
       <c r="G9" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="H9" t="n">
         <v>3.3</v>
       </c>
       <c r="I9" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="J9" t="n">
         <v>3.25</v>
@@ -2163,10 +2163,10 @@
         <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W9" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="X9" t="n">
         <v>12</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -2697,19 +2697,19 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="G12" t="n">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="I12" t="n">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="J12" t="n">
-        <v>3.45</v>
+        <v>3.95</v>
       </c>
       <c r="K12" t="n">
         <v>4.6</v>
@@ -2721,7 +2721,7 @@
         <v>1.02</v>
       </c>
       <c r="N12" t="n">
-        <v>2.44</v>
+        <v>4.9</v>
       </c>
       <c r="O12" t="n">
         <v>1.12</v>
@@ -2733,22 +2733,22 @@
         <v>1.42</v>
       </c>
       <c r="R12" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="S12" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="T12" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="U12" t="n">
         <v>1.01</v>
       </c>
       <c r="V12" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="W12" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -2891,10 +2891,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="G13" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="H13" t="n">
         <v>4.2</v>
@@ -2906,7 +2906,7 @@
         <v>4.5</v>
       </c>
       <c r="K13" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L13" t="n">
         <v>1.01</v>
@@ -2921,28 +2921,28 @@
         <v>1.13</v>
       </c>
       <c r="P13" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="Q13" t="n">
         <v>1.43</v>
       </c>
       <c r="R13" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="S13" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="T13" t="n">
         <v>1.5</v>
       </c>
       <c r="U13" t="n">
-        <v>2.42</v>
+        <v>2.66</v>
       </c>
       <c r="V13" t="n">
         <v>1.27</v>
       </c>
       <c r="W13" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="X13" t="n">
         <v>42</v>
@@ -2957,7 +2957,7 @@
         <v>100</v>
       </c>
       <c r="AB13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AC13" t="n">
         <v>14.5</v>
@@ -2984,7 +2984,7 @@
         <v>25</v>
       </c>
       <c r="AK13" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AL13" t="n">
         <v>29</v>
@@ -2999,16 +2999,16 @@
         <v>32</v>
       </c>
       <c r="AP13" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AQ13" t="n">
         <v>3.9</v>
       </c>
-      <c r="AQ13" t="n">
-        <v>23</v>
-      </c>
       <c r="AR13" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AS13" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AT13" t="n">
         <v>14</v>
@@ -3020,7 +3020,7 @@
         <v>15.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AX13" t="n">
         <v>13.5</v>
@@ -3032,10 +3032,10 @@
         <v>13</v>
       </c>
       <c r="BA13" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BB13" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BC13" t="n">
         <v>13.5</v>
@@ -3044,7 +3044,7 @@
         <v>19.5</v>
       </c>
       <c r="BE13" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BF13" t="n">
         <v>4.7</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -3085,22 +3085,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="G14" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="H14" t="n">
         <v>4.8</v>
       </c>
       <c r="I14" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="J14" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K14" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
@@ -3115,28 +3115,28 @@
         <v>1.37</v>
       </c>
       <c r="P14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U14" t="n">
         <v>1.79</v>
       </c>
-      <c r="Q14" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.01</v>
-      </c>
       <c r="V14" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W14" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="X14" t="n">
         <v>18</v>
@@ -3145,7 +3145,7 @@
         <v>23</v>
       </c>
       <c r="Z14" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AA14" t="n">
         <v>1000</v>
@@ -3157,7 +3157,7 @@
         <v>11</v>
       </c>
       <c r="AD14" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE14" t="n">
         <v>100</v>
@@ -3193,7 +3193,7 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AQ14" t="n">
         <v>10</v>
@@ -3202,31 +3202,31 @@
         <v>2.26</v>
       </c>
       <c r="AS14" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AV14" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AX14" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="AY14" t="n">
         <v>2.04</v>
       </c>
       <c r="AZ14" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="BA14" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="BB14" t="n">
         <v>2.2</v>
@@ -3235,20 +3235,20 @@
         <v>2.2</v>
       </c>
       <c r="BD14" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="BE14" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -3288,13 +3288,13 @@
         <v>1.96</v>
       </c>
       <c r="I15" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="J15" t="n">
         <v>2.76</v>
       </c>
       <c r="K15" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L15" t="n">
         <v>1.43</v>
@@ -3306,7 +3306,7 @@
         <v>1.51</v>
       </c>
       <c r="O15" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P15" t="n">
         <v>1.51</v>
@@ -3330,7 +3330,7 @@
         <v>1.63</v>
       </c>
       <c r="W15" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -3667,16 +3667,16 @@
         </is>
       </c>
       <c r="F17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="G17" t="n">
         <v>1.3</v>
       </c>
-      <c r="G17" t="n">
-        <v>1.31</v>
-      </c>
       <c r="H17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I17" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="J17" t="n">
         <v>6.2</v>
@@ -3718,13 +3718,13 @@
         <v>1.07</v>
       </c>
       <c r="W17" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="X17" t="n">
         <v>20</v>
       </c>
       <c r="Y17" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="Z17" t="n">
         <v>150</v>
@@ -3757,7 +3757,7 @@
         <v>230</v>
       </c>
       <c r="AJ17" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AK17" t="n">
         <v>15</v>
@@ -3775,16 +3775,16 @@
         <v>420</v>
       </c>
       <c r="AP17" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AQ17" t="n">
         <v>30</v>
       </c>
       <c r="AR17" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="AS17" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AT17" t="n">
         <v>7.4</v>
@@ -3796,7 +3796,7 @@
         <v>42</v>
       </c>
       <c r="AW17" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AX17" t="n">
         <v>6.4</v>
@@ -3808,7 +3808,7 @@
         <v>34</v>
       </c>
       <c r="BA17" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BB17" t="n">
         <v>8.4</v>
@@ -3820,17 +3820,17 @@
         <v>42</v>
       </c>
       <c r="BE17" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="BF17" t="n">
         <v>4.9</v>
       </c>
       <c r="BG17" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
         <v>1.39</v>
       </c>
       <c r="S18" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="T18" t="n">
         <v>1.94</v>
@@ -3915,7 +3915,7 @@
         <v>2.32</v>
       </c>
       <c r="X18" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y18" t="n">
         <v>18.5</v>
@@ -3969,16 +3969,16 @@
         <v>90</v>
       </c>
       <c r="AP18" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AR18" t="n">
         <v>38</v>
       </c>
       <c r="AS18" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="AT18" t="n">
         <v>8.199999999999999</v>
@@ -3987,7 +3987,7 @@
         <v>8.4</v>
       </c>
       <c r="AV18" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AW18" t="n">
         <v>60</v>
@@ -3999,10 +3999,10 @@
         <v>9.4</v>
       </c>
       <c r="AZ18" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BB18" t="n">
         <v>16</v>
@@ -4014,17 +4014,17 @@
         <v>32</v>
       </c>
       <c r="BE18" t="n">
+        <v>100</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BG18" t="n">
         <v>70</v>
       </c>
-      <c r="BF18" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>75</v>
-      </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -4297,7 +4297,7 @@
         <v>2.46</v>
       </c>
       <c r="V20" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W20" t="n">
         <v>1.68</v>
@@ -4354,7 +4354,7 @@
         <v>17.5</v>
       </c>
       <c r="AO20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AP20" t="n">
         <v>18</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -4443,16 +4443,16 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="G21" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="H21" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="I21" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="J21" t="n">
         <v>3.9</v>
@@ -4476,7 +4476,7 @@
         <v>2.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R21" t="n">
         <v>1.48</v>
@@ -4494,13 +4494,13 @@
         <v>1.39</v>
       </c>
       <c r="W21" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="X21" t="n">
         <v>21</v>
       </c>
       <c r="Y21" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Z21" t="n">
         <v>27</v>
@@ -4509,7 +4509,7 @@
         <v>65</v>
       </c>
       <c r="AB21" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC21" t="n">
         <v>9.199999999999999</v>
@@ -4524,31 +4524,31 @@
         <v>15.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI21" t="n">
         <v>42</v>
       </c>
       <c r="AJ21" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AK21" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AL21" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM21" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AN21" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AO21" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="AP21" t="n">
         <v>16</v>
@@ -4557,10 +4557,10 @@
         <v>15</v>
       </c>
       <c r="AR21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AS21" t="n">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="AT21" t="n">
         <v>10.5</v>
@@ -4569,10 +4569,10 @@
         <v>8</v>
       </c>
       <c r="AV21" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW21" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AX21" t="n">
         <v>12.5</v>
@@ -4584,7 +4584,7 @@
         <v>14.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BB21" t="n">
         <v>22</v>
@@ -4602,11 +4602,11 @@
         <v>10</v>
       </c>
       <c r="BG21" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -4637,19 +4637,19 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.72</v>
+        <v>2.86</v>
       </c>
       <c r="G22" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="H22" t="n">
         <v>2.44</v>
       </c>
       <c r="I22" t="n">
-        <v>2.72</v>
+        <v>2.56</v>
       </c>
       <c r="J22" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="K22" t="n">
         <v>3.9</v>
@@ -4667,7 +4667,7 @@
         <v>1.21</v>
       </c>
       <c r="P22" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="Q22" t="n">
         <v>1.66</v>
@@ -4682,13 +4682,13 @@
         <v>1.56</v>
       </c>
       <c r="U22" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="V22" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="W22" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="X22" t="n">
         <v>21</v>
@@ -4706,7 +4706,7 @@
         <v>17</v>
       </c>
       <c r="AC22" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD22" t="n">
         <v>13.5</v>
@@ -4745,7 +4745,7 @@
         <v>15.5</v>
       </c>
       <c r="AP22" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AQ22" t="n">
         <v>12.5</v>
@@ -4781,16 +4781,16 @@
         <v>23</v>
       </c>
       <c r="BB22" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BC22" t="n">
         <v>21</v>
       </c>
       <c r="BD22" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BE22" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BF22" t="n">
         <v>17</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -4831,19 +4831,19 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="G23" t="n">
         <v>1.27</v>
       </c>
       <c r="H23" t="n">
-        <v>15</v>
+        <v>1.04</v>
       </c>
       <c r="I23" t="n">
         <v>29</v>
       </c>
       <c r="J23" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="K23" t="n">
         <v>10</v>
@@ -4882,7 +4882,7 @@
         <v>1.03</v>
       </c>
       <c r="W23" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="X23" t="n">
         <v>1000</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -5025,16 +5025,16 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="G24" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="H24" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="I24" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="J24" t="n">
         <v>3.85</v>
@@ -5073,22 +5073,22 @@
         <v>2.18</v>
       </c>
       <c r="V24" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="W24" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="X24" t="n">
         <v>21</v>
       </c>
       <c r="Y24" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Z24" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AA24" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AB24" t="n">
         <v>12</v>
@@ -5097,10 +5097,10 @@
         <v>9.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AE24" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AF24" t="n">
         <v>13.5</v>
@@ -5109,10 +5109,10 @@
         <v>10.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI24" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="AJ24" t="n">
         <v>22</v>
@@ -5130,19 +5130,19 @@
         <v>10.5</v>
       </c>
       <c r="AO24" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AP24" t="n">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="AQ24" t="n">
         <v>15.5</v>
       </c>
       <c r="AR24" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="AS24" t="n">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="AT24" t="n">
         <v>10</v>
@@ -5154,7 +5154,7 @@
         <v>14</v>
       </c>
       <c r="AW24" t="n">
-        <v>9.6</v>
+        <v>8</v>
       </c>
       <c r="AX24" t="n">
         <v>11.5</v>
@@ -5166,10 +5166,10 @@
         <v>14</v>
       </c>
       <c r="BA24" t="n">
-        <v>36</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB24" t="n">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="BC24" t="n">
         <v>13.5</v>
@@ -5178,17 +5178,17 @@
         <v>21</v>
       </c>
       <c r="BE24" t="n">
-        <v>10.5</v>
+        <v>8.4</v>
       </c>
       <c r="BF24" t="n">
         <v>7.2</v>
       </c>
       <c r="BG24" t="n">
-        <v>9.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -5267,7 +5267,7 @@
         <v>2.28</v>
       </c>
       <c r="V25" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W25" t="n">
         <v>1.92</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5652,7 @@
         <v>1.44</v>
       </c>
       <c r="U27" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="V27" t="n">
         <v>1.43</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -6410,7 +6410,7 @@
         <v>1.47</v>
       </c>
       <c r="O31" t="n">
-        <v>1.02</v>
+        <v>1.46</v>
       </c>
       <c r="P31" t="n">
         <v>1.47</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -6577,7 +6577,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="G32" t="n">
         <v>1.79</v>
@@ -6592,7 +6592,7 @@
         <v>3.85</v>
       </c>
       <c r="K32" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L32" t="n">
         <v>1.01</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -6777,7 +6777,7 @@
         <v>2.14</v>
       </c>
       <c r="H33" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I33" t="n">
         <v>3.55</v>
@@ -6813,7 +6813,7 @@
         <v>2.34</v>
       </c>
       <c r="T33" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="U33" t="n">
         <v>2.34</v>
@@ -6855,7 +6855,7 @@
         <v>11</v>
       </c>
       <c r="AH33" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AI33" t="n">
         <v>36</v>
@@ -6873,13 +6873,13 @@
         <v>55</v>
       </c>
       <c r="AN33" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AO33" t="n">
         <v>22</v>
       </c>
       <c r="AP33" t="n">
-        <v>10.5</v>
+        <v>23</v>
       </c>
       <c r="AQ33" t="n">
         <v>18</v>
@@ -6888,7 +6888,7 @@
         <v>25</v>
       </c>
       <c r="AS33" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AT33" t="n">
         <v>13.5</v>
@@ -6900,7 +6900,7 @@
         <v>13.5</v>
       </c>
       <c r="AW33" t="n">
-        <v>12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX33" t="n">
         <v>15</v>
@@ -6924,17 +6924,17 @@
         <v>23</v>
       </c>
       <c r="BE33" t="n">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="BF33" t="n">
         <v>8.6</v>
       </c>
       <c r="BG33" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -7159,7 +7159,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="G35" t="n">
         <v>2.52</v>
@@ -7174,7 +7174,7 @@
         <v>3.65</v>
       </c>
       <c r="K35" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="L35" t="n">
         <v>1.28</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -7938,19 +7938,19 @@
         <v>2.96</v>
       </c>
       <c r="G39" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="H39" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="I39" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="J39" t="n">
         <v>3.65</v>
       </c>
       <c r="K39" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L39" t="n">
         <v>1.01</v>
@@ -7968,7 +7968,7 @@
         <v>2.2</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="R39" t="n">
         <v>1.47</v>
@@ -7986,7 +7986,7 @@
         <v>1.64</v>
       </c>
       <c r="W39" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="X39" t="n">
         <v>17.5</v>
@@ -8028,7 +8028,7 @@
         <v>48</v>
       </c>
       <c r="AK39" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL39" t="n">
         <v>38</v>
@@ -8046,10 +8046,10 @@
         <v>16</v>
       </c>
       <c r="AQ39" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR39" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AS39" t="n">
         <v>30</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -8144,7 +8144,7 @@
         <v>5</v>
       </c>
       <c r="K40" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L40" t="n">
         <v>1.4</v>
@@ -8156,7 +8156,7 @@
         <v>4.1</v>
       </c>
       <c r="O40" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P40" t="n">
         <v>2.08</v>
@@ -8186,7 +8186,7 @@
         <v>16</v>
       </c>
       <c r="Y40" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Z40" t="n">
         <v>90</v>
@@ -8234,10 +8234,10 @@
         <v>7.2</v>
       </c>
       <c r="AO40" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AP40" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AQ40" t="n">
         <v>23</v>
@@ -8246,7 +8246,7 @@
         <v>75</v>
       </c>
       <c r="AS40" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AT40" t="n">
         <v>7</v>
@@ -8264,13 +8264,13 @@
         <v>7.4</v>
       </c>
       <c r="AY40" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ40" t="n">
         <v>26</v>
       </c>
       <c r="BA40" t="n">
-        <v>44</v>
+        <v>16.5</v>
       </c>
       <c r="BB40" t="n">
         <v>10.5</v>
@@ -8288,11 +8288,11 @@
         <v>6.6</v>
       </c>
       <c r="BG40" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -8440,7 +8440,7 @@
         <v>20</v>
       </c>
       <c r="AS41" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="AT41" t="n">
         <v>8</v>
@@ -8464,16 +8464,16 @@
         <v>19</v>
       </c>
       <c r="BA41" t="n">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="BB41" t="n">
         <v>30</v>
       </c>
       <c r="BC41" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BD41" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="BE41" t="n">
         <v>18.5</v>
@@ -8482,11 +8482,11 @@
         <v>25</v>
       </c>
       <c r="BG41" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -8717,13 +8717,13 @@
         <v>3.3</v>
       </c>
       <c r="H43" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="I43" t="n">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="J43" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="K43" t="n">
         <v>3.25</v>
@@ -8738,13 +8738,13 @@
         <v>3.6</v>
       </c>
       <c r="O43" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="P43" t="n">
         <v>1.82</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R43" t="n">
         <v>1.31</v>
@@ -8759,10 +8759,10 @@
         <v>2.16</v>
       </c>
       <c r="V43" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="W43" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X43" t="n">
         <v>13.5</v>
@@ -8789,31 +8789,31 @@
         <v>38</v>
       </c>
       <c r="AF43" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AG43" t="n">
         <v>14</v>
       </c>
       <c r="AH43" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI43" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AJ43" t="n">
         <v>55</v>
       </c>
       <c r="AK43" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AL43" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM43" t="n">
         <v>110</v>
       </c>
       <c r="AN43" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AO43" t="n">
         <v>32</v>
@@ -8822,28 +8822,28 @@
         <v>9.6</v>
       </c>
       <c r="AQ43" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR43" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AS43" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="AT43" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AU43" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AV43" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AW43" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AX43" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AY43" t="n">
         <v>10</v>
@@ -8852,29 +8852,29 @@
         <v>13.5</v>
       </c>
       <c r="BA43" t="n">
-        <v>5.8</v>
+        <v>34</v>
       </c>
       <c r="BB43" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="BC43" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BD43" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BE43" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF43" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BG43" t="n">
         <v>6</v>
       </c>
-      <c r="BF43" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BG43" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -8908,7 +8908,7 @@
         <v>2.06</v>
       </c>
       <c r="G44" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="H44" t="n">
         <v>3.6</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -9123,16 +9123,16 @@
         <v>1.01</v>
       </c>
       <c r="N45" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="O45" t="n">
         <v>1.41</v>
       </c>
       <c r="P45" t="n">
-        <v>1.24</v>
+        <v>1.53</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.41</v>
+        <v>2.12</v>
       </c>
       <c r="R45" t="n">
         <v>1.19</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
         <v>1.32</v>
       </c>
       <c r="P46" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="Q46" t="n">
         <v>2</v>
@@ -9386,7 +9386,7 @@
         <v>32</v>
       </c>
       <c r="AK46" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL46" t="n">
         <v>38</v>
@@ -9401,7 +9401,7 @@
         <v>34</v>
       </c>
       <c r="AP46" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AQ46" t="n">
         <v>12.5</v>
@@ -9452,11 +9452,11 @@
         <v>16.5</v>
       </c>
       <c r="BG46" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -9640,7 +9640,7 @@
         <v>30</v>
       </c>
       <c r="BE47" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="BF47" t="n">
         <v>11</v>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -9690,16 +9690,16 @@
         <v>3.45</v>
       </c>
       <c r="I48" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J48" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K48" t="n">
         <v>3.75</v>
       </c>
-      <c r="K48" t="n">
-        <v>3.8</v>
-      </c>
       <c r="L48" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M48" t="n">
         <v>1.06</v>
@@ -9732,7 +9732,7 @@
         <v>1.4</v>
       </c>
       <c r="W48" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="X48" t="n">
         <v>17.5</v>
@@ -9744,7 +9744,7 @@
         <v>26</v>
       </c>
       <c r="AA48" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB48" t="n">
         <v>12</v>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
         <v>1.94</v>
       </c>
       <c r="R49" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="S49" t="n">
         <v>1.94</v>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -10108,7 +10108,7 @@
         <v>1.32</v>
       </c>
       <c r="S50" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="T50" t="n">
         <v>1.83</v>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -10266,7 +10266,7 @@
         <v>1.41</v>
       </c>
       <c r="G51" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="H51" t="n">
         <v>7.6</v>
@@ -10377,7 +10377,7 @@
         <v>9.6</v>
       </c>
       <c r="AR51" t="n">
-        <v>10.5</v>
+        <v>50</v>
       </c>
       <c r="AS51" t="n">
         <v>12</v>
@@ -10404,7 +10404,7 @@
         <v>18.5</v>
       </c>
       <c r="BA51" t="n">
-        <v>10.5</v>
+        <v>50</v>
       </c>
       <c r="BB51" t="n">
         <v>11.5</v>
@@ -10416,7 +10416,7 @@
         <v>8.6</v>
       </c>
       <c r="BE51" t="n">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="BF51" t="n">
         <v>3.55</v>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -10478,25 +10478,25 @@
         <v>1.01</v>
       </c>
       <c r="M52" t="n">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="N52" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="O52" t="n">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="P52" t="n">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="R52" t="n">
         <v>1.08</v>
       </c>
       <c r="S52" t="n">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="T52" t="n">
         <v>1.01</v>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -10654,13 +10654,13 @@
         <v>1.98</v>
       </c>
       <c r="G53" t="n">
-        <v>2.76</v>
+        <v>2.66</v>
       </c>
       <c r="H53" t="n">
         <v>2.9</v>
       </c>
       <c r="I53" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J53" t="n">
         <v>2.98</v>
@@ -10699,10 +10699,10 @@
         <v>1.01</v>
       </c>
       <c r="V53" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W53" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="X53" t="n">
         <v>1000</v>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -11257,16 +11257,16 @@
         <v>1.01</v>
       </c>
       <c r="N56" t="n">
-        <v>1.22</v>
+        <v>1.56</v>
       </c>
       <c r="O56" t="n">
-        <v>1.39</v>
+        <v>1.02</v>
       </c>
       <c r="P56" t="n">
-        <v>1.21</v>
+        <v>1.56</v>
       </c>
       <c r="Q56" t="n">
-        <v>1.39</v>
+        <v>2.04</v>
       </c>
       <c r="R56" t="n">
         <v>1.21</v>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -11590,7 +11590,7 @@
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -11765,7 +11765,7 @@
         <v>6.8</v>
       </c>
       <c r="BB58" t="n">
-        <v>7.2</v>
+        <v>30</v>
       </c>
       <c r="BC58" t="n">
         <v>21</v>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -11978,7 +11978,7 @@
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -12015,7 +12015,7 @@
         <v>18.5</v>
       </c>
       <c r="H60" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="I60" t="n">
         <v>1.67</v>
@@ -12024,7 +12024,7 @@
         <v>4.1</v>
       </c>
       <c r="K60" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L60" t="n">
         <v>1.01</v>
@@ -12036,7 +12036,7 @@
         <v>2.1</v>
       </c>
       <c r="O60" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P60" t="n">
         <v>2.1</v>
@@ -12060,7 +12060,7 @@
         <v>2.48</v>
       </c>
       <c r="W60" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X60" t="n">
         <v>1000</v>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -12236,7 +12236,7 @@
         <v>1.75</v>
       </c>
       <c r="Q61" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="R61" t="n">
         <v>1.22</v>
@@ -12366,7 +12366,7 @@
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -12606,7 +12606,7 @@
         <v>3.25</v>
       </c>
       <c r="K63" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L63" t="n">
         <v>1.01</v>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -12821,7 +12821,7 @@
         <v>1.39</v>
       </c>
       <c r="R64" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="S64" t="n">
         <v>2</v>
@@ -12948,7 +12948,7 @@
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -13009,13 +13009,13 @@
         <v>1.26</v>
       </c>
       <c r="P65" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q65" t="n">
         <v>1.78</v>
       </c>
       <c r="R65" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S65" t="n">
         <v>2.96</v>
@@ -13142,7 +13142,7 @@
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -13203,7 +13203,7 @@
         <v>1.41</v>
       </c>
       <c r="P66" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="Q66" t="n">
         <v>2.22</v>
@@ -13290,7 +13290,7 @@
         <v>26</v>
       </c>
       <c r="AS66" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AT66" t="n">
         <v>7.8</v>
@@ -13314,7 +13314,7 @@
         <v>17.5</v>
       </c>
       <c r="BA66" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BB66" t="n">
         <v>22</v>
@@ -13326,7 +13326,7 @@
         <v>38</v>
       </c>
       <c r="BE66" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BF66" t="n">
         <v>16.5</v>
@@ -13336,7 +13336,7 @@
       </c>
       <c r="BH66" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -13367,10 +13367,10 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="G67" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="H67" t="n">
         <v>9.199999999999999</v>
@@ -13382,7 +13382,7 @@
         <v>5.7</v>
       </c>
       <c r="K67" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="L67" t="n">
         <v>1.01</v>
@@ -13415,7 +13415,7 @@
         <v>2</v>
       </c>
       <c r="V67" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="W67" t="n">
         <v>3.5</v>
@@ -13445,7 +13445,7 @@
         <v>140</v>
       </c>
       <c r="AF67" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AG67" t="n">
         <v>10.5</v>
@@ -13484,10 +13484,10 @@
         <v>15.5</v>
       </c>
       <c r="AS67" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AT67" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AU67" t="n">
         <v>11.5</v>
@@ -13530,7 +13530,7 @@
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -13564,10 +13564,10 @@
         <v>1.96</v>
       </c>
       <c r="G68" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="H68" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I68" t="n">
         <v>4.3</v>
@@ -13576,7 +13576,7 @@
         <v>3.85</v>
       </c>
       <c r="K68" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L68" t="n">
         <v>1.01</v>
@@ -13591,7 +13591,7 @@
         <v>1.28</v>
       </c>
       <c r="P68" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="Q68" t="n">
         <v>1.84</v>
@@ -13612,7 +13612,7 @@
         <v>1.3</v>
       </c>
       <c r="W68" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X68" t="n">
         <v>16.5</v>
@@ -13639,7 +13639,7 @@
         <v>48</v>
       </c>
       <c r="AF68" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG68" t="n">
         <v>10.5</v>
@@ -13690,7 +13690,7 @@
         <v>15</v>
       </c>
       <c r="AW68" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="AX68" t="n">
         <v>11.5</v>
@@ -13702,7 +13702,7 @@
         <v>16</v>
       </c>
       <c r="BA68" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BB68" t="n">
         <v>20</v>
@@ -13720,11 +13720,11 @@
         <v>11</v>
       </c>
       <c r="BG68" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BH68" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -13918,7 +13918,7 @@
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -14024,7 +14024,7 @@
         <v>13</v>
       </c>
       <c r="AE70" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AF70" t="n">
         <v>17.5</v>
@@ -14102,7 +14102,7 @@
         <v>30</v>
       </c>
       <c r="BE70" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BF70" t="n">
         <v>32</v>
@@ -14112,7 +14112,7 @@
       </c>
       <c r="BH70" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -14176,13 +14176,13 @@
         <v>1.61</v>
       </c>
       <c r="Q71" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="R71" t="n">
         <v>1.02</v>
       </c>
       <c r="S71" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="T71" t="n">
         <v>1.01</v>
@@ -14306,7 +14306,7 @@
       </c>
       <c r="BH71" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -14500,7 +14500,7 @@
       </c>
       <c r="BH72" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -14573,7 +14573,7 @@
         <v>4.2</v>
       </c>
       <c r="T73" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="U73" t="n">
         <v>1.96</v>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -14740,7 +14740,7 @@
         <v>3.15</v>
       </c>
       <c r="K74" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L74" t="n">
         <v>1.01</v>
@@ -14888,7 +14888,7 @@
       </c>
       <c r="BH74" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -15057,10 +15057,10 @@
         <v>10</v>
       </c>
       <c r="AZ75" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BA75" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="BB75" t="n">
         <v>11.5</v>
@@ -15082,7 +15082,7 @@
       </c>
       <c r="BH75" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -15116,16 +15116,16 @@
         <v>1.16</v>
       </c>
       <c r="G76" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="H76" t="n">
         <v>21</v>
       </c>
       <c r="I76" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="J76" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="K76" t="n">
         <v>9</v>
@@ -15140,13 +15140,13 @@
         <v>4.4</v>
       </c>
       <c r="O76" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P76" t="n">
         <v>2.16</v>
       </c>
       <c r="Q76" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="R76" t="n">
         <v>1.45</v>
@@ -15158,19 +15158,19 @@
         <v>2.62</v>
       </c>
       <c r="U76" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="V76" t="n">
         <v>1.03</v>
       </c>
       <c r="W76" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="X76" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="Y76" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="Z76" t="n">
         <v>1000</v>
@@ -15185,7 +15185,7 @@
         <v>21</v>
       </c>
       <c r="AD76" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AE76" t="n">
         <v>1000</v>
@@ -15197,7 +15197,7 @@
         <v>14.5</v>
       </c>
       <c r="AH76" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AI76" t="n">
         <v>1000</v>
@@ -15221,28 +15221,28 @@
         <v>1000</v>
       </c>
       <c r="AP76" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AQ76" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AR76" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AS76" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT76" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AU76" t="n">
         <v>4.7</v>
       </c>
-      <c r="AQ76" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AR76" t="n">
+      <c r="AV76" t="n">
         <v>5.7</v>
       </c>
-      <c r="AS76" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AT76" t="n">
+      <c r="AW76" t="n">
         <v>6</v>
-      </c>
-      <c r="AU76" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AV76" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AW76" t="n">
-        <v>5.8</v>
       </c>
       <c r="AX76" t="n">
         <v>4.9</v>
@@ -15251,32 +15251,32 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ76" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BA76" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BB76" t="n">
-        <v>6</v>
+        <v>3.55</v>
       </c>
       <c r="BC76" t="n">
         <v>12.5</v>
       </c>
       <c r="BD76" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BE76" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BF76" t="n">
         <v>3.7</v>
       </c>
       <c r="BG76" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BH76" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -15470,7 +15470,7 @@
       </c>
       <c r="BH77" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -15510,10 +15510,10 @@
         <v>1.76</v>
       </c>
       <c r="I78" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="J78" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K78" t="n">
         <v>3.8</v>
@@ -15555,7 +15555,7 @@
         <v>1.16</v>
       </c>
       <c r="X78" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Y78" t="n">
         <v>9.199999999999999</v>
@@ -15612,16 +15612,16 @@
         <v>2.12</v>
       </c>
       <c r="AQ78" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AR78" t="n">
         <v>2.12</v>
       </c>
       <c r="AS78" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="AT78" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="AU78" t="n">
         <v>2.06</v>
@@ -15633,7 +15633,7 @@
         <v>2.34</v>
       </c>
       <c r="AX78" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="AY78" t="n">
         <v>2.34</v>
@@ -15642,29 +15642,29 @@
         <v>2.36</v>
       </c>
       <c r="BA78" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="BB78" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="BC78" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="BD78" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="BE78" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="BF78" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="BG78" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="BH78" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -15701,49 +15701,49 @@
         <v>17</v>
       </c>
       <c r="H79" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="I79" t="n">
         <v>1.3</v>
       </c>
       <c r="J79" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="K79" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="L79" t="n">
         <v>1.01</v>
       </c>
       <c r="M79" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N79" t="n">
-        <v>2.96</v>
+        <v>4</v>
       </c>
       <c r="O79" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P79" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q79" t="n">
-        <v>1.33</v>
+        <v>1.73</v>
       </c>
       <c r="R79" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S79" t="n">
-        <v>2.74</v>
+        <v>3.1</v>
       </c>
       <c r="T79" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="U79" t="n">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="V79" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="W79" t="n">
         <v>1.06</v>
@@ -15758,7 +15758,7 @@
         <v>7.2</v>
       </c>
       <c r="AA79" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AB79" t="n">
         <v>40</v>
@@ -15827,38 +15827,38 @@
         <v>14</v>
       </c>
       <c r="AX79" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AY79" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ79" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BA79" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB79" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BC79" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BC79" t="n">
-        <v>9</v>
-      </c>
       <c r="BD79" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE79" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF79" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BG79" t="n">
         <v>4.8</v>
       </c>
       <c r="BH79" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -15904,13 +15904,13 @@
         <v>3.15</v>
       </c>
       <c r="K80" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L80" t="n">
         <v>1.01</v>
       </c>
       <c r="M80" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N80" t="n">
         <v>1.76</v>
@@ -15943,7 +15943,7 @@
         <v>1.71</v>
       </c>
       <c r="X80" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Y80" t="n">
         <v>17.5</v>
@@ -16000,59 +16000,59 @@
         <v>2.12</v>
       </c>
       <c r="AQ80" t="n">
-        <v>2.14</v>
+        <v>1.89</v>
       </c>
       <c r="AR80" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AS80" t="n">
-        <v>2.44</v>
+        <v>2.12</v>
       </c>
       <c r="AT80" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AU80" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AV80" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AW80" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AX80" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AY80" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AZ80" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BA80" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BB80" t="n">
         <v>2.02</v>
       </c>
-      <c r="AU80" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AV80" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AW80" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AX80" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AY80" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AZ80" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="BA80" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BB80" t="n">
-        <v>2.32</v>
-      </c>
       <c r="BC80" t="n">
-        <v>2.32</v>
+        <v>2.02</v>
       </c>
       <c r="BD80" t="n">
-        <v>2.36</v>
+        <v>2.04</v>
       </c>
       <c r="BE80" t="n">
-        <v>2.44</v>
+        <v>2.12</v>
       </c>
       <c r="BF80" t="n">
-        <v>2.44</v>
+        <v>2.12</v>
       </c>
       <c r="BG80" t="n">
-        <v>2.44</v>
+        <v>2.12</v>
       </c>
       <c r="BH80" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -16246,7 +16246,7 @@
       </c>
       <c r="BH81" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -16319,7 +16319,7 @@
         <v>2.62</v>
       </c>
       <c r="T82" t="n">
-        <v>1.66</v>
+        <v>1.01</v>
       </c>
       <c r="U82" t="n">
         <v>1.01</v>
@@ -16440,7 +16440,7 @@
       </c>
       <c r="BH82" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -16471,7 +16471,7 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>1.99</v>
+        <v>1.79</v>
       </c>
       <c r="G83" t="n">
         <v>2.56</v>
@@ -16486,7 +16486,7 @@
         <v>3</v>
       </c>
       <c r="K83" t="n">
-        <v>5.3</v>
+        <v>7.4</v>
       </c>
       <c r="L83" t="n">
         <v>1.01</v>
@@ -16634,7 +16634,7 @@
       </c>
       <c r="BH83" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -16668,10 +16668,10 @@
         <v>1.91</v>
       </c>
       <c r="G84" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="H84" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="I84" t="n">
         <v>6.2</v>
@@ -16710,13 +16710,13 @@
         <v>1.01</v>
       </c>
       <c r="U84" t="n">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="V84" t="n">
         <v>1.2</v>
       </c>
       <c r="W84" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="X84" t="n">
         <v>13.5</v>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="BH84" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="BH85" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -17059,7 +17059,7 @@
         <v>5.6</v>
       </c>
       <c r="H86" t="n">
-        <v>1.04</v>
+        <v>2.12</v>
       </c>
       <c r="I86" t="n">
         <v>2.6</v>
@@ -17068,7 +17068,7 @@
         <v>2.28</v>
       </c>
       <c r="K86" t="n">
-        <v>950</v>
+        <v>4.1</v>
       </c>
       <c r="L86" t="n">
         <v>1.01</v>
@@ -17080,7 +17080,7 @@
         <v>1.54</v>
       </c>
       <c r="O86" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="P86" t="n">
         <v>1.54</v>
@@ -17216,7 +17216,7 @@
       </c>
       <c r="BH86" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -17250,7 +17250,7 @@
         <v>2.08</v>
       </c>
       <c r="G87" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="H87" t="n">
         <v>4.8</v>
@@ -17298,7 +17298,7 @@
         <v>1.22</v>
       </c>
       <c r="W87" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="X87" t="n">
         <v>6.8</v>
@@ -17410,7 +17410,7 @@
       </c>
       <c r="BH87" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -17498,7 +17498,7 @@
         <v>24</v>
       </c>
       <c r="Y88" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Z88" t="n">
         <v>8.199999999999999</v>
@@ -17561,7 +17561,7 @@
         <v>9</v>
       </c>
       <c r="AT88" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AU88" t="n">
         <v>11</v>
@@ -17573,38 +17573,38 @@
         <v>12.5</v>
       </c>
       <c r="AX88" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AY88" t="n">
         <v>34</v>
       </c>
       <c r="AZ88" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BA88" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BB88" t="n">
         <v>10</v>
       </c>
       <c r="BC88" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BD88" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE88" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BF88" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BG88" t="n">
         <v>4.5</v>
       </c>
       <c r="BH88" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -17798,7 +17798,7 @@
       </c>
       <c r="BH89" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -17838,10 +17838,10 @@
         <v>1.62</v>
       </c>
       <c r="I90" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="J90" t="n">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="K90" t="n">
         <v>5</v>
@@ -17877,7 +17877,7 @@
         <v>1.01</v>
       </c>
       <c r="V90" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="W90" t="n">
         <v>1.16</v>
@@ -17992,7 +17992,7 @@
       </c>
       <c r="BH90" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -18029,10 +18029,10 @@
         <v>3.7</v>
       </c>
       <c r="H91" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="I91" t="n">
         <v>2.1</v>
-      </c>
-      <c r="I91" t="n">
-        <v>2.12</v>
       </c>
       <c r="J91" t="n">
         <v>4</v>
@@ -18098,7 +18098,7 @@
         <v>10.5</v>
       </c>
       <c r="AE91" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AF91" t="n">
         <v>29</v>
@@ -18107,7 +18107,7 @@
         <v>15.5</v>
       </c>
       <c r="AH91" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AI91" t="n">
         <v>28</v>
@@ -18125,7 +18125,7 @@
         <v>65</v>
       </c>
       <c r="AN91" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO91" t="n">
         <v>10.5</v>
@@ -18186,7 +18186,7 @@
       </c>
       <c r="BH91" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -18238,10 +18238,10 @@
         <v>1.43</v>
       </c>
       <c r="M92" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N92" t="n">
-        <v>1.03</v>
+        <v>1.6</v>
       </c>
       <c r="O92" t="n">
         <v>1.43</v>
@@ -18259,7 +18259,7 @@
         <v>4</v>
       </c>
       <c r="T92" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="U92" t="n">
         <v>1.01</v>
@@ -18271,7 +18271,7 @@
         <v>1.89</v>
       </c>
       <c r="X92" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Y92" t="n">
         <v>19</v>
@@ -18331,10 +18331,10 @@
         <v>9</v>
       </c>
       <c r="AR92" t="n">
-        <v>2.42</v>
+        <v>2.06</v>
       </c>
       <c r="AS92" t="n">
-        <v>2.54</v>
+        <v>2.16</v>
       </c>
       <c r="AT92" t="n">
         <v>6</v>
@@ -18346,7 +18346,7 @@
         <v>13</v>
       </c>
       <c r="AW92" t="n">
-        <v>2.54</v>
+        <v>2.16</v>
       </c>
       <c r="AX92" t="n">
         <v>9.4</v>
@@ -18358,29 +18358,29 @@
         <v>18</v>
       </c>
       <c r="BA92" t="n">
-        <v>2.54</v>
+        <v>2.16</v>
       </c>
       <c r="BB92" t="n">
-        <v>2.38</v>
+        <v>2.04</v>
       </c>
       <c r="BC92" t="n">
-        <v>2.36</v>
+        <v>2.02</v>
       </c>
       <c r="BD92" t="n">
-        <v>2.44</v>
+        <v>2.08</v>
       </c>
       <c r="BE92" t="n">
-        <v>2.54</v>
+        <v>2.16</v>
       </c>
       <c r="BF92" t="n">
-        <v>2.54</v>
+        <v>2.16</v>
       </c>
       <c r="BG92" t="n">
-        <v>2.54</v>
+        <v>2.16</v>
       </c>
       <c r="BH92" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -18574,7 +18574,7 @@
       </c>
       <c r="BH93" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -18608,7 +18608,7 @@
         <v>2.26</v>
       </c>
       <c r="G94" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="H94" t="n">
         <v>4</v>
@@ -18617,7 +18617,7 @@
         <v>4.3</v>
       </c>
       <c r="J94" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="K94" t="n">
         <v>3.1</v>
@@ -18656,7 +18656,7 @@
         <v>1.32</v>
       </c>
       <c r="W94" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="X94" t="n">
         <v>9</v>
@@ -18768,7 +18768,7 @@
       </c>
       <c r="BH94" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -18962,7 +18962,7 @@
       </c>
       <c r="BH95" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -19156,7 +19156,7 @@
       </c>
       <c r="BH96" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -19211,16 +19211,16 @@
         <v>1.07</v>
       </c>
       <c r="N97" t="n">
-        <v>1.9</v>
+        <v>1.32</v>
       </c>
       <c r="O97" t="n">
         <v>1.3</v>
       </c>
       <c r="P97" t="n">
-        <v>1.9</v>
+        <v>1.31</v>
       </c>
       <c r="Q97" t="n">
-        <v>1.96</v>
+        <v>1.3</v>
       </c>
       <c r="R97" t="n">
         <v>1.31</v>
@@ -19350,7 +19350,7 @@
       </c>
       <c r="BH97" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -19426,7 +19426,7 @@
         <v>2.02</v>
       </c>
       <c r="U98" t="n">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="V98" t="n">
         <v>1.27</v>
@@ -19544,7 +19544,7 @@
       </c>
       <c r="BH98" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -19575,10 +19575,10 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="G99" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="H99" t="n">
         <v>4.4</v>
@@ -19617,16 +19617,16 @@
         <v>3.55</v>
       </c>
       <c r="T99" t="n">
-        <v>1.71</v>
+        <v>1.87</v>
       </c>
       <c r="U99" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V99" t="n">
         <v>1.26</v>
       </c>
       <c r="W99" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="X99" t="n">
         <v>17.5</v>
@@ -19738,7 +19738,7 @@
       </c>
       <c r="BH99" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -19793,22 +19793,22 @@
         <v>1.11</v>
       </c>
       <c r="N100" t="n">
-        <v>2.68</v>
+        <v>1.25</v>
       </c>
       <c r="O100" t="n">
-        <v>1.48</v>
+        <v>1.11</v>
       </c>
       <c r="P100" t="n">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="Q100" t="n">
-        <v>2.42</v>
+        <v>1.11</v>
       </c>
       <c r="R100" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="S100" t="n">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="T100" t="n">
         <v>1.01</v>
@@ -19932,7 +19932,7 @@
       </c>
       <c r="BH100" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -20017,7 +20017,7 @@
         <v>1.54</v>
       </c>
       <c r="X101" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="Y101" t="n">
         <v>1000</v>
@@ -20074,59 +20074,59 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AQ101" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AR101" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AS101" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT101" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AU101" t="n">
         <v>6.2</v>
       </c>
       <c r="AV101" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AW101" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AX101" t="n">
         <v>6</v>
       </c>
       <c r="AY101" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AZ101" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BA101" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB101" t="n">
         <v>7.6</v>
       </c>
-      <c r="BB101" t="n">
+      <c r="BC101" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BD101" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BE101" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BF101" t="n">
         <v>7</v>
       </c>
-      <c r="BC101" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BD101" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BE101" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BF101" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BG101" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH101" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -20190,7 +20190,7 @@
         <v>2.34</v>
       </c>
       <c r="Q102" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="R102" t="n">
         <v>1.53</v>
@@ -20320,7 +20320,7 @@
       </c>
       <c r="BH102" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -20399,7 +20399,7 @@
         <v>1.01</v>
       </c>
       <c r="V103" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W103" t="n">
         <v>1.57</v>
@@ -20514,7 +20514,7 @@
       </c>
       <c r="BH103" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -20548,7 +20548,7 @@
         <v>3.8</v>
       </c>
       <c r="G104" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="H104" t="n">
         <v>2.12</v>
@@ -20708,7 +20708,7 @@
       </c>
       <c r="BH104" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -20742,28 +20742,28 @@
         <v>5.3</v>
       </c>
       <c r="G105" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="H105" t="n">
         <v>1.71</v>
       </c>
       <c r="I105" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="J105" t="n">
         <v>4.3</v>
       </c>
       <c r="K105" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L105" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="M105" t="n">
         <v>1.06</v>
       </c>
       <c r="N105" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O105" t="n">
         <v>1.27</v>
@@ -20778,16 +20778,16 @@
         <v>1.45</v>
       </c>
       <c r="S105" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T105" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="U105" t="n">
         <v>2.12</v>
       </c>
       <c r="V105" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="W105" t="n">
         <v>1.22</v>
@@ -20796,7 +20796,7 @@
         <v>17.5</v>
       </c>
       <c r="Y105" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Z105" t="n">
         <v>10.5</v>
@@ -20814,13 +20814,13 @@
         <v>10</v>
       </c>
       <c r="AE105" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AF105" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AG105" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH105" t="n">
         <v>20</v>
@@ -20850,7 +20850,7 @@
         <v>16</v>
       </c>
       <c r="AQ105" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR105" t="n">
         <v>9.6</v>
@@ -20871,7 +20871,7 @@
         <v>15.5</v>
       </c>
       <c r="AX105" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="AY105" t="n">
         <v>19</v>
@@ -20883,16 +20883,16 @@
         <v>29</v>
       </c>
       <c r="BB105" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="BC105" t="n">
         <v>32</v>
       </c>
       <c r="BD105" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="BE105" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BF105" t="n">
         <v>34</v>
@@ -20902,7 +20902,7 @@
       </c>
       <c r="BH105" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -20933,10 +20933,10 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="G106" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="H106" t="n">
         <v>2.3</v>
@@ -20990,28 +20990,28 @@
         <v>10.5</v>
       </c>
       <c r="Y106" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z106" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AA106" t="n">
         <v>34</v>
       </c>
       <c r="AB106" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC106" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AD106" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE106" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF106" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AG106" t="n">
         <v>16</v>
@@ -21029,74 +21029,74 @@
         <v>55</v>
       </c>
       <c r="AL106" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AM106" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AN106" t="n">
         <v>70</v>
       </c>
       <c r="AO106" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AP106" t="n">
-        <v>4.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ106" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AR106" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AS106" t="n">
-        <v>27</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT106" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AU106" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV106" t="n">
         <v>10</v>
       </c>
       <c r="AW106" t="n">
-        <v>6.2</v>
+        <v>26</v>
       </c>
       <c r="AX106" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AY106" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ106" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BA106" t="n">
-        <v>6.8</v>
+        <v>44</v>
       </c>
       <c r="BB106" t="n">
-        <v>7</v>
+        <v>12.5</v>
       </c>
       <c r="BC106" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="BD106" t="n">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="BE106" t="n">
-        <v>7.4</v>
+        <v>11.5</v>
       </c>
       <c r="BF106" t="n">
-        <v>7</v>
+        <v>12.5</v>
       </c>
       <c r="BG106" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BH106" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -21290,7 +21290,7 @@
       </c>
       <c r="BH107" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -21321,13 +21321,13 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="G108" t="n">
         <v>9.6</v>
       </c>
       <c r="H108" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="I108" t="n">
         <v>1.87</v>
@@ -21336,7 +21336,7 @@
         <v>3.15</v>
       </c>
       <c r="K108" t="n">
-        <v>4.6</v>
+        <v>950</v>
       </c>
       <c r="L108" t="n">
         <v>1.01</v>
@@ -21366,7 +21366,7 @@
         <v>1.01</v>
       </c>
       <c r="U108" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="V108" t="n">
         <v>2.14</v>
@@ -21484,7 +21484,7 @@
       </c>
       <c r="BH108" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -21527,7 +21527,7 @@
         <v>4.5</v>
       </c>
       <c r="J109" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K109" t="n">
         <v>3.8</v>
@@ -21678,7 +21678,7 @@
       </c>
       <c r="BH109" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -21718,10 +21718,10 @@
         <v>4.5</v>
       </c>
       <c r="I110" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="J110" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="K110" t="n">
         <v>4.2</v>
@@ -21872,7 +21872,7 @@
       </c>
       <c r="BH110" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -21909,10 +21909,10 @@
         <v>3.5</v>
       </c>
       <c r="H111" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="I111" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="J111" t="n">
         <v>3.1</v>
@@ -21951,7 +21951,7 @@
         <v>1.85</v>
       </c>
       <c r="V111" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W111" t="n">
         <v>1.4</v>
@@ -21999,7 +21999,7 @@
         <v>60</v>
       </c>
       <c r="AL111" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AM111" t="n">
         <v>190</v>
@@ -22032,7 +22032,7 @@
         <v>9.6</v>
       </c>
       <c r="AW111" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AX111" t="n">
         <v>16</v>
@@ -22047,26 +22047,26 @@
         <v>5.4</v>
       </c>
       <c r="BB111" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BC111" t="n">
         <v>5.4</v>
-      </c>
-      <c r="BC111" t="n">
-        <v>5.3</v>
       </c>
       <c r="BD111" t="n">
         <v>5.5</v>
       </c>
       <c r="BE111" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BF111" t="n">
         <v>5.4</v>
       </c>
       <c r="BG111" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BH111" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -22097,13 +22097,13 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="G112" t="n">
         <v>2.82</v>
       </c>
       <c r="H112" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="I112" t="n">
         <v>3</v>
@@ -22121,22 +22121,22 @@
         <v>1.01</v>
       </c>
       <c r="N112" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O112" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="P112" t="n">
         <v>1.25</v>
       </c>
       <c r="Q112" t="n">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="R112" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S112" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="T112" t="n">
         <v>1.01</v>
@@ -22205,19 +22205,19 @@
         <v>1000</v>
       </c>
       <c r="AP112" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AQ112" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AR112" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AS112" t="n">
         <v>34</v>
       </c>
       <c r="AT112" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU112" t="n">
         <v>6.2</v>
@@ -22226,19 +22226,19 @@
         <v>10</v>
       </c>
       <c r="AW112" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AX112" t="n">
         <v>12</v>
       </c>
       <c r="AY112" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ112" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA112" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BB112" t="n">
         <v>26</v>
@@ -22260,7 +22260,7 @@
       </c>
       <c r="BH112" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -22291,19 +22291,19 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="G113" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="H113" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="I113" t="n">
         <v>9.6</v>
       </c>
       <c r="J113" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K113" t="n">
         <v>5.1</v>
@@ -22312,149 +22312,149 @@
         <v>1.01</v>
       </c>
       <c r="M113" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N113" t="n">
-        <v>1.34</v>
+        <v>4.1</v>
       </c>
       <c r="O113" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="P113" t="n">
-        <v>1.34</v>
+        <v>2.06</v>
       </c>
       <c r="Q113" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="R113" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="S113" t="n">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="T113" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="U113" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="V113" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W113" t="n">
-        <v>2.72</v>
+        <v>2.88</v>
       </c>
       <c r="X113" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Y113" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Z113" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AA113" t="n">
-        <v>1000</v>
+        <v>340</v>
       </c>
       <c r="AB113" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AC113" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD113" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AE113" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AF113" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG113" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH113" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI113" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AJ113" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AK113" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AL113" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM113" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN113" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AO113" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AP113" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AQ113" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AR113" t="n">
-        <v>38</v>
+        <v>7.8</v>
       </c>
       <c r="AS113" t="n">
-        <v>100</v>
+        <v>8.6</v>
       </c>
       <c r="AT113" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AU113" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV113" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW113" t="n">
         <v>8.4</v>
       </c>
-      <c r="AV113" t="n">
-        <v>19</v>
-      </c>
-      <c r="AW113" t="n">
-        <v>60</v>
-      </c>
       <c r="AX113" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AY113" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ113" t="n">
-        <v>17.5</v>
+        <v>6.6</v>
       </c>
       <c r="BA113" t="n">
-        <v>48</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB113" t="n">
         <v>11</v>
       </c>
       <c r="BC113" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BD113" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="BE113" t="n">
-        <v>75</v>
+        <v>8.4</v>
       </c>
       <c r="BF113" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BG113" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BH113" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -22509,22 +22509,22 @@
         <v>1.01</v>
       </c>
       <c r="N114" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O114" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P114" t="n">
         <v>1.24</v>
       </c>
       <c r="Q114" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="R114" t="n">
         <v>1.08</v>
       </c>
       <c r="S114" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="T114" t="n">
         <v>1.01</v>
@@ -22593,19 +22593,19 @@
         <v>1000</v>
       </c>
       <c r="AP114" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AQ114" t="n">
         <v>5.8</v>
       </c>
       <c r="AR114" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AS114" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT114" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AU114" t="n">
         <v>6.4</v>
@@ -22617,16 +22617,16 @@
         <v>17.5</v>
       </c>
       <c r="AX114" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AY114" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AZ114" t="n">
         <v>17.5</v>
       </c>
       <c r="BA114" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BB114" t="n">
         <v>40</v>
@@ -22648,7 +22648,7 @@
       </c>
       <c r="BH114" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -22688,7 +22688,7 @@
         <v>5.9</v>
       </c>
       <c r="I115" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="J115" t="n">
         <v>3.25</v>
@@ -22697,16 +22697,16 @@
         <v>3.6</v>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="O115" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="P115" t="n">
         <v>1.52</v>
@@ -22715,134 +22715,134 @@
         <v>2.7</v>
       </c>
       <c r="R115" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="S115" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="T115" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U115" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V115" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W115" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="X115" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="Y115" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="Z115" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AA115" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB115" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AC115" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AD115" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AE115" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF115" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AG115" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AH115" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AI115" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ115" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AK115" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AL115" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AM115" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN115" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO115" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP115" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AQ115" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AR115" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AS115" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AT115" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AU115" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AV115" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AW115" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AX115" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AY115" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AZ115" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BA115" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BB115" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="BC115" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BD115" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BE115" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BF115" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BG115" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BH115" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -22873,7 +22873,7 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="G116" t="n">
         <v>970</v>
@@ -22888,7 +22888,7 @@
         <v>2.64</v>
       </c>
       <c r="K116" t="n">
-        <v>6.4</v>
+        <v>110</v>
       </c>
       <c r="L116" t="n">
         <v>1.01</v>
@@ -22924,7 +22924,7 @@
         <v>1.15</v>
       </c>
       <c r="W116" t="n">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="X116" t="n">
         <v>1000</v>
@@ -23036,7 +23036,7 @@
       </c>
       <c r="BH116" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -23070,7 +23070,7 @@
         <v>3.9</v>
       </c>
       <c r="G117" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="H117" t="n">
         <v>1.94</v>
@@ -23085,152 +23085,152 @@
         <v>4.1</v>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M117" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O117" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="P117" t="n">
         <v>2.1</v>
       </c>
       <c r="Q117" t="n">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="R117" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S117" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T117" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="U117" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="V117" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="W117" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X117" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Y117" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z117" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AA117" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AB117" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AC117" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AD117" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AE117" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AF117" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AG117" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AH117" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AI117" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AJ117" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AK117" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AL117" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AM117" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AN117" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AO117" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AP117" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AQ117" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AR117" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AS117" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AT117" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AU117" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AV117" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AW117" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AX117" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY117" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AZ117" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BA117" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB117" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BC117" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD117" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE117" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BF117" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BG117" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="BH117" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -23261,34 +23261,34 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>2.34</v>
+        <v>1.04</v>
       </c>
       <c r="G118" t="n">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="H118" t="n">
         <v>2.56</v>
       </c>
       <c r="I118" t="n">
-        <v>3.35</v>
+        <v>4.4</v>
       </c>
       <c r="J118" t="n">
-        <v>3.05</v>
+        <v>2.22</v>
       </c>
       <c r="K118" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="L118" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M118" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O118" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="P118" t="n">
         <v>1.94</v>
@@ -23297,134 +23297,134 @@
         <v>1.67</v>
       </c>
       <c r="R118" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S118" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="T118" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U118" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V118" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W118" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="X118" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Y118" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Z118" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AA118" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AB118" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AC118" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AD118" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AE118" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AF118" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AG118" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AH118" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI118" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AJ118" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AK118" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AL118" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AM118" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AN118" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO118" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP118" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AQ118" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AR118" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AS118" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AT118" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AU118" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV118" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AW118" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AX118" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AY118" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AZ118" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BA118" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BB118" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BC118" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BD118" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BE118" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BF118" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BG118" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BH118" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -23455,170 +23455,170 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="G119" t="n">
-        <v>3.2</v>
+        <v>2.84</v>
       </c>
       <c r="H119" t="n">
-        <v>2.72</v>
+        <v>2.94</v>
       </c>
       <c r="I119" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="J119" t="n">
-        <v>2.82</v>
+        <v>1.45</v>
       </c>
       <c r="K119" t="n">
-        <v>4.7</v>
+        <v>3.85</v>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O119" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="P119" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="Q119" t="n">
         <v>2.04</v>
       </c>
       <c r="R119" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S119" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="T119" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U119" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V119" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W119" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X119" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y119" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z119" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA119" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB119" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC119" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD119" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE119" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF119" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG119" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH119" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI119" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ119" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK119" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL119" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM119" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN119" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO119" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP119" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AQ119" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR119" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AS119" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AT119" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AU119" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AV119" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AW119" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AX119" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AY119" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AZ119" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BA119" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BB119" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BC119" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BD119" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BE119" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BF119" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG119" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH119" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -23649,170 +23649,170 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="G120" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="H120" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="I120" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="J120" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K120" t="n">
         <v>3.45</v>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O120" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="P120" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="Q120" t="n">
         <v>2.34</v>
       </c>
       <c r="R120" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="S120" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="T120" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U120" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V120" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="W120" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X120" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Y120" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z120" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AA120" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AB120" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AC120" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AD120" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AE120" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AF120" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AG120" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AH120" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AI120" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AJ120" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK120" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AL120" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AM120" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN120" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO120" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP120" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AQ120" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AR120" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AS120" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AT120" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AU120" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AV120" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AW120" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AX120" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AY120" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AZ120" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="BA120" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BB120" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="BC120" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BD120" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BE120" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="BF120" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="BG120" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="BH120" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-22.xlsx
@@ -757,55 +757,55 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.86</v>
+        <v>2.96</v>
       </c>
       <c r="G2" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="I2" t="n">
-        <v>2.66</v>
+        <v>2.56</v>
       </c>
       <c r="J2" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K2" t="n">
         <v>3.75</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M2" t="n">
         <v>1.06</v>
       </c>
       <c r="N2" t="n">
+        <v>4</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="U2" t="n">
         <v>2.22</v>
       </c>
-      <c r="O2" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S2" t="n">
-        <v>3</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2.1</v>
-      </c>
       <c r="V2" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="W2" t="n">
         <v>1.5</v>
@@ -817,7 +817,7 @@
         <v>12</v>
       </c>
       <c r="Z2" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AA2" t="n">
         <v>38</v>
@@ -826,13 +826,13 @@
         <v>13.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD2" t="n">
         <v>12.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AF2" t="n">
         <v>24</v>
@@ -841,7 +841,7 @@
         <v>14</v>
       </c>
       <c r="AH2" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI2" t="n">
         <v>40</v>
@@ -874,7 +874,7 @@
         <v>14.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AT2" t="n">
         <v>10.5</v>
@@ -910,7 +910,7 @@
         <v>34</v>
       </c>
       <c r="BE2" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BF2" t="n">
         <v>21</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -975,31 +975,31 @@
         <v>1.02</v>
       </c>
       <c r="N3" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="O3" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="P3" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="Q3" t="n">
         <v>1.37</v>
       </c>
       <c r="R3" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="S3" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="T3" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="U3" t="n">
         <v>3.4</v>
       </c>
       <c r="V3" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W3" t="n">
         <v>1.74</v>
@@ -1050,16 +1050,16 @@
         <v>23</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AN3" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO3" t="n">
         <v>12</v>
       </c>
       <c r="AP3" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AQ3" t="n">
         <v>23</v>
@@ -1068,13 +1068,13 @@
         <v>27</v>
       </c>
       <c r="AS3" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AT3" t="n">
         <v>20</v>
       </c>
       <c r="AU3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AV3" t="n">
         <v>13.5</v>
@@ -1089,7 +1089,7 @@
         <v>11.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BA3" t="n">
         <v>23</v>
@@ -1107,14 +1107,14 @@
         <v>30</v>
       </c>
       <c r="BF3" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BG3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -1366,7 +1366,7 @@
         <v>2.42</v>
       </c>
       <c r="O5" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="P5" t="n">
         <v>2.42</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -1566,19 +1566,19 @@
         <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="R6" t="n">
         <v>1.39</v>
       </c>
       <c r="S6" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T6" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="U6" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="V6" t="n">
         <v>1.96</v>
@@ -1587,16 +1587,16 @@
         <v>1.3</v>
       </c>
       <c r="X6" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y6" t="n">
         <v>9.6</v>
       </c>
       <c r="Z6" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AA6" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AB6" t="n">
         <v>16</v>
@@ -1614,7 +1614,7 @@
         <v>32</v>
       </c>
       <c r="AG6" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AH6" t="n">
         <v>20</v>
@@ -1626,10 +1626,10 @@
         <v>100</v>
       </c>
       <c r="AK6" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AL6" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
         <v>120</v>
@@ -1644,7 +1644,7 @@
         <v>13.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AR6" t="n">
         <v>11</v>
@@ -1671,22 +1671,22 @@
         <v>14.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA6" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="BB6" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BC6" t="n">
         <v>42</v>
       </c>
       <c r="BD6" t="n">
-        <v>46</v>
+        <v>9.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="BF6" t="n">
         <v>42</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -1739,7 +1739,7 @@
         <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K7" t="n">
         <v>1000</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
         <v>1.75</v>
       </c>
       <c r="I8" t="n">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="J8" t="n">
         <v>3.95</v>
@@ -1969,7 +1969,7 @@
         <v>2.24</v>
       </c>
       <c r="V8" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="W8" t="n">
         <v>1.24</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -2118,13 +2118,13 @@
         <v>2.28</v>
       </c>
       <c r="G9" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="H9" t="n">
         <v>3.3</v>
       </c>
       <c r="I9" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="J9" t="n">
         <v>3.25</v>
@@ -2163,10 +2163,10 @@
         <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W9" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="X9" t="n">
         <v>12</v>
@@ -2178,7 +2178,7 @@
         <v>25</v>
       </c>
       <c r="AA9" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AB9" t="n">
         <v>9</v>
@@ -2220,7 +2220,7 @@
         <v>29</v>
       </c>
       <c r="AO9" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
         <v>9.6</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -2527,13 +2527,13 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="O11" t="n">
         <v>1.38</v>
       </c>
       <c r="P11" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q11" t="n">
         <v>2.02</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -2697,13 +2697,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="G12" t="n">
         <v>3.65</v>
       </c>
       <c r="H12" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="I12" t="n">
         <v>2.24</v>
@@ -2712,7 +2712,7 @@
         <v>3.95</v>
       </c>
       <c r="K12" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
@@ -2742,7 +2742,7 @@
         <v>1.38</v>
       </c>
       <c r="U12" t="n">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="V12" t="n">
         <v>1.8</v>
@@ -2805,52 +2805,52 @@
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="AQ12" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AR12" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AS12" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AT12" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU12" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV12" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AW12" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AX12" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="AY12" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AZ12" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BA12" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BB12" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BC12" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BD12" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BE12" t="n">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="BF12" t="n">
         <v>1.01</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -2891,13 +2891,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="G13" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="H13" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="I13" t="n">
         <v>4.6</v>
@@ -2924,25 +2924,25 @@
         <v>3.05</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="R13" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="S13" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="T13" t="n">
         <v>1.5</v>
       </c>
       <c r="U13" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="V13" t="n">
         <v>1.27</v>
       </c>
       <c r="W13" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="X13" t="n">
         <v>42</v>
@@ -2987,28 +2987,28 @@
         <v>19.5</v>
       </c>
       <c r="AL13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AM13" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AN13" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AO13" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AP13" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AQ13" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AR13" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AS13" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AT13" t="n">
         <v>14</v>
@@ -3020,7 +3020,7 @@
         <v>15.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AX13" t="n">
         <v>13.5</v>
@@ -3032,10 +3032,10 @@
         <v>13</v>
       </c>
       <c r="BA13" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BB13" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="BC13" t="n">
         <v>13.5</v>
@@ -3044,7 +3044,7 @@
         <v>19.5</v>
       </c>
       <c r="BE13" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF13" t="n">
         <v>4.7</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -3085,31 +3085,31 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="G14" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="H14" t="n">
         <v>4.8</v>
       </c>
       <c r="I14" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="J14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N14" t="n">
         <v>3.35</v>
-      </c>
-      <c r="K14" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1.8</v>
       </c>
       <c r="O14" t="n">
         <v>1.37</v>
@@ -3121,134 +3121,134 @@
         <v>2.1</v>
       </c>
       <c r="R14" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="S14" t="n">
-        <v>3.15</v>
+        <v>3.85</v>
       </c>
       <c r="T14" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="U14" t="n">
-        <v>1.79</v>
+        <v>1.97</v>
       </c>
       <c r="V14" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W14" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X14" t="n">
-        <v>18</v>
+        <v>12.5</v>
       </c>
       <c r="Y14" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ14" t="n">
         <v>23</v>
       </c>
-      <c r="Z14" t="n">
-        <v>50</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB14" t="n">
+      <c r="AK14" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>9</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF14" t="n">
         <v>11.5</v>
       </c>
-      <c r="AC14" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>29</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>100</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>2.38</v>
-      </c>
       <c r="BG14" t="n">
-        <v>2.38</v>
+        <v>10.5</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -3306,7 +3306,7 @@
         <v>1.51</v>
       </c>
       <c r="O15" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P15" t="n">
         <v>1.51</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -3685,28 +3685,28 @@
         <v>6.6</v>
       </c>
       <c r="L17" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="M17" t="n">
         <v>1.05</v>
       </c>
       <c r="N17" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O17" t="n">
         <v>1.26</v>
       </c>
       <c r="P17" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="R17" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="S17" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="T17" t="n">
         <v>2.44</v>
@@ -3745,7 +3745,7 @@
         <v>300</v>
       </c>
       <c r="AF17" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AG17" t="n">
         <v>11.5</v>
@@ -3754,7 +3754,7 @@
         <v>42</v>
       </c>
       <c r="AI17" t="n">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="AJ17" t="n">
         <v>9</v>
@@ -3772,7 +3772,7 @@
         <v>5.2</v>
       </c>
       <c r="AO17" t="n">
-        <v>420</v>
+        <v>490</v>
       </c>
       <c r="AP17" t="n">
         <v>18</v>
@@ -3784,7 +3784,7 @@
         <v>20</v>
       </c>
       <c r="AS17" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AT17" t="n">
         <v>7.4</v>
@@ -3796,7 +3796,7 @@
         <v>42</v>
       </c>
       <c r="AW17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX17" t="n">
         <v>6.4</v>
@@ -3808,7 +3808,7 @@
         <v>34</v>
       </c>
       <c r="BA17" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BB17" t="n">
         <v>8.4</v>
@@ -3820,17 +3820,17 @@
         <v>42</v>
       </c>
       <c r="BE17" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BF17" t="n">
         <v>4.9</v>
       </c>
       <c r="BG17" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -4076,7 +4076,7 @@
         <v>1.41</v>
       </c>
       <c r="M19" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N19" t="n">
         <v>4</v>
@@ -4088,13 +4088,13 @@
         <v>2.02</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="R19" t="n">
         <v>1.39</v>
       </c>
       <c r="S19" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="T19" t="n">
         <v>1.94</v>
@@ -4172,7 +4172,7 @@
         <v>38</v>
       </c>
       <c r="AS19" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="AT19" t="n">
         <v>8.199999999999999</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -4255,7 +4255,7 @@
         <v>6.2</v>
       </c>
       <c r="H20" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="I20" t="n">
         <v>2.08</v>
@@ -4264,10 +4264,10 @@
         <v>3.45</v>
       </c>
       <c r="K20" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="L20" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M20" t="n">
         <v>1.01</v>
@@ -4276,19 +4276,19 @@
         <v>1.74</v>
       </c>
       <c r="O20" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="P20" t="n">
         <v>1.74</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="R20" t="n">
         <v>1.08</v>
       </c>
       <c r="S20" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="T20" t="n">
         <v>1.01</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -4446,13 +4446,13 @@
         <v>2.34</v>
       </c>
       <c r="G21" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="H21" t="n">
         <v>3</v>
       </c>
       <c r="I21" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J21" t="n">
         <v>3.75</v>
@@ -4473,22 +4473,22 @@
         <v>1.23</v>
       </c>
       <c r="P21" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q21" t="n">
         <v>1.7</v>
       </c>
       <c r="R21" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="S21" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="T21" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="U21" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="V21" t="n">
         <v>1.46</v>
@@ -4512,13 +4512,13 @@
         <v>16</v>
       </c>
       <c r="AC21" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD21" t="n">
         <v>14.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF21" t="n">
         <v>18.5</v>
@@ -4548,7 +4548,7 @@
         <v>15.5</v>
       </c>
       <c r="AO21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP21" t="n">
         <v>18</v>
@@ -4560,7 +4560,7 @@
         <v>19.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AT21" t="n">
         <v>11</v>
@@ -4584,7 +4584,7 @@
         <v>13</v>
       </c>
       <c r="BA21" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB21" t="n">
         <v>24</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
         <v>3.4</v>
       </c>
       <c r="I22" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="J22" t="n">
         <v>3.9</v>
@@ -4661,7 +4661,7 @@
         <v>1.05</v>
       </c>
       <c r="N22" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="O22" t="n">
         <v>1.25</v>
@@ -4673,25 +4673,25 @@
         <v>1.74</v>
       </c>
       <c r="R22" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S22" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="T22" t="n">
         <v>1.66</v>
       </c>
       <c r="U22" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="V22" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W22" t="n">
         <v>1.83</v>
       </c>
       <c r="X22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y22" t="n">
         <v>16.5</v>
@@ -4706,7 +4706,7 @@
         <v>12</v>
       </c>
       <c r="AC22" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD22" t="n">
         <v>14.5</v>
@@ -4754,7 +4754,7 @@
         <v>23</v>
       </c>
       <c r="AS22" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AT22" t="n">
         <v>10.5</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -4831,19 +4831,19 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="G23" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="H23" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="I23" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="J23" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K23" t="n">
         <v>3.9</v>
@@ -4858,7 +4858,7 @@
         <v>4.9</v>
       </c>
       <c r="O23" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P23" t="n">
         <v>2.32</v>
@@ -4867,7 +4867,7 @@
         <v>1.67</v>
       </c>
       <c r="R23" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="S23" t="n">
         <v>2.66</v>
@@ -4876,13 +4876,13 @@
         <v>1.58</v>
       </c>
       <c r="U23" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="V23" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W23" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X23" t="n">
         <v>21</v>
@@ -4897,10 +4897,10 @@
         <v>36</v>
       </c>
       <c r="AB23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AC23" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AD23" t="n">
         <v>13.5</v>
@@ -4921,7 +4921,7 @@
         <v>36</v>
       </c>
       <c r="AJ23" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AK23" t="n">
         <v>30</v>
@@ -4939,13 +4939,13 @@
         <v>15.5</v>
       </c>
       <c r="AP23" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AQ23" t="n">
         <v>12.5</v>
       </c>
       <c r="AR23" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AS23" t="n">
         <v>25</v>
@@ -4975,16 +4975,16 @@
         <v>23</v>
       </c>
       <c r="BB23" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BC23" t="n">
         <v>21</v>
       </c>
       <c r="BD23" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BE23" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BF23" t="n">
         <v>17</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -5028,19 +5028,19 @@
         <v>1.2</v>
       </c>
       <c r="G24" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="H24" t="n">
-        <v>12.5</v>
+        <v>1.04</v>
       </c>
       <c r="I24" t="n">
         <v>28</v>
       </c>
       <c r="J24" t="n">
-        <v>6.4</v>
+        <v>5.4</v>
       </c>
       <c r="K24" t="n">
-        <v>7.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L24" t="n">
         <v>1.27</v>
@@ -5049,37 +5049,37 @@
         <v>1.04</v>
       </c>
       <c r="N24" t="n">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="O24" t="n">
         <v>1.22</v>
       </c>
       <c r="P24" t="n">
-        <v>2.1</v>
+        <v>1.34</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.71</v>
+        <v>1.22</v>
       </c>
       <c r="R24" t="n">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="S24" t="n">
-        <v>2.8</v>
+        <v>2.52</v>
       </c>
       <c r="T24" t="n">
-        <v>1.01</v>
+        <v>2.62</v>
       </c>
       <c r="U24" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="V24" t="n">
         <v>1.03</v>
       </c>
       <c r="W24" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="X24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y24" t="n">
         <v>60</v>
@@ -5091,7 +5091,7 @@
         <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC24" t="n">
         <v>19</v>
@@ -5103,7 +5103,7 @@
         <v>1000</v>
       </c>
       <c r="AF24" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AG24" t="n">
         <v>14.5</v>
@@ -5115,7 +5115,7 @@
         <v>1000</v>
       </c>
       <c r="AJ24" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AK24" t="n">
         <v>19</v>
@@ -5133,62 +5133,62 @@
         <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AR24" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AS24" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AT24" t="n">
         <v>6.4</v>
       </c>
       <c r="AU24" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AV24" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AW24" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AX24" t="n">
         <v>5.7</v>
       </c>
       <c r="AY24" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="AZ24" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BA24" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BB24" t="n">
         <v>7</v>
       </c>
       <c r="BC24" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BD24" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BE24" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BF24" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BG24" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -5222,7 +5222,7 @@
         <v>1.83</v>
       </c>
       <c r="G25" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="H25" t="n">
         <v>4.6</v>
@@ -5249,28 +5249,28 @@
         <v>1.22</v>
       </c>
       <c r="P25" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="R25" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="S25" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="T25" t="n">
         <v>1.55</v>
       </c>
       <c r="U25" t="n">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="V25" t="n">
         <v>1.25</v>
       </c>
       <c r="W25" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="X25" t="n">
         <v>21</v>
@@ -5318,7 +5318,7 @@
         <v>28</v>
       </c>
       <c r="AM25" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AN25" t="n">
         <v>9.199999999999999</v>
@@ -5327,13 +5327,13 @@
         <v>42</v>
       </c>
       <c r="AP25" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AQ25" t="n">
         <v>19</v>
       </c>
       <c r="AR25" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AS25" t="n">
         <v>12.5</v>
@@ -5360,10 +5360,10 @@
         <v>14</v>
       </c>
       <c r="BA25" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BB25" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BC25" t="n">
         <v>13.5</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -5413,13 +5413,13 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="G26" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H26" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="I26" t="n">
         <v>4</v>
@@ -5452,19 +5452,19 @@
         <v>1.53</v>
       </c>
       <c r="S26" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="T26" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="U26" t="n">
         <v>2.38</v>
       </c>
       <c r="V26" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W26" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="X26" t="n">
         <v>27</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -5807,7 +5807,7 @@
         <v>2.34</v>
       </c>
       <c r="H28" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I28" t="n">
         <v>3.35</v>
@@ -5816,7 +5816,7 @@
         <v>3.8</v>
       </c>
       <c r="K28" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="L28" t="n">
         <v>1.01</v>
@@ -5825,25 +5825,25 @@
         <v>1.04</v>
       </c>
       <c r="N28" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="O28" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="P28" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="Q28" t="n">
         <v>1.52</v>
       </c>
       <c r="R28" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="S28" t="n">
-        <v>2.22</v>
+        <v>2.34</v>
       </c>
       <c r="T28" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="U28" t="n">
         <v>2.38</v>
@@ -5903,34 +5903,34 @@
         <v>1000</v>
       </c>
       <c r="AN28" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AO28" t="n">
         <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>2.36</v>
+        <v>2.76</v>
       </c>
       <c r="AQ28" t="n">
-        <v>2.14</v>
+        <v>2.48</v>
       </c>
       <c r="AR28" t="n">
-        <v>2.2</v>
+        <v>2.56</v>
       </c>
       <c r="AS28" t="n">
-        <v>2.28</v>
+        <v>2.66</v>
       </c>
       <c r="AT28" t="n">
         <v>10</v>
       </c>
       <c r="AU28" t="n">
-        <v>1.99</v>
+        <v>2.26</v>
       </c>
       <c r="AV28" t="n">
         <v>10</v>
       </c>
       <c r="AW28" t="n">
-        <v>2.24</v>
+        <v>2.6</v>
       </c>
       <c r="AX28" t="n">
         <v>12.5</v>
@@ -5942,10 +5942,10 @@
         <v>11</v>
       </c>
       <c r="BA28" t="n">
-        <v>2.26</v>
+        <v>2.62</v>
       </c>
       <c r="BB28" t="n">
-        <v>2.22</v>
+        <v>2.58</v>
       </c>
       <c r="BC28" t="n">
         <v>14.5</v>
@@ -5954,17 +5954,17 @@
         <v>19</v>
       </c>
       <c r="BE28" t="n">
-        <v>2.3</v>
+        <v>2.68</v>
       </c>
       <c r="BF28" t="n">
-        <v>2.36</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG28" t="n">
-        <v>2.36</v>
+        <v>2.76</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -6965,22 +6965,22 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="G34" t="n">
         <v>1.79</v>
       </c>
       <c r="H34" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I34" t="n">
         <v>5.6</v>
       </c>
       <c r="J34" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K34" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L34" t="n">
         <v>1.01</v>
@@ -6992,34 +6992,34 @@
         <v>4.6</v>
       </c>
       <c r="O34" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P34" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q34" t="n">
         <v>1.7</v>
       </c>
       <c r="R34" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S34" t="n">
         <v>2.72</v>
       </c>
       <c r="T34" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="U34" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V34" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W34" t="n">
         <v>2.26</v>
       </c>
       <c r="X34" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="Y34" t="n">
         <v>23</v>
@@ -7055,7 +7055,7 @@
         <v>65</v>
       </c>
       <c r="AJ34" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AK34" t="n">
         <v>17.5</v>
@@ -7073,16 +7073,16 @@
         <v>60</v>
       </c>
       <c r="AP34" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AQ34" t="n">
         <v>19.5</v>
       </c>
       <c r="AR34" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AS34" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AT34" t="n">
         <v>9.4</v>
@@ -7091,7 +7091,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV34" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AW34" t="n">
         <v>10.5</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -7159,7 +7159,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="G35" t="n">
         <v>2.12</v>
@@ -7189,25 +7189,25 @@
         <v>1.18</v>
       </c>
       <c r="P35" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="R35" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="S35" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="T35" t="n">
         <v>1.54</v>
       </c>
       <c r="U35" t="n">
-        <v>2.34</v>
+        <v>2.66</v>
       </c>
       <c r="V35" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W35" t="n">
         <v>1.89</v>
@@ -7243,7 +7243,7 @@
         <v>11</v>
       </c>
       <c r="AH35" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AI35" t="n">
         <v>36</v>
@@ -7264,10 +7264,10 @@
         <v>11</v>
       </c>
       <c r="AO35" t="n">
+        <v>21</v>
+      </c>
+      <c r="AP35" t="n">
         <v>22</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>23</v>
       </c>
       <c r="AQ35" t="n">
         <v>18</v>
@@ -7276,7 +7276,7 @@
         <v>25</v>
       </c>
       <c r="AS35" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AT35" t="n">
         <v>13.5</v>
@@ -7312,17 +7312,17 @@
         <v>23</v>
       </c>
       <c r="BE35" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BF35" t="n">
         <v>8.6</v>
       </c>
       <c r="BG35" t="n">
-        <v>8.800000000000001</v>
+        <v>16.5</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -7374,7 +7374,7 @@
         <v>1.36</v>
       </c>
       <c r="M36" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N36" t="n">
         <v>3.15</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -7547,7 +7547,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="G37" t="n">
         <v>1.49</v>
@@ -7562,7 +7562,7 @@
         <v>5.3</v>
       </c>
       <c r="K37" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="L37" t="n">
         <v>1.01</v>
@@ -7589,7 +7589,7 @@
         <v>1.93</v>
       </c>
       <c r="T37" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="U37" t="n">
         <v>1.01</v>
@@ -7655,52 +7655,52 @@
         <v>1000</v>
       </c>
       <c r="AP37" t="n">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="AQ37" t="n">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="AR37" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AS37" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AT37" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AU37" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV37" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW37" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AX37" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AY37" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ37" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA37" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BB37" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BC37" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BD37" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BE37" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BF37" t="n">
         <v>1.01</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -7774,13 +7774,13 @@
         <v>1.08</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="R38" t="n">
         <v>1.08</v>
       </c>
       <c r="S38" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T38" t="n">
         <v>1.01</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -7935,7 +7935,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="G39" t="n">
         <v>2.06</v>
@@ -7950,7 +7950,7 @@
         <v>3.3</v>
       </c>
       <c r="K39" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="L39" t="n">
         <v>1.3</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -8132,10 +8132,10 @@
         <v>2.96</v>
       </c>
       <c r="G40" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="H40" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="I40" t="n">
         <v>2.56</v>
@@ -8153,10 +8153,10 @@
         <v>1.05</v>
       </c>
       <c r="N40" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="O40" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P40" t="n">
         <v>2.2</v>
@@ -8165,7 +8165,7 @@
         <v>1.78</v>
       </c>
       <c r="R40" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S40" t="n">
         <v>2.92</v>
@@ -8174,13 +8174,13 @@
         <v>1.65</v>
       </c>
       <c r="U40" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="V40" t="n">
         <v>1.64</v>
       </c>
       <c r="W40" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="X40" t="n">
         <v>17.5</v>
@@ -8198,7 +8198,7 @@
         <v>15</v>
       </c>
       <c r="AC40" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD40" t="n">
         <v>12</v>
@@ -8282,7 +8282,7 @@
         <v>32</v>
       </c>
       <c r="BE40" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BF40" t="n">
         <v>19.5</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -8338,7 +8338,7 @@
         <v>5</v>
       </c>
       <c r="K41" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L41" t="n">
         <v>1.4</v>
@@ -8356,13 +8356,13 @@
         <v>2.08</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="R41" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S41" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="T41" t="n">
         <v>2.22</v>
@@ -8476,7 +8476,7 @@
         <v>38</v>
       </c>
       <c r="BE41" t="n">
-        <v>48</v>
+        <v>16.5</v>
       </c>
       <c r="BF41" t="n">
         <v>6.6</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -8535,7 +8535,7 @@
         <v>3.2</v>
       </c>
       <c r="L42" t="n">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="M42" t="n">
         <v>1.11</v>
@@ -8556,13 +8556,13 @@
         <v>1.25</v>
       </c>
       <c r="S42" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="T42" t="n">
         <v>1.98</v>
       </c>
       <c r="U42" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="V42" t="n">
         <v>1.37</v>
@@ -8664,10 +8664,10 @@
         <v>30</v>
       </c>
       <c r="BC42" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BD42" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="BE42" t="n">
         <v>18.5</v>
@@ -8676,11 +8676,11 @@
         <v>25</v>
       </c>
       <c r="BG42" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="G43" t="n">
         <v>3.2</v>
@@ -8720,16 +8720,16 @@
         <v>2.5</v>
       </c>
       <c r="I43" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="J43" t="n">
         <v>3.35</v>
       </c>
       <c r="K43" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="L43" t="n">
-        <v>1.02</v>
+        <v>1.36</v>
       </c>
       <c r="M43" t="n">
         <v>1.07</v>
@@ -8741,10 +8741,10 @@
         <v>1.31</v>
       </c>
       <c r="P43" t="n">
-        <v>1.36</v>
+        <v>1.95</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.31</v>
+        <v>1.96</v>
       </c>
       <c r="R43" t="n">
         <v>1.36</v>
@@ -8753,13 +8753,13 @@
         <v>3.3</v>
       </c>
       <c r="T43" t="n">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="U43" t="n">
         <v>2.18</v>
       </c>
       <c r="V43" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W43" t="n">
         <v>1.45</v>
@@ -8813,7 +8813,7 @@
         <v>100</v>
       </c>
       <c r="AN43" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AO43" t="n">
         <v>23</v>
@@ -8828,7 +8828,7 @@
         <v>6</v>
       </c>
       <c r="AS43" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AT43" t="n">
         <v>10.5</v>
@@ -8840,13 +8840,13 @@
         <v>5.3</v>
       </c>
       <c r="AW43" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AX43" t="n">
         <v>6.4</v>
       </c>
       <c r="AY43" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AZ43" t="n">
         <v>6</v>
@@ -8855,13 +8855,13 @@
         <v>7.4</v>
       </c>
       <c r="BB43" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BC43" t="n">
         <v>7.4</v>
       </c>
       <c r="BD43" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BE43" t="n">
         <v>8.4</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -8911,16 +8911,16 @@
         <v>3.2</v>
       </c>
       <c r="H44" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="I44" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="J44" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="K44" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="L44" t="n">
         <v>1.01</v>
@@ -8929,13 +8929,13 @@
         <v>1.09</v>
       </c>
       <c r="N44" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O44" t="n">
         <v>1.36</v>
       </c>
       <c r="P44" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="Q44" t="n">
         <v>2.12</v>
@@ -8947,10 +8947,10 @@
         <v>3.85</v>
       </c>
       <c r="T44" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U44" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V44" t="n">
         <v>1.52</v>
@@ -8959,10 +8959,10 @@
         <v>1.45</v>
       </c>
       <c r="X44" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="Y44" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z44" t="n">
         <v>18.5</v>
@@ -8971,10 +8971,10 @@
         <v>44</v>
       </c>
       <c r="AB44" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC44" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AD44" t="n">
         <v>13</v>
@@ -9013,34 +9013,34 @@
         <v>32</v>
       </c>
       <c r="AP44" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AQ44" t="n">
         <v>10</v>
       </c>
       <c r="AR44" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS44" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="AT44" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU44" t="n">
         <v>6</v>
       </c>
       <c r="AV44" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW44" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="AX44" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY44" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AZ44" t="n">
         <v>14</v>
@@ -9049,26 +9049,26 @@
         <v>34</v>
       </c>
       <c r="BB44" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BC44" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="BD44" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BE44" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF44" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="BG44" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -9102,58 +9102,58 @@
         <v>2.06</v>
       </c>
       <c r="G45" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H45" t="n">
         <v>3.6</v>
       </c>
       <c r="I45" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="J45" t="n">
         <v>3.65</v>
       </c>
       <c r="K45" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L45" t="n">
         <v>1.3</v>
       </c>
       <c r="M45" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N45" t="n">
         <v>4.1</v>
       </c>
       <c r="O45" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P45" t="n">
         <v>2.08</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="R45" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S45" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="T45" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U45" t="n">
         <v>2.24</v>
       </c>
       <c r="V45" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W45" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="X45" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Y45" t="n">
         <v>16</v>
@@ -9168,10 +9168,10 @@
         <v>11</v>
       </c>
       <c r="AC45" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD45" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE45" t="n">
         <v>44</v>
@@ -9201,19 +9201,19 @@
         <v>85</v>
       </c>
       <c r="AN45" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO45" t="n">
         <v>40</v>
       </c>
       <c r="AP45" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AQ45" t="n">
         <v>13.5</v>
       </c>
       <c r="AR45" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS45" t="n">
         <v>9.800000000000001</v>
@@ -9225,7 +9225,7 @@
         <v>7.6</v>
       </c>
       <c r="AV45" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AW45" t="n">
         <v>9</v>
@@ -9243,26 +9243,26 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BB45" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BC45" t="n">
         <v>18.5</v>
       </c>
       <c r="BD45" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BE45" t="n">
         <v>10</v>
       </c>
       <c r="BF45" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BG45" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -9505,7 +9505,7 @@
         <v>3.55</v>
       </c>
       <c r="L47" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="M47" t="n">
         <v>1.07</v>
@@ -9517,7 +9517,7 @@
         <v>1.32</v>
       </c>
       <c r="P47" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="Q47" t="n">
         <v>2</v>
@@ -9589,7 +9589,7 @@
         <v>85</v>
       </c>
       <c r="AN47" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AO47" t="n">
         <v>34</v>
@@ -9628,7 +9628,7 @@
         <v>16</v>
       </c>
       <c r="BA47" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BB47" t="n">
         <v>29</v>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -9714,7 +9714,7 @@
         <v>2.1</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="R48" t="n">
         <v>1.45</v>
@@ -9723,10 +9723,10 @@
         <v>3.15</v>
       </c>
       <c r="T48" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U48" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="V48" t="n">
         <v>1.32</v>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -9884,7 +9884,7 @@
         <v>3.45</v>
       </c>
       <c r="I49" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="J49" t="n">
         <v>3.7</v>
@@ -9893,7 +9893,7 @@
         <v>3.75</v>
       </c>
       <c r="L49" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M49" t="n">
         <v>1.06</v>
@@ -9920,7 +9920,7 @@
         <v>1.68</v>
       </c>
       <c r="U49" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="V49" t="n">
         <v>1.4</v>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -10069,7 +10069,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="G50" t="n">
         <v>1.92</v>
@@ -10078,13 +10078,13 @@
         <v>5.1</v>
       </c>
       <c r="I50" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J50" t="n">
         <v>3.55</v>
       </c>
       <c r="K50" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L50" t="n">
         <v>1.35</v>
@@ -10099,10 +10099,10 @@
         <v>1.35</v>
       </c>
       <c r="P50" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="R50" t="n">
         <v>1.29</v>
@@ -10111,10 +10111,10 @@
         <v>3.7</v>
       </c>
       <c r="T50" t="n">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="U50" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="V50" t="n">
         <v>1.22</v>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -10263,13 +10263,13 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="G51" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="H51" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I51" t="n">
         <v>5.1</v>
@@ -10302,7 +10302,7 @@
         <v>1.33</v>
       </c>
       <c r="S51" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="T51" t="n">
         <v>1.83</v>
@@ -10314,7 +10314,7 @@
         <v>1.24</v>
       </c>
       <c r="W51" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="X51" t="n">
         <v>1000</v>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -10460,10 +10460,10 @@
         <v>1.41</v>
       </c>
       <c r="G52" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="H52" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="I52" t="n">
         <v>8.199999999999999</v>
@@ -10487,16 +10487,16 @@
         <v>1.15</v>
       </c>
       <c r="P52" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="Q52" t="n">
         <v>1.45</v>
       </c>
       <c r="R52" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="S52" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="T52" t="n">
         <v>1.58</v>
@@ -10520,10 +10520,10 @@
         <v>75</v>
       </c>
       <c r="AA52" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AB52" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AC52" t="n">
         <v>13.5</v>
@@ -10541,10 +10541,10 @@
         <v>11</v>
       </c>
       <c r="AH52" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI52" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ52" t="n">
         <v>13.5</v>
@@ -10556,25 +10556,25 @@
         <v>27</v>
       </c>
       <c r="AM52" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AN52" t="n">
         <v>4.6</v>
       </c>
       <c r="AO52" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AP52" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AQ52" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AR52" t="n">
-        <v>50</v>
+        <v>11.5</v>
       </c>
       <c r="AS52" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AT52" t="n">
         <v>11.5</v>
@@ -10583,10 +10583,10 @@
         <v>12</v>
       </c>
       <c r="AV52" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AW52" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AX52" t="n">
         <v>10</v>
@@ -10598,7 +10598,7 @@
         <v>18.5</v>
       </c>
       <c r="BA52" t="n">
-        <v>50</v>
+        <v>11.5</v>
       </c>
       <c r="BB52" t="n">
         <v>11.5</v>
@@ -10607,20 +10607,20 @@
         <v>12</v>
       </c>
       <c r="BD52" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE52" t="n">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="BF52" t="n">
         <v>3.55</v>
       </c>
       <c r="BG52" t="n">
-        <v>11.5</v>
+        <v>55</v>
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -10651,16 +10651,16 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="G53" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="H53" t="n">
         <v>3.8</v>
       </c>
       <c r="I53" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="J53" t="n">
         <v>2.52</v>
@@ -10699,10 +10699,10 @@
         <v>1.01</v>
       </c>
       <c r="V53" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="W53" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="X53" t="n">
         <v>7</v>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -10845,7 +10845,7 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="G54" t="n">
         <v>2.66</v>
@@ -10953,52 +10953,52 @@
         <v>1000</v>
       </c>
       <c r="AP54" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AQ54" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AR54" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AS54" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AT54" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AU54" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV54" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW54" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="AX54" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AY54" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ54" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BA54" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BB54" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BC54" t="n">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="BD54" t="n">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BE54" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BF54" t="n">
         <v>1.01</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -11233,10 +11233,10 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="G56" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="H56" t="n">
         <v>4.7</v>
@@ -11245,10 +11245,10 @@
         <v>5</v>
       </c>
       <c r="J56" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K56" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L56" t="n">
         <v>1.01</v>
@@ -11269,7 +11269,7 @@
         <v>1.67</v>
       </c>
       <c r="R56" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S56" t="n">
         <v>2.72</v>
@@ -11290,55 +11290,55 @@
         <v>23</v>
       </c>
       <c r="Y56" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Z56" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AA56" t="n">
         <v>120</v>
       </c>
       <c r="AB56" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC56" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AD56" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AE56" t="n">
         <v>65</v>
       </c>
       <c r="AF56" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG56" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH56" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI56" t="n">
         <v>65</v>
       </c>
       <c r="AJ56" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AK56" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AL56" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AM56" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN56" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO56" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP56" t="n">
         <v>17.5</v>
@@ -11347,10 +11347,10 @@
         <v>16.5</v>
       </c>
       <c r="AR56" t="n">
-        <v>4.5</v>
+        <v>30</v>
       </c>
       <c r="AS56" t="n">
-        <v>4.8</v>
+        <v>7</v>
       </c>
       <c r="AT56" t="n">
         <v>9.199999999999999</v>
@@ -11362,7 +11362,7 @@
         <v>16</v>
       </c>
       <c r="AW56" t="n">
-        <v>4.6</v>
+        <v>6.6</v>
       </c>
       <c r="AX56" t="n">
         <v>10.5</v>
@@ -11374,7 +11374,7 @@
         <v>14.5</v>
       </c>
       <c r="BA56" t="n">
-        <v>4.6</v>
+        <v>6.6</v>
       </c>
       <c r="BB56" t="n">
         <v>16.5</v>
@@ -11386,17 +11386,17 @@
         <v>22</v>
       </c>
       <c r="BE56" t="n">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="BF56" t="n">
         <v>7.4</v>
       </c>
       <c r="BG56" t="n">
-        <v>4.6</v>
+        <v>6.6</v>
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
         <v>2.12</v>
       </c>
       <c r="G57" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="H57" t="n">
         <v>3.3</v>
@@ -11439,7 +11439,7 @@
         <v>5.2</v>
       </c>
       <c r="J57" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="K57" t="n">
         <v>4.4</v>
@@ -11451,13 +11451,13 @@
         <v>1.01</v>
       </c>
       <c r="N57" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="O57" t="n">
         <v>1.02</v>
       </c>
       <c r="P57" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q57" t="n">
         <v>2.04</v>
@@ -11478,7 +11478,7 @@
         <v>1.24</v>
       </c>
       <c r="W57" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="X57" t="n">
         <v>1000</v>
@@ -11590,7 +11590,7 @@
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -11627,16 +11627,16 @@
         <v>5.4</v>
       </c>
       <c r="H58" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="I58" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="J58" t="n">
         <v>4.5</v>
       </c>
       <c r="K58" t="n">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="L58" t="n">
         <v>1.01</v>
@@ -11645,19 +11645,19 @@
         <v>1.02</v>
       </c>
       <c r="N58" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="O58" t="n">
         <v>1.13</v>
       </c>
       <c r="P58" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="Q58" t="n">
         <v>1.4</v>
       </c>
       <c r="R58" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="S58" t="n">
         <v>1.98</v>
@@ -11666,7 +11666,7 @@
         <v>1.44</v>
       </c>
       <c r="U58" t="n">
-        <v>2.46</v>
+        <v>2.7</v>
       </c>
       <c r="V58" t="n">
         <v>2.28</v>
@@ -11780,11 +11780,11 @@
         <v>4.3</v>
       </c>
       <c r="BG58" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -11818,13 +11818,13 @@
         <v>2.64</v>
       </c>
       <c r="G59" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="H59" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="I59" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="J59" t="n">
         <v>3.75</v>
@@ -11845,28 +11845,28 @@
         <v>1.21</v>
       </c>
       <c r="P59" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="Q59" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="R59" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S59" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="T59" t="n">
         <v>1.56</v>
       </c>
-      <c r="S59" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T59" t="n">
-        <v>1.57</v>
-      </c>
       <c r="U59" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="V59" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W59" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="X59" t="n">
         <v>24</v>
@@ -11978,7 +11978,7 @@
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -12042,10 +12042,10 @@
         <v>3.5</v>
       </c>
       <c r="Q60" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="R60" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="S60" t="n">
         <v>1.84</v>
@@ -12054,7 +12054,7 @@
         <v>1.44</v>
       </c>
       <c r="U60" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="V60" t="n">
         <v>3.05</v>
@@ -12087,7 +12087,7 @@
         <v>14.5</v>
       </c>
       <c r="AF60" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AG60" t="n">
         <v>29</v>
@@ -12105,19 +12105,19 @@
         <v>70</v>
       </c>
       <c r="AL60" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM60" t="n">
         <v>60</v>
       </c>
       <c r="AN60" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AO60" t="n">
         <v>4.3</v>
       </c>
       <c r="AP60" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AQ60" t="n">
         <v>14.5</v>
@@ -12129,7 +12129,7 @@
         <v>13</v>
       </c>
       <c r="AT60" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU60" t="n">
         <v>11</v>
@@ -12141,10 +12141,10 @@
         <v>11.5</v>
       </c>
       <c r="AX60" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY60" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AZ60" t="n">
         <v>15.5</v>
@@ -12153,16 +12153,16 @@
         <v>6.6</v>
       </c>
       <c r="BB60" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC60" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BD60" t="n">
         <v>8</v>
       </c>
-      <c r="BD60" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BE60" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BF60" t="n">
         <v>7.6</v>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -12230,7 +12230,7 @@
         <v>2.1</v>
       </c>
       <c r="O61" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P61" t="n">
         <v>2.1</v>
@@ -12366,7 +12366,7 @@
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -12412,7 +12412,7 @@
         <v>2.82</v>
       </c>
       <c r="K62" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L62" t="n">
         <v>1.01</v>
@@ -12427,10 +12427,10 @@
         <v>1.35</v>
       </c>
       <c r="P62" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q62" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="R62" t="n">
         <v>1.22</v>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -12594,13 +12594,13 @@
         <v>2.38</v>
       </c>
       <c r="G63" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="H63" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I63" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J63" t="n">
         <v>3.3</v>
@@ -12612,25 +12612,25 @@
         <v>1.37</v>
       </c>
       <c r="M63" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N63" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O63" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P63" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="Q63" t="n">
         <v>2.16</v>
       </c>
       <c r="R63" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S63" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="T63" t="n">
         <v>1.82</v>
@@ -12657,7 +12657,7 @@
         <v>60</v>
       </c>
       <c r="AB63" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AC63" t="n">
         <v>7.8</v>
@@ -12708,7 +12708,7 @@
         <v>20</v>
       </c>
       <c r="AS63" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AT63" t="n">
         <v>8.6</v>
@@ -12735,10 +12735,10 @@
         <v>11</v>
       </c>
       <c r="BB63" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BC63" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BD63" t="n">
         <v>36</v>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -12785,19 +12785,19 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="G64" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="H64" t="n">
         <v>3.4</v>
       </c>
       <c r="I64" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="J64" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K64" t="n">
         <v>4</v>
@@ -12809,34 +12809,34 @@
         <v>1.05</v>
       </c>
       <c r="N64" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O64" t="n">
         <v>1.26</v>
       </c>
       <c r="P64" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="Q64" t="n">
         <v>1.78</v>
       </c>
       <c r="R64" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S64" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="T64" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U64" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="V64" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W64" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="X64" t="n">
         <v>22</v>
@@ -12851,19 +12851,19 @@
         <v>75</v>
       </c>
       <c r="AB64" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="AC64" t="n">
         <v>10.5</v>
       </c>
       <c r="AD64" t="n">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="AE64" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="AF64" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG64" t="n">
         <v>13</v>
@@ -12872,37 +12872,37 @@
         <v>20</v>
       </c>
       <c r="AI64" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ64" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AK64" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="AL64" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AM64" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AN64" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AO64" t="n">
         <v>40</v>
       </c>
       <c r="AP64" t="n">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="AQ64" t="n">
         <v>13.5</v>
       </c>
       <c r="AR64" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="AS64" t="n">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="AT64" t="n">
         <v>10</v>
@@ -12914,41 +12914,41 @@
         <v>13</v>
       </c>
       <c r="AW64" t="n">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="AX64" t="n">
         <v>13</v>
       </c>
       <c r="AY64" t="n">
-        <v>3.75</v>
+        <v>4.8</v>
       </c>
       <c r="AZ64" t="n">
         <v>14</v>
       </c>
       <c r="BA64" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="BB64" t="n">
-        <v>4.5</v>
+        <v>5.9</v>
       </c>
       <c r="BC64" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="BD64" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="BE64" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="BF64" t="n">
         <v>10</v>
       </c>
       <c r="BG64" t="n">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -12979,22 +12979,22 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="G65" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H65" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I65" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J65" t="n">
         <v>4.1</v>
       </c>
       <c r="K65" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L65" t="n">
         <v>1.01</v>
@@ -13003,34 +13003,34 @@
         <v>1.03</v>
       </c>
       <c r="N65" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="O65" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="P65" t="n">
         <v>2.48</v>
       </c>
       <c r="Q65" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="R65" t="n">
         <v>1.64</v>
       </c>
       <c r="S65" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="T65" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="U65" t="n">
         <v>1.01</v>
       </c>
       <c r="V65" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W65" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="X65" t="n">
         <v>36</v>
@@ -13045,7 +13045,7 @@
         <v>1000</v>
       </c>
       <c r="AB65" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AC65" t="n">
         <v>12.5</v>
@@ -13090,7 +13090,7 @@
         <v>4.5</v>
       </c>
       <c r="AQ65" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AR65" t="n">
         <v>4.5</v>
@@ -13132,7 +13132,7 @@
         <v>4.4</v>
       </c>
       <c r="BE65" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BF65" t="n">
         <v>7</v>
@@ -13142,7 +13142,7 @@
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -13173,19 +13173,19 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="G66" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="H66" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="I66" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="J66" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K66" t="n">
         <v>3.6</v>
@@ -13203,13 +13203,13 @@
         <v>1.33</v>
       </c>
       <c r="P66" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="Q66" t="n">
         <v>1.99</v>
       </c>
       <c r="R66" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S66" t="n">
         <v>3.5</v>
@@ -13218,13 +13218,13 @@
         <v>1.76</v>
       </c>
       <c r="U66" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="V66" t="n">
         <v>1.51</v>
       </c>
       <c r="W66" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X66" t="n">
         <v>16.5</v>
@@ -13320,7 +13320,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BC66" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD66" t="n">
         <v>8.800000000000001</v>
@@ -13336,7 +13336,7 @@
       </c>
       <c r="BH66" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -13373,10 +13373,10 @@
         <v>2.14</v>
       </c>
       <c r="H67" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I67" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J67" t="n">
         <v>3.25</v>
@@ -13391,25 +13391,25 @@
         <v>1.1</v>
       </c>
       <c r="N67" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O67" t="n">
         <v>1.41</v>
       </c>
       <c r="P67" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="Q67" t="n">
         <v>2.22</v>
       </c>
       <c r="R67" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S67" t="n">
         <v>4.1</v>
       </c>
       <c r="T67" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="U67" t="n">
         <v>2</v>
@@ -13451,13 +13451,13 @@
         <v>11</v>
       </c>
       <c r="AH67" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI67" t="n">
         <v>75</v>
       </c>
       <c r="AJ67" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK67" t="n">
         <v>24</v>
@@ -13469,7 +13469,7 @@
         <v>130</v>
       </c>
       <c r="AN67" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AO67" t="n">
         <v>75</v>
@@ -13484,7 +13484,7 @@
         <v>26</v>
       </c>
       <c r="AS67" t="n">
-        <v>16.5</v>
+        <v>48</v>
       </c>
       <c r="AT67" t="n">
         <v>7.8</v>
@@ -13520,17 +13520,17 @@
         <v>38</v>
       </c>
       <c r="BE67" t="n">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="BF67" t="n">
         <v>16.5</v>
       </c>
       <c r="BG67" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -13573,7 +13573,7 @@
         <v>10.5</v>
       </c>
       <c r="J68" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="K68" t="n">
         <v>6.2</v>
@@ -13585,7 +13585,7 @@
         <v>1.04</v>
       </c>
       <c r="N68" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="O68" t="n">
         <v>1.2</v>
@@ -13594,13 +13594,13 @@
         <v>2.54</v>
       </c>
       <c r="Q68" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="R68" t="n">
         <v>1.61</v>
       </c>
       <c r="S68" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="T68" t="n">
         <v>1.95</v>
@@ -13609,10 +13609,10 @@
         <v>2</v>
       </c>
       <c r="V68" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W68" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="X68" t="n">
         <v>25</v>
@@ -13639,7 +13639,7 @@
         <v>140</v>
       </c>
       <c r="AF68" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG68" t="n">
         <v>10.5</v>
@@ -13654,7 +13654,7 @@
         <v>11.5</v>
       </c>
       <c r="AK68" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AL68" t="n">
         <v>34</v>
@@ -13675,10 +13675,10 @@
         <v>30</v>
       </c>
       <c r="AR68" t="n">
-        <v>15.5</v>
+        <v>50</v>
       </c>
       <c r="AS68" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AT68" t="n">
         <v>9.4</v>
@@ -13690,7 +13690,7 @@
         <v>30</v>
       </c>
       <c r="AW68" t="n">
-        <v>16.5</v>
+        <v>42</v>
       </c>
       <c r="AX68" t="n">
         <v>8</v>
@@ -13702,7 +13702,7 @@
         <v>23</v>
       </c>
       <c r="BA68" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="BB68" t="n">
         <v>10.5</v>
@@ -13714,17 +13714,17 @@
         <v>28</v>
       </c>
       <c r="BE68" t="n">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="BF68" t="n">
         <v>4.7</v>
       </c>
       <c r="BG68" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="BH68" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -13755,7 +13755,7 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="G69" t="n">
         <v>1.98</v>
@@ -13782,22 +13782,22 @@
         <v>4.2</v>
       </c>
       <c r="O69" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P69" t="n">
         <v>2.12</v>
       </c>
       <c r="Q69" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="R69" t="n">
         <v>1.44</v>
       </c>
       <c r="S69" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T69" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="U69" t="n">
         <v>2.22</v>
@@ -13812,13 +13812,13 @@
         <v>16.5</v>
       </c>
       <c r="Y69" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z69" t="n">
         <v>32</v>
       </c>
       <c r="AA69" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AB69" t="n">
         <v>10.5</v>
@@ -13872,7 +13872,7 @@
         <v>28</v>
       </c>
       <c r="AS69" t="n">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="AT69" t="n">
         <v>9.4</v>
@@ -13884,13 +13884,13 @@
         <v>15</v>
       </c>
       <c r="AW69" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="AX69" t="n">
         <v>11.5</v>
       </c>
       <c r="AY69" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ69" t="n">
         <v>16</v>
@@ -13899,7 +13899,7 @@
         <v>40</v>
       </c>
       <c r="BB69" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC69" t="n">
         <v>17.5</v>
@@ -13908,7 +13908,7 @@
         <v>29</v>
       </c>
       <c r="BE69" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="BF69" t="n">
         <v>11</v>
@@ -13918,7 +13918,7 @@
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -13973,22 +13973,22 @@
         <v>1.01</v>
       </c>
       <c r="N70" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="O70" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="P70" t="n">
         <v>1.08</v>
       </c>
       <c r="Q70" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="R70" t="n">
         <v>1.08</v>
       </c>
       <c r="S70" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T70" t="n">
         <v>1.01</v>
@@ -14000,7 +14000,7 @@
         <v>1.01</v>
       </c>
       <c r="W70" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X70" t="n">
         <v>1000</v>
@@ -14112,7 +14112,7 @@
       </c>
       <c r="BH70" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -14170,19 +14170,19 @@
         <v>3.15</v>
       </c>
       <c r="O71" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P71" t="n">
         <v>1.7</v>
       </c>
       <c r="Q71" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="R71" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S71" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="T71" t="n">
         <v>1.97</v>
@@ -14278,7 +14278,7 @@
         <v>15.5</v>
       </c>
       <c r="AY71" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AZ71" t="n">
         <v>18</v>
@@ -14306,7 +14306,7 @@
       </c>
       <c r="BH71" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -14500,7 +14500,7 @@
       </c>
       <c r="BH72" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -14740,7 +14740,7 @@
         <v>3.15</v>
       </c>
       <c r="K74" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L74" t="n">
         <v>1.01</v>
@@ -14752,13 +14752,13 @@
         <v>3.05</v>
       </c>
       <c r="O74" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P74" t="n">
         <v>1.7</v>
       </c>
       <c r="Q74" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="R74" t="n">
         <v>1.26</v>
@@ -14767,10 +14767,10 @@
         <v>4.2</v>
       </c>
       <c r="T74" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="U74" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="V74" t="n">
         <v>1.38</v>
@@ -14791,7 +14791,7 @@
         <v>80</v>
       </c>
       <c r="AB74" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC74" t="n">
         <v>8.6</v>
@@ -14803,7 +14803,7 @@
         <v>55</v>
       </c>
       <c r="AF74" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG74" t="n">
         <v>13.5</v>
@@ -14815,7 +14815,7 @@
         <v>70</v>
       </c>
       <c r="AJ74" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AK74" t="n">
         <v>36</v>
@@ -14842,7 +14842,7 @@
         <v>17.5</v>
       </c>
       <c r="AS74" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AT74" t="n">
         <v>7.8</v>
@@ -14854,7 +14854,7 @@
         <v>11</v>
       </c>
       <c r="AW74" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AX74" t="n">
         <v>11.5</v>
@@ -14863,32 +14863,32 @@
         <v>10</v>
       </c>
       <c r="AZ74" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BA74" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BB74" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BC74" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BD74" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BE74" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BF74" t="n">
         <v>21</v>
       </c>
       <c r="BG74" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BH74" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -14925,7 +14925,7 @@
         <v>2.7</v>
       </c>
       <c r="H75" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I75" t="n">
         <v>3.4</v>
@@ -14934,7 +14934,7 @@
         <v>3.15</v>
       </c>
       <c r="K75" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L75" t="n">
         <v>1.01</v>
@@ -14961,19 +14961,19 @@
         <v>3.7</v>
       </c>
       <c r="T75" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="U75" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="V75" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W75" t="n">
         <v>1.58</v>
       </c>
       <c r="X75" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Y75" t="n">
         <v>15</v>
@@ -14997,7 +14997,7 @@
         <v>60</v>
       </c>
       <c r="AF75" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG75" t="n">
         <v>17</v>
@@ -15009,7 +15009,7 @@
         <v>85</v>
       </c>
       <c r="AJ75" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AK75" t="n">
         <v>46</v>
@@ -15027,62 +15027,62 @@
         <v>1000</v>
       </c>
       <c r="AP75" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="AQ75" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="AR75" t="n">
         <v>15</v>
       </c>
       <c r="AS75" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AT75" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AU75" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AV75" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AW75" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AX75" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY75" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AZ75" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BA75" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BB75" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BC75" t="n">
         <v>2.62</v>
       </c>
-      <c r="AT75" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AU75" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AV75" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AW75" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AX75" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY75" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AZ75" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="BA75" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BB75" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="BC75" t="n">
-        <v>2.54</v>
-      </c>
       <c r="BD75" t="n">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="BE75" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="BF75" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="BG75" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="BH75" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -15122,7 +15122,7 @@
         <v>8.6</v>
       </c>
       <c r="I76" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="J76" t="n">
         <v>4.2</v>
@@ -15131,19 +15131,19 @@
         <v>4.3</v>
       </c>
       <c r="L76" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="M76" t="n">
         <v>1.08</v>
       </c>
       <c r="N76" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="O76" t="n">
         <v>1.38</v>
       </c>
       <c r="P76" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="Q76" t="n">
         <v>2.16</v>
@@ -15155,7 +15155,7 @@
         <v>4</v>
       </c>
       <c r="T76" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="U76" t="n">
         <v>1.69</v>
@@ -15185,7 +15185,7 @@
         <v>10</v>
       </c>
       <c r="AD76" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AE76" t="n">
         <v>170</v>
@@ -15242,7 +15242,7 @@
         <v>29</v>
       </c>
       <c r="AW76" t="n">
-        <v>44</v>
+        <v>17.5</v>
       </c>
       <c r="AX76" t="n">
         <v>7</v>
@@ -15263,7 +15263,7 @@
         <v>16.5</v>
       </c>
       <c r="BD76" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="BE76" t="n">
         <v>17.5</v>
@@ -15276,7 +15276,7 @@
       </c>
       <c r="BH76" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -15307,22 +15307,22 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="G77" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="H77" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I77" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="J77" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="K77" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L77" t="n">
         <v>1.01</v>
@@ -15331,19 +15331,19 @@
         <v>1.04</v>
       </c>
       <c r="N77" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O77" t="n">
         <v>1.24</v>
       </c>
       <c r="P77" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q77" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="R77" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="S77" t="n">
         <v>2.78</v>
@@ -15358,7 +15358,7 @@
         <v>1.03</v>
       </c>
       <c r="W77" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="X77" t="n">
         <v>24</v>
@@ -15397,80 +15397,80 @@
         <v>1000</v>
       </c>
       <c r="AJ77" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AK77" t="n">
         <v>17.5</v>
       </c>
       <c r="AL77" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM77" t="n">
         <v>1000</v>
       </c>
       <c r="AN77" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="AO77" t="n">
         <v>1000</v>
       </c>
       <c r="AP77" t="n">
-        <v>5.5</v>
+        <v>17</v>
       </c>
       <c r="AQ77" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="AR77" t="n">
-        <v>3.6</v>
+        <v>1.93</v>
       </c>
       <c r="AS77" t="n">
-        <v>5.3</v>
+        <v>2.18</v>
       </c>
       <c r="AT77" t="n">
         <v>6</v>
       </c>
       <c r="AU77" t="n">
-        <v>5.3</v>
+        <v>14.5</v>
       </c>
       <c r="AV77" t="n">
-        <v>5.1</v>
+        <v>4</v>
       </c>
       <c r="AW77" t="n">
-        <v>5.3</v>
+        <v>2.18</v>
       </c>
       <c r="AX77" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="AY77" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ77" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BA77" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BB77" t="n">
         <v>6.6</v>
-      </c>
-      <c r="BA77" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BB77" t="n">
-        <v>6</v>
       </c>
       <c r="BC77" t="n">
         <v>12.5</v>
       </c>
       <c r="BD77" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE77" t="n">
-        <v>3.6</v>
+        <v>1.93</v>
       </c>
       <c r="BF77" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="BG77" t="n">
-        <v>3</v>
+        <v>1.94</v>
       </c>
       <c r="BH77" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -15504,7 +15504,7 @@
         <v>1.66</v>
       </c>
       <c r="G78" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="H78" t="n">
         <v>6.2</v>
@@ -15513,7 +15513,7 @@
         <v>7</v>
       </c>
       <c r="J78" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K78" t="n">
         <v>4.1</v>
@@ -15528,7 +15528,7 @@
         <v>3.2</v>
       </c>
       <c r="O78" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P78" t="n">
         <v>1.76</v>
@@ -15552,7 +15552,7 @@
         <v>1.17</v>
       </c>
       <c r="W78" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="X78" t="n">
         <v>15</v>
@@ -15664,7 +15664,7 @@
       </c>
       <c r="BH78" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -15698,22 +15698,22 @@
         <v>5.5</v>
       </c>
       <c r="G79" t="n">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="H79" t="n">
         <v>1.76</v>
       </c>
       <c r="I79" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="J79" t="n">
         <v>3.35</v>
       </c>
       <c r="K79" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L79" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M79" t="n">
         <v>1.07</v>
@@ -15737,7 +15737,7 @@
         <v>4</v>
       </c>
       <c r="T79" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="U79" t="n">
         <v>1.01</v>
@@ -15746,7 +15746,7 @@
         <v>2.12</v>
       </c>
       <c r="W79" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="X79" t="n">
         <v>13.5</v>
@@ -15806,13 +15806,13 @@
         <v>2.12</v>
       </c>
       <c r="AQ79" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AR79" t="n">
         <v>2.12</v>
       </c>
       <c r="AS79" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AT79" t="n">
         <v>2.24</v>
@@ -15839,26 +15839,26 @@
         <v>2.44</v>
       </c>
       <c r="BB79" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="BC79" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="BD79" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="BE79" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="BF79" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="BG79" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="BH79" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -15889,22 +15889,22 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="G80" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="H80" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="I80" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J80" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K80" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L80" t="n">
         <v>1.01</v>
@@ -15925,13 +15925,13 @@
         <v>2.26</v>
       </c>
       <c r="R80" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="S80" t="n">
         <v>3.75</v>
       </c>
       <c r="T80" t="n">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="U80" t="n">
         <v>1.01</v>
@@ -15940,16 +15940,16 @@
         <v>1.32</v>
       </c>
       <c r="W80" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="X80" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Y80" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Z80" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA80" t="n">
         <v>1000</v>
@@ -15961,7 +15961,7 @@
         <v>10.5</v>
       </c>
       <c r="AD80" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE80" t="n">
         <v>85</v>
@@ -15997,62 +15997,62 @@
         <v>1000</v>
       </c>
       <c r="AP80" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="AQ80" t="n">
-        <v>1.89</v>
+        <v>2.18</v>
       </c>
       <c r="AR80" t="n">
-        <v>2</v>
+        <v>2.36</v>
       </c>
       <c r="AS80" t="n">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="AT80" t="n">
-        <v>1.79</v>
+        <v>2.06</v>
       </c>
       <c r="AU80" t="n">
-        <v>1.76</v>
+        <v>2.02</v>
       </c>
       <c r="AV80" t="n">
-        <v>1.94</v>
+        <v>2.26</v>
       </c>
       <c r="AW80" t="n">
-        <v>2.06</v>
+        <v>2.44</v>
       </c>
       <c r="AX80" t="n">
-        <v>1.91</v>
+        <v>2.24</v>
       </c>
       <c r="AY80" t="n">
-        <v>1.88</v>
+        <v>2.18</v>
       </c>
       <c r="AZ80" t="n">
-        <v>1.98</v>
+        <v>2.32</v>
       </c>
       <c r="BA80" t="n">
-        <v>2.06</v>
+        <v>2.46</v>
       </c>
       <c r="BB80" t="n">
-        <v>2.02</v>
+        <v>2.38</v>
       </c>
       <c r="BC80" t="n">
-        <v>2.02</v>
+        <v>2.38</v>
       </c>
       <c r="BD80" t="n">
-        <v>2.04</v>
+        <v>2.42</v>
       </c>
       <c r="BE80" t="n">
-        <v>2.12</v>
+        <v>2.52</v>
       </c>
       <c r="BF80" t="n">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="BG80" t="n">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="BH80" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -16083,13 +16083,13 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="G81" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="H81" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="I81" t="n">
         <v>6.2</v>
@@ -16098,7 +16098,7 @@
         <v>2.92</v>
       </c>
       <c r="K81" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L81" t="n">
         <v>1.01</v>
@@ -16125,7 +16125,7 @@
         <v>4</v>
       </c>
       <c r="T81" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="U81" t="n">
         <v>1.01</v>
@@ -16134,7 +16134,7 @@
         <v>1.2</v>
       </c>
       <c r="W81" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="X81" t="n">
         <v>13.5</v>
@@ -16191,62 +16191,62 @@
         <v>1000</v>
       </c>
       <c r="AP81" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="AQ81" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AR81" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="AS81" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AT81" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="AU81" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AV81" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="AW81" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AX81" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="AY81" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="AZ81" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="BA81" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="BB81" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="BC81" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="BD81" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="BE81" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="BF81" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="BG81" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="BH81" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -16280,19 +16280,19 @@
         <v>1.17</v>
       </c>
       <c r="G82" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="H82" t="n">
         <v>22</v>
       </c>
       <c r="I82" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J82" t="n">
         <v>8.6</v>
       </c>
       <c r="K82" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="L82" t="n">
         <v>1.01</v>
@@ -16316,13 +16316,13 @@
         <v>1.6</v>
       </c>
       <c r="S82" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="T82" t="n">
         <v>2.52</v>
       </c>
       <c r="U82" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="V82" t="n">
         <v>1.03</v>
@@ -16334,28 +16334,28 @@
         <v>29</v>
       </c>
       <c r="Y82" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="Z82" t="n">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="AA82" t="n">
         <v>1000</v>
       </c>
       <c r="AB82" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC82" t="n">
         <v>21</v>
       </c>
       <c r="AD82" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AE82" t="n">
         <v>1000</v>
       </c>
       <c r="AF82" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AG82" t="n">
         <v>13.5</v>
@@ -16364,7 +16364,7 @@
         <v>60</v>
       </c>
       <c r="AI82" t="n">
-        <v>460</v>
+        <v>440</v>
       </c>
       <c r="AJ82" t="n">
         <v>8.199999999999999</v>
@@ -16376,37 +16376,37 @@
         <v>60</v>
       </c>
       <c r="AM82" t="n">
-        <v>440</v>
+        <v>420</v>
       </c>
       <c r="AN82" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="AO82" t="n">
         <v>1000</v>
       </c>
       <c r="AP82" t="n">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="AQ82" t="n">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="AR82" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS82" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AT82" t="n">
         <v>8</v>
-      </c>
-      <c r="AS82" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AT82" t="n">
-        <v>7.8</v>
       </c>
       <c r="AU82" t="n">
         <v>16.5</v>
       </c>
       <c r="AV82" t="n">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="AW82" t="n">
-        <v>8.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AX82" t="n">
         <v>6.2</v>
@@ -16415,32 +16415,32 @@
         <v>11</v>
       </c>
       <c r="AZ82" t="n">
-        <v>7.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BA82" t="n">
-        <v>8</v>
+        <v>11.5</v>
       </c>
       <c r="BB82" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BC82" t="n">
         <v>13</v>
       </c>
       <c r="BD82" t="n">
-        <v>7.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE82" t="n">
-        <v>8</v>
+        <v>11.5</v>
       </c>
       <c r="BF82" t="n">
         <v>3.25</v>
       </c>
       <c r="BG82" t="n">
-        <v>8.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="BH82" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -16474,7 +16474,7 @@
         <v>1.77</v>
       </c>
       <c r="G83" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="H83" t="n">
         <v>4.7</v>
@@ -16495,49 +16495,49 @@
         <v>1.06</v>
       </c>
       <c r="N83" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O83" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P83" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="Q83" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="R83" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S83" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="T83" t="n">
-        <v>1.64</v>
+        <v>1.81</v>
       </c>
       <c r="U83" t="n">
-        <v>1.91</v>
+        <v>2.12</v>
       </c>
       <c r="V83" t="n">
         <v>1.23</v>
       </c>
       <c r="W83" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="X83" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y83" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Z83" t="n">
         <v>40</v>
       </c>
       <c r="AA83" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AB83" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AC83" t="n">
         <v>9.199999999999999</v>
@@ -16561,7 +16561,7 @@
         <v>75</v>
       </c>
       <c r="AJ83" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AK83" t="n">
         <v>19</v>
@@ -16588,7 +16588,7 @@
         <v>32</v>
       </c>
       <c r="AS83" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AT83" t="n">
         <v>8.6</v>
@@ -16597,10 +16597,10 @@
         <v>8</v>
       </c>
       <c r="AV83" t="n">
-        <v>17</v>
+        <v>7.8</v>
       </c>
       <c r="AW83" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AX83" t="n">
         <v>10</v>
@@ -16612,29 +16612,29 @@
         <v>16.5</v>
       </c>
       <c r="BA83" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BB83" t="n">
         <v>17</v>
       </c>
       <c r="BC83" t="n">
-        <v>16</v>
+        <v>7.6</v>
       </c>
       <c r="BD83" t="n">
         <v>28</v>
       </c>
       <c r="BE83" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BF83" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BG83" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BH83" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -16665,16 +16665,16 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="G84" t="n">
         <v>2.56</v>
       </c>
       <c r="H84" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="I84" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="J84" t="n">
         <v>3</v>
@@ -16701,10 +16701,10 @@
         <v>1.92</v>
       </c>
       <c r="R84" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="S84" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T84" t="n">
         <v>1.01</v>
@@ -16713,7 +16713,7 @@
         <v>1.01</v>
       </c>
       <c r="V84" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="W84" t="n">
         <v>1.64</v>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="BH84" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -16865,13 +16865,13 @@
         <v>17</v>
       </c>
       <c r="H85" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="I85" t="n">
         <v>1.3</v>
       </c>
       <c r="J85" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="K85" t="n">
         <v>6.4</v>
@@ -16889,19 +16889,19 @@
         <v>1.28</v>
       </c>
       <c r="P85" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="Q85" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="R85" t="n">
         <v>1.38</v>
       </c>
       <c r="S85" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T85" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="U85" t="n">
         <v>1.56</v>
@@ -16970,7 +16970,7 @@
         <v>14.5</v>
       </c>
       <c r="AQ85" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AR85" t="n">
         <v>5.9</v>
@@ -16979,10 +16979,10 @@
         <v>8</v>
       </c>
       <c r="AT85" t="n">
-        <v>27</v>
+        <v>7.6</v>
       </c>
       <c r="AU85" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AV85" t="n">
         <v>9.6</v>
@@ -17018,11 +17018,11 @@
         <v>9.4</v>
       </c>
       <c r="BG85" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BH85" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -17062,7 +17062,7 @@
         <v>1.64</v>
       </c>
       <c r="I86" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="J86" t="n">
         <v>3.4</v>
@@ -17101,7 +17101,7 @@
         <v>1.01</v>
       </c>
       <c r="V86" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="W86" t="n">
         <v>1.13</v>
@@ -17161,52 +17161,52 @@
         <v>1000</v>
       </c>
       <c r="AP86" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AQ86" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR86" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AS86" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT86" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AU86" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV86" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AW86" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX86" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="AY86" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="AZ86" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BA86" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BB86" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BC86" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BD86" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BE86" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BF86" t="n">
         <v>1.01</v>
@@ -17216,7 +17216,7 @@
       </c>
       <c r="BH86" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -17253,7 +17253,7 @@
         <v>5.6</v>
       </c>
       <c r="H87" t="n">
-        <v>2.14</v>
+        <v>1.04</v>
       </c>
       <c r="I87" t="n">
         <v>2.6</v>
@@ -17262,7 +17262,7 @@
         <v>2.28</v>
       </c>
       <c r="K87" t="n">
-        <v>4</v>
+        <v>950</v>
       </c>
       <c r="L87" t="n">
         <v>1.01</v>
@@ -17274,7 +17274,7 @@
         <v>1.54</v>
       </c>
       <c r="O87" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="P87" t="n">
         <v>1.54</v>
@@ -17358,7 +17358,7 @@
         <v>2.32</v>
       </c>
       <c r="AQ87" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AR87" t="n">
         <v>9.199999999999999</v>
@@ -17397,7 +17397,7 @@
         <v>2.26</v>
       </c>
       <c r="BD87" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="BE87" t="n">
         <v>2.32</v>
@@ -17410,7 +17410,7 @@
       </c>
       <c r="BH87" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -17444,10 +17444,10 @@
         <v>2.08</v>
       </c>
       <c r="G88" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="H88" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I88" t="n">
         <v>5.4</v>
@@ -17507,7 +17507,7 @@
         <v>200</v>
       </c>
       <c r="AB88" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AC88" t="n">
         <v>8.6</v>
@@ -17519,7 +17519,7 @@
         <v>1000</v>
       </c>
       <c r="AF88" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG88" t="n">
         <v>15</v>
@@ -17531,7 +17531,7 @@
         <v>200</v>
       </c>
       <c r="AJ88" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK88" t="n">
         <v>44</v>
@@ -17543,7 +17543,7 @@
         <v>430</v>
       </c>
       <c r="AN88" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AO88" t="n">
         <v>1000</v>
@@ -17555,10 +17555,10 @@
         <v>8.4</v>
       </c>
       <c r="AR88" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AS88" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="AT88" t="n">
         <v>5</v>
@@ -17570,7 +17570,7 @@
         <v>18.5</v>
       </c>
       <c r="AW88" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AX88" t="n">
         <v>8.6</v>
@@ -17579,32 +17579,32 @@
         <v>10</v>
       </c>
       <c r="AZ88" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BA88" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BB88" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BC88" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BD88" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BE88" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BF88" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BG88" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BH88" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -17668,7 +17668,7 @@
         <v>2.28</v>
       </c>
       <c r="Q89" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="R89" t="n">
         <v>1.52</v>
@@ -17680,7 +17680,7 @@
         <v>2.18</v>
       </c>
       <c r="U89" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="V89" t="n">
         <v>4.1</v>
@@ -17722,7 +17722,7 @@
         <v>34</v>
       </c>
       <c r="AI89" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ89" t="n">
         <v>520</v>
@@ -17798,7 +17798,7 @@
       </c>
       <c r="BH89" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -17862,13 +17862,13 @@
         <v>1.67</v>
       </c>
       <c r="Q90" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="R90" t="n">
         <v>1.08</v>
       </c>
       <c r="S90" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="T90" t="n">
         <v>1.01</v>
@@ -17992,7 +17992,7 @@
       </c>
       <c r="BH90" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -18032,10 +18032,10 @@
         <v>1.62</v>
       </c>
       <c r="I91" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="J91" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="K91" t="n">
         <v>5</v>
@@ -18056,13 +18056,13 @@
         <v>2.04</v>
       </c>
       <c r="Q91" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="R91" t="n">
         <v>1.12</v>
       </c>
       <c r="S91" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="T91" t="n">
         <v>1.01</v>
@@ -18071,7 +18071,7 @@
         <v>1.01</v>
       </c>
       <c r="V91" t="n">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="W91" t="n">
         <v>1.16</v>
@@ -18186,7 +18186,7 @@
       </c>
       <c r="BH91" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -18235,19 +18235,19 @@
         <v>4.1</v>
       </c>
       <c r="L92" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="M92" t="n">
         <v>1.04</v>
       </c>
       <c r="N92" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="O92" t="n">
         <v>1.21</v>
       </c>
       <c r="P92" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="Q92" t="n">
         <v>1.65</v>
@@ -18256,7 +18256,7 @@
         <v>1.6</v>
       </c>
       <c r="S92" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="T92" t="n">
         <v>1.59</v>
@@ -18346,7 +18346,7 @@
         <v>10</v>
       </c>
       <c r="AW92" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AX92" t="n">
         <v>26</v>
@@ -18380,7 +18380,7 @@
       </c>
       <c r="BH92" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -18441,10 +18441,10 @@
         <v>1.46</v>
       </c>
       <c r="P93" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="Q93" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R93" t="n">
         <v>1.22</v>
@@ -18456,7 +18456,7 @@
         <v>1.87</v>
       </c>
       <c r="U93" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="V93" t="n">
         <v>1.25</v>
@@ -18465,7 +18465,7 @@
         <v>1.89</v>
       </c>
       <c r="X93" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Y93" t="n">
         <v>13</v>
@@ -18486,7 +18486,7 @@
         <v>20</v>
       </c>
       <c r="AE93" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AF93" t="n">
         <v>11.5</v>
@@ -18498,13 +18498,13 @@
         <v>23</v>
       </c>
       <c r="AI93" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ93" t="n">
         <v>26</v>
       </c>
       <c r="AK93" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL93" t="n">
         <v>55</v>
@@ -18522,13 +18522,13 @@
         <v>8.6</v>
       </c>
       <c r="AQ93" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AR93" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS93" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AT93" t="n">
         <v>6.4</v>
@@ -18540,7 +18540,7 @@
         <v>17</v>
       </c>
       <c r="AW93" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AX93" t="n">
         <v>10</v>
@@ -18552,29 +18552,29 @@
         <v>19.5</v>
       </c>
       <c r="BA93" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BB93" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC93" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD93" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE93" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="BF93" t="n">
         <v>16.5</v>
       </c>
       <c r="BG93" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BH93" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -18665,7 +18665,7 @@
         <v>14.5</v>
       </c>
       <c r="Z94" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AA94" t="n">
         <v>1000</v>
@@ -18713,62 +18713,62 @@
         <v>1000</v>
       </c>
       <c r="AP94" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="AQ94" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AR94" t="n">
         <v>18.5</v>
       </c>
       <c r="AS94" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AT94" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AU94" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="AV94" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="AW94" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AX94" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="AY94" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="AZ94" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="BA94" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="BB94" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="BC94" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="BD94" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="BE94" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="BF94" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="BG94" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="BH94" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -18962,7 +18962,7 @@
       </c>
       <c r="BH95" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -19026,13 +19026,13 @@
         <v>1.08</v>
       </c>
       <c r="Q96" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="R96" t="n">
         <v>1.08</v>
       </c>
       <c r="S96" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T96" t="n">
         <v>1.01</v>
@@ -19156,7 +19156,7 @@
       </c>
       <c r="BH96" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -19202,7 +19202,7 @@
         <v>3.4</v>
       </c>
       <c r="K97" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L97" t="n">
         <v>1.01</v>
@@ -19350,7 +19350,7 @@
       </c>
       <c r="BH97" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -19381,7 +19381,7 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="G98" t="n">
         <v>2.1</v>
@@ -19408,13 +19408,13 @@
         <v>1.03</v>
       </c>
       <c r="O98" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P98" t="n">
         <v>1.32</v>
       </c>
       <c r="Q98" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="R98" t="n">
         <v>1.31</v>
@@ -19462,10 +19462,10 @@
         <v>17.5</v>
       </c>
       <c r="AG98" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH98" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI98" t="n">
         <v>85</v>
@@ -19489,62 +19489,62 @@
         <v>1000</v>
       </c>
       <c r="AP98" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="AQ98" t="n">
         <v>10.5</v>
       </c>
       <c r="AR98" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AS98" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AT98" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AU98" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AV98" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW98" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AX98" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY98" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AZ98" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BA98" t="n">
         <v>2.22</v>
       </c>
-      <c r="AT98" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AU98" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AV98" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AW98" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AX98" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AY98" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AZ98" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="BA98" t="n">
-        <v>2.16</v>
-      </c>
       <c r="BB98" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="BC98" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="BD98" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="BE98" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="BF98" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="BG98" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="BH98" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -19614,13 +19614,13 @@
         <v>1.25</v>
       </c>
       <c r="S99" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="T99" t="n">
         <v>2.02</v>
       </c>
       <c r="U99" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="V99" t="n">
         <v>1.27</v>
@@ -19674,7 +19674,7 @@
         <v>60</v>
       </c>
       <c r="AM99" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AN99" t="n">
         <v>26</v>
@@ -19683,13 +19683,13 @@
         <v>120</v>
       </c>
       <c r="AP99" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AQ99" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AR99" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AS99" t="n">
         <v>5.6</v>
@@ -19713,7 +19713,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ99" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BA99" t="n">
         <v>5.5</v>
@@ -19722,23 +19722,23 @@
         <v>4.8</v>
       </c>
       <c r="BC99" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BD99" t="n">
         <v>5.2</v>
       </c>
       <c r="BE99" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BF99" t="n">
         <v>15.5</v>
       </c>
       <c r="BG99" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BH99" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -19772,19 +19772,19 @@
         <v>1.87</v>
       </c>
       <c r="G100" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="H100" t="n">
         <v>4.4</v>
       </c>
       <c r="I100" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J100" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="K100" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L100" t="n">
         <v>1.01</v>
@@ -19799,10 +19799,10 @@
         <v>1.34</v>
       </c>
       <c r="P100" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="Q100" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R100" t="n">
         <v>1.33</v>
@@ -19814,22 +19814,22 @@
         <v>1.87</v>
       </c>
       <c r="U100" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V100" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W100" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="X100" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Y100" t="n">
         <v>15.5</v>
       </c>
       <c r="Z100" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="AA100" t="n">
         <v>130</v>
@@ -19841,7 +19841,7 @@
         <v>8.6</v>
       </c>
       <c r="AD100" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AE100" t="n">
         <v>65</v>
@@ -19865,7 +19865,7 @@
         <v>21</v>
       </c>
       <c r="AL100" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AM100" t="n">
         <v>150</v>
@@ -19874,19 +19874,19 @@
         <v>14.5</v>
       </c>
       <c r="AO100" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AP100" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AQ100" t="n">
         <v>13.5</v>
       </c>
       <c r="AR100" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AS100" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT100" t="n">
         <v>7.4</v>
@@ -19910,7 +19910,7 @@
         <v>18</v>
       </c>
       <c r="BA100" t="n">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="BB100" t="n">
         <v>19</v>
@@ -19919,20 +19919,20 @@
         <v>18</v>
       </c>
       <c r="BD100" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="BE100" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF100" t="n">
         <v>10.5</v>
       </c>
       <c r="BG100" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BH100" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -19963,10 +19963,10 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G101" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="H101" t="n">
         <v>3.95</v>
@@ -19975,7 +19975,7 @@
         <v>4.6</v>
       </c>
       <c r="J101" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="K101" t="n">
         <v>3.4</v>
@@ -20011,10 +20011,10 @@
         <v>1.01</v>
       </c>
       <c r="V101" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W101" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="X101" t="n">
         <v>10.5</v>
@@ -20029,7 +20029,7 @@
         <v>120</v>
       </c>
       <c r="AB101" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC101" t="n">
         <v>8.6</v>
@@ -20038,7 +20038,7 @@
         <v>22</v>
       </c>
       <c r="AE101" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AF101" t="n">
         <v>15</v>
@@ -20071,16 +20071,16 @@
         <v>120</v>
       </c>
       <c r="AP101" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ101" t="n">
         <v>10</v>
       </c>
       <c r="AR101" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AS101" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AT101" t="n">
         <v>6.4</v>
@@ -20092,7 +20092,7 @@
         <v>15.5</v>
       </c>
       <c r="AW101" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AX101" t="n">
         <v>10.5</v>
@@ -20104,29 +20104,29 @@
         <v>19.5</v>
       </c>
       <c r="BA101" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB101" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC101" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BD101" t="n">
         <v>4.5</v>
       </c>
-      <c r="BB101" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BC101" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BD101" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BE101" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BF101" t="n">
         <v>20</v>
       </c>
       <c r="BG101" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BH101" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -20166,7 +20166,7 @@
         <v>2.12</v>
       </c>
       <c r="I102" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="J102" t="n">
         <v>3.9</v>
@@ -20184,13 +20184,13 @@
         <v>4.9</v>
       </c>
       <c r="O102" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="P102" t="n">
         <v>2.34</v>
       </c>
       <c r="Q102" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="R102" t="n">
         <v>1.53</v>
@@ -20199,13 +20199,13 @@
         <v>2.62</v>
       </c>
       <c r="T102" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="U102" t="n">
         <v>2.44</v>
       </c>
       <c r="V102" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="W102" t="n">
         <v>1.39</v>
@@ -20226,10 +20226,10 @@
         <v>17.5</v>
       </c>
       <c r="AC102" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AD102" t="n">
-        <v>210</v>
+        <v>260</v>
       </c>
       <c r="AE102" t="n">
         <v>21</v>
@@ -20262,55 +20262,55 @@
         <v>26</v>
       </c>
       <c r="AO102" t="n">
-        <v>270</v>
+        <v>340</v>
       </c>
       <c r="AP102" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AQ102" t="n">
         <v>6.2</v>
       </c>
       <c r="AR102" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AS102" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT102" t="n">
         <v>7</v>
       </c>
-      <c r="AS102" t="n">
+      <c r="AU102" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AV102" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AW102" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AX102" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY102" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AZ102" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BA102" t="n">
         <v>8.4</v>
       </c>
-      <c r="AT102" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU102" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AV102" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AW102" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AX102" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AY102" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AZ102" t="n">
-        <v>7</v>
-      </c>
-      <c r="BA102" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BB102" t="n">
-        <v>2.26</v>
+        <v>2.44</v>
       </c>
       <c r="BC102" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BD102" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE102" t="n">
-        <v>2.28</v>
+        <v>2.48</v>
       </c>
       <c r="BF102" t="n">
         <v>19.5</v>
@@ -20320,7 +20320,7 @@
       </c>
       <c r="BH102" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -20375,7 +20375,7 @@
         <v>1.1</v>
       </c>
       <c r="N103" t="n">
-        <v>2.8</v>
+        <v>1.98</v>
       </c>
       <c r="O103" t="n">
         <v>1.36</v>
@@ -20514,7 +20514,7 @@
       </c>
       <c r="BH103" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -20653,52 +20653,52 @@
         <v>1000</v>
       </c>
       <c r="AP104" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ104" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AR104" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS104" t="n">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="AT104" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU104" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AV104" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AW104" t="n">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="AX104" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY104" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AZ104" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BA104" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BB104" t="n">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="BC104" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD104" t="n">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="BE104" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BF104" t="n">
         <v>1.01</v>
@@ -20708,7 +20708,7 @@
       </c>
       <c r="BH104" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -20742,10 +20742,10 @@
         <v>3.8</v>
       </c>
       <c r="G105" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="H105" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="I105" t="n">
         <v>2.14</v>
@@ -20763,16 +20763,16 @@
         <v>1.08</v>
       </c>
       <c r="N105" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="O105" t="n">
         <v>1.35</v>
       </c>
       <c r="P105" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q105" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="R105" t="n">
         <v>1.34</v>
@@ -20814,7 +20814,7 @@
         <v>11.5</v>
       </c>
       <c r="AE105" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF105" t="n">
         <v>29</v>
@@ -20826,7 +20826,7 @@
         <v>19</v>
       </c>
       <c r="AI105" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ105" t="n">
         <v>1000</v>
@@ -20844,7 +20844,7 @@
         <v>55</v>
       </c>
       <c r="AO105" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AP105" t="n">
         <v>12</v>
@@ -20856,7 +20856,7 @@
         <v>11.5</v>
       </c>
       <c r="AS105" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="AT105" t="n">
         <v>11.5</v>
@@ -20871,7 +20871,7 @@
         <v>19.5</v>
       </c>
       <c r="AX105" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AY105" t="n">
         <v>14</v>
@@ -20880,29 +20880,29 @@
         <v>16.5</v>
       </c>
       <c r="BA105" t="n">
-        <v>32</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB105" t="n">
-        <v>55</v>
+        <v>10.5</v>
       </c>
       <c r="BC105" t="n">
-        <v>36</v>
+        <v>9.6</v>
       </c>
       <c r="BD105" t="n">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="BE105" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BF105" t="n">
-        <v>40</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG105" t="n">
         <v>14.5</v>
       </c>
       <c r="BH105" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -20942,22 +20942,22 @@
         <v>1.71</v>
       </c>
       <c r="I106" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="J106" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K106" t="n">
         <v>4.4</v>
       </c>
       <c r="L106" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="M106" t="n">
         <v>1.06</v>
       </c>
       <c r="N106" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O106" t="n">
         <v>1.27</v>
@@ -20972,16 +20972,16 @@
         <v>1.45</v>
       </c>
       <c r="S106" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="T106" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="U106" t="n">
         <v>2.12</v>
       </c>
       <c r="V106" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="W106" t="n">
         <v>1.22</v>
@@ -20993,13 +20993,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="Z106" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AA106" t="n">
         <v>17</v>
       </c>
       <c r="AB106" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AC106" t="n">
         <v>9.4</v>
@@ -21008,7 +21008,7 @@
         <v>10</v>
       </c>
       <c r="AE106" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AF106" t="n">
         <v>42</v>
@@ -21017,7 +21017,7 @@
         <v>21</v>
       </c>
       <c r="AH106" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI106" t="n">
         <v>32</v>
@@ -21044,7 +21044,7 @@
         <v>16</v>
       </c>
       <c r="AQ106" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AR106" t="n">
         <v>9.6</v>
@@ -21077,7 +21077,7 @@
         <v>29</v>
       </c>
       <c r="BB106" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="BC106" t="n">
         <v>32</v>
@@ -21089,14 +21089,14 @@
         <v>38</v>
       </c>
       <c r="BF106" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="BG106" t="n">
         <v>8.4</v>
       </c>
       <c r="BH106" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -21235,52 +21235,52 @@
         <v>1000</v>
       </c>
       <c r="AP107" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AQ107" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AR107" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS107" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AT107" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AU107" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV107" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW107" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="AX107" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY107" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ107" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BA107" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BB107" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC107" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BD107" t="n">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="BE107" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BF107" t="n">
         <v>1.01</v>
@@ -21290,7 +21290,7 @@
       </c>
       <c r="BH107" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -21324,7 +21324,7 @@
         <v>3.65</v>
       </c>
       <c r="G108" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="H108" t="n">
         <v>2.3</v>
@@ -21339,7 +21339,7 @@
         <v>3.3</v>
       </c>
       <c r="L108" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M108" t="n">
         <v>1.1</v>
@@ -21366,7 +21366,7 @@
         <v>1.97</v>
       </c>
       <c r="U108" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="V108" t="n">
         <v>1.7</v>
@@ -21378,7 +21378,7 @@
         <v>10.5</v>
       </c>
       <c r="Y108" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="Z108" t="n">
         <v>13.5</v>
@@ -21411,13 +21411,13 @@
         <v>55</v>
       </c>
       <c r="AJ108" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AK108" t="n">
         <v>55</v>
       </c>
       <c r="AL108" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AM108" t="n">
         <v>160</v>
@@ -21438,7 +21438,7 @@
         <v>12</v>
       </c>
       <c r="AS108" t="n">
-        <v>9.199999999999999</v>
+        <v>23</v>
       </c>
       <c r="AT108" t="n">
         <v>10</v>
@@ -21462,7 +21462,7 @@
         <v>18.5</v>
       </c>
       <c r="BA108" t="n">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="BB108" t="n">
         <v>12.5</v>
@@ -21471,20 +21471,20 @@
         <v>12</v>
       </c>
       <c r="BD108" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="BE108" t="n">
         <v>11.5</v>
       </c>
       <c r="BF108" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="BG108" t="n">
         <v>22</v>
       </c>
       <c r="BH108" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -21515,13 +21515,13 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="G109" t="n">
         <v>10.5</v>
       </c>
       <c r="H109" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="I109" t="n">
         <v>1.87</v>
@@ -21566,7 +21566,7 @@
         <v>2.14</v>
       </c>
       <c r="W109" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X109" t="n">
         <v>1000</v>
@@ -21623,52 +21623,52 @@
         <v>1000</v>
       </c>
       <c r="AP109" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AQ109" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR109" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AS109" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AT109" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU109" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV109" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AW109" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AX109" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="AY109" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ109" t="n">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="BA109" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BB109" t="n">
-        <v>100</v>
+        <v>1.01</v>
       </c>
       <c r="BC109" t="n">
-        <v>75</v>
+        <v>1.01</v>
       </c>
       <c r="BD109" t="n">
-        <v>90</v>
+        <v>1.01</v>
       </c>
       <c r="BE109" t="n">
-        <v>100</v>
+        <v>1.01</v>
       </c>
       <c r="BF109" t="n">
         <v>1.01</v>
@@ -21678,7 +21678,7 @@
       </c>
       <c r="BH109" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -21709,13 +21709,13 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G110" t="n">
         <v>3.5</v>
       </c>
       <c r="H110" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="I110" t="n">
         <v>2.7</v>
@@ -21730,25 +21730,25 @@
         <v>1.01</v>
       </c>
       <c r="M110" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N110" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="O110" t="n">
         <v>1.49</v>
       </c>
       <c r="P110" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="Q110" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="R110" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S110" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="T110" t="n">
         <v>1.89</v>
@@ -21763,7 +21763,7 @@
         <v>1.4</v>
       </c>
       <c r="X110" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Y110" t="n">
         <v>9.199999999999999</v>
@@ -21772,7 +21772,7 @@
         <v>18</v>
       </c>
       <c r="AA110" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AB110" t="n">
         <v>11</v>
@@ -21796,10 +21796,10 @@
         <v>26</v>
       </c>
       <c r="AI110" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ110" t="n">
         <v>70</v>
-      </c>
-      <c r="AJ110" t="n">
-        <v>75</v>
       </c>
       <c r="AK110" t="n">
         <v>60</v>
@@ -21808,13 +21808,13 @@
         <v>70</v>
       </c>
       <c r="AM110" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AN110" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AO110" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AP110" t="n">
         <v>8.6</v>
@@ -21838,7 +21838,7 @@
         <v>9.6</v>
       </c>
       <c r="AW110" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AX110" t="n">
         <v>16</v>
@@ -21850,29 +21850,29 @@
         <v>16.5</v>
       </c>
       <c r="BA110" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BB110" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BC110" t="n">
         <v>5.5</v>
       </c>
-      <c r="BC110" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BD110" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BE110" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BF110" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BG110" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BH110" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -21903,10 +21903,10 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G111" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="H111" t="n">
         <v>3.75</v>
@@ -21915,10 +21915,10 @@
         <v>4.5</v>
       </c>
       <c r="J111" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K111" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L111" t="n">
         <v>1.01</v>
@@ -21927,13 +21927,13 @@
         <v>1.11</v>
       </c>
       <c r="N111" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="O111" t="n">
         <v>1.48</v>
       </c>
       <c r="P111" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="Q111" t="n">
         <v>2.42</v>
@@ -21954,7 +21954,7 @@
         <v>1.3</v>
       </c>
       <c r="W111" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="X111" t="n">
         <v>11.5</v>
@@ -22011,7 +22011,7 @@
         <v>1000</v>
       </c>
       <c r="AP111" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AQ111" t="n">
         <v>5</v>
@@ -22066,7 +22066,7 @@
       </c>
       <c r="BH111" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -22106,10 +22106,10 @@
         <v>4.5</v>
       </c>
       <c r="I112" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="J112" t="n">
-        <v>2.54</v>
+        <v>2.64</v>
       </c>
       <c r="K112" t="n">
         <v>4.2</v>
@@ -22260,7 +22260,7 @@
       </c>
       <c r="BH112" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -22297,7 +22297,7 @@
         <v>2.82</v>
       </c>
       <c r="H113" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="I113" t="n">
         <v>3</v>
@@ -22318,16 +22318,16 @@
         <v>3.15</v>
       </c>
       <c r="O113" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="P113" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="Q113" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R113" t="n">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="S113" t="n">
         <v>3.55</v>
@@ -22399,52 +22399,52 @@
         <v>1000</v>
       </c>
       <c r="AP113" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ113" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR113" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS113" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="AT113" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AU113" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV113" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AW113" t="n">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="AX113" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AY113" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ113" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BA113" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BB113" t="n">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="BC113" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BD113" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BE113" t="n">
-        <v>70</v>
+        <v>1.01</v>
       </c>
       <c r="BF113" t="n">
         <v>1.01</v>
@@ -22454,7 +22454,7 @@
       </c>
       <c r="BH113" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -22521,16 +22521,16 @@
         <v>1.8</v>
       </c>
       <c r="R114" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S114" t="n">
         <v>3</v>
       </c>
       <c r="T114" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="U114" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="V114" t="n">
         <v>1.12</v>
@@ -22548,7 +22548,7 @@
         <v>75</v>
       </c>
       <c r="AA114" t="n">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="AB114" t="n">
         <v>8.6</v>
@@ -22560,7 +22560,7 @@
         <v>32</v>
       </c>
       <c r="AE114" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AF114" t="n">
         <v>9.199999999999999</v>
@@ -22572,7 +22572,7 @@
         <v>26</v>
       </c>
       <c r="AI114" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AJ114" t="n">
         <v>14</v>
@@ -22584,13 +22584,13 @@
         <v>40</v>
       </c>
       <c r="AM114" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AN114" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AO114" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="AP114" t="n">
         <v>14.5</v>
@@ -22599,10 +22599,10 @@
         <v>21</v>
       </c>
       <c r="AR114" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS114" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AT114" t="n">
         <v>7</v>
@@ -22614,7 +22614,7 @@
         <v>21</v>
       </c>
       <c r="AW114" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX114" t="n">
         <v>7.4</v>
@@ -22623,10 +22623,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ114" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BA114" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BB114" t="n">
         <v>11</v>
@@ -22635,20 +22635,20 @@
         <v>13.5</v>
       </c>
       <c r="BD114" t="n">
-        <v>30</v>
+        <v>7.6</v>
       </c>
       <c r="BE114" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF114" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BG114" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH114" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -22787,52 +22787,52 @@
         <v>1000</v>
       </c>
       <c r="AP115" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AQ115" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AR115" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AS115" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AT115" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU115" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV115" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AW115" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX115" t="n">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="AY115" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ115" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA115" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BB115" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BC115" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BD115" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BE115" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BF115" t="n">
         <v>1.01</v>
@@ -22842,7 +22842,7 @@
       </c>
       <c r="BH115" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -22876,7 +22876,7 @@
         <v>1.78</v>
       </c>
       <c r="G116" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="H116" t="n">
         <v>5.9</v>
@@ -22885,7 +22885,7 @@
         <v>6.6</v>
       </c>
       <c r="J116" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="K116" t="n">
         <v>3.6</v>
@@ -22903,10 +22903,10 @@
         <v>1.58</v>
       </c>
       <c r="P116" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="Q116" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="R116" t="n">
         <v>1.18</v>
@@ -22915,19 +22915,19 @@
         <v>5.1</v>
       </c>
       <c r="T116" t="n">
-        <v>2.18</v>
+        <v>2.34</v>
       </c>
       <c r="U116" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="V116" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W116" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="X116" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y116" t="n">
         <v>14.5</v>
@@ -22936,7 +22936,7 @@
         <v>55</v>
       </c>
       <c r="AA116" t="n">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="AB116" t="n">
         <v>5.9</v>
@@ -22957,10 +22957,10 @@
         <v>11.5</v>
       </c>
       <c r="AH116" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AI116" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AJ116" t="n">
         <v>21</v>
@@ -22969,16 +22969,16 @@
         <v>27</v>
       </c>
       <c r="AL116" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AM116" t="n">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="AN116" t="n">
         <v>22</v>
       </c>
       <c r="AO116" t="n">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="AP116" t="n">
         <v>7.6</v>
@@ -22987,10 +22987,10 @@
         <v>12.5</v>
       </c>
       <c r="AR116" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AS116" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AT116" t="n">
         <v>5.3</v>
@@ -22999,10 +22999,10 @@
         <v>7.2</v>
       </c>
       <c r="AV116" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AW116" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AX116" t="n">
         <v>8.199999999999999</v>
@@ -23011,32 +23011,32 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ116" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BA116" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BB116" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC116" t="n">
         <v>8</v>
       </c>
-      <c r="BC116" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BD116" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BE116" t="n">
         <v>11</v>
-      </c>
-      <c r="BE116" t="n">
-        <v>12.5</v>
       </c>
       <c r="BF116" t="n">
         <v>16.5</v>
       </c>
       <c r="BG116" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BH116" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -23070,7 +23070,7 @@
         <v>1.52</v>
       </c>
       <c r="G117" t="n">
-        <v>970</v>
+        <v>1.97</v>
       </c>
       <c r="H117" t="n">
         <v>5.7</v>
@@ -23079,7 +23079,7 @@
         <v>7.8</v>
       </c>
       <c r="J117" t="n">
-        <v>2.64</v>
+        <v>2.76</v>
       </c>
       <c r="K117" t="n">
         <v>110</v>
@@ -23230,7 +23230,7 @@
       </c>
       <c r="BH117" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -23276,7 +23276,7 @@
         <v>3.7</v>
       </c>
       <c r="K118" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L118" t="n">
         <v>1.01</v>
@@ -23294,13 +23294,13 @@
         <v>2.1</v>
       </c>
       <c r="Q118" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="R118" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S118" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="T118" t="n">
         <v>1.71</v>
@@ -23363,13 +23363,13 @@
         <v>85</v>
       </c>
       <c r="AN118" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AO118" t="n">
         <v>12.5</v>
       </c>
       <c r="AP118" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AQ118" t="n">
         <v>9.4</v>
@@ -23378,7 +23378,7 @@
         <v>11.5</v>
       </c>
       <c r="AS118" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT118" t="n">
         <v>14.5</v>
@@ -23393,7 +23393,7 @@
         <v>7.6</v>
       </c>
       <c r="AX118" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AY118" t="n">
         <v>14.5</v>
@@ -23402,7 +23402,7 @@
         <v>15</v>
       </c>
       <c r="BA118" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BB118" t="n">
         <v>10.5</v>
@@ -23411,7 +23411,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BD118" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BE118" t="n">
         <v>10.5</v>
@@ -23424,7 +23424,7 @@
       </c>
       <c r="BH118" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -23461,16 +23461,16 @@
         <v>2.96</v>
       </c>
       <c r="H119" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="I119" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J119" t="n">
         <v>2.22</v>
       </c>
       <c r="K119" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L119" t="n">
         <v>1.32</v>
@@ -23527,7 +23527,7 @@
         <v>12.5</v>
       </c>
       <c r="AD119" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE119" t="n">
         <v>46</v>
@@ -23563,62 +23563,62 @@
         <v>1000</v>
       </c>
       <c r="AP119" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AQ119" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AT119" t="n">
         <v>2.12</v>
       </c>
-      <c r="AR119" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AS119" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AT119" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AU119" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AV119" t="n">
         <v>2.12</v>
       </c>
       <c r="AW119" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BC119" t="n">
         <v>2.26</v>
       </c>
-      <c r="AX119" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AY119" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AZ119" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BA119" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BB119" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BC119" t="n">
-        <v>2.24</v>
-      </c>
       <c r="BD119" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="BE119" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="BF119" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="BG119" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="BH119" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -23649,7 +23649,7 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="G120" t="n">
         <v>3.2</v>
@@ -23658,13 +23658,13 @@
         <v>2.94</v>
       </c>
       <c r="I120" t="n">
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
       <c r="J120" t="n">
         <v>2.66</v>
       </c>
       <c r="K120" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="L120" t="n">
         <v>1.01</v>
@@ -23700,7 +23700,7 @@
         <v>1.45</v>
       </c>
       <c r="W120" t="n">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="X120" t="n">
         <v>1000</v>
@@ -23757,52 +23757,52 @@
         <v>1000</v>
       </c>
       <c r="AP120" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AQ120" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AR120" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AS120" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="AT120" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AU120" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV120" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AW120" t="n">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="AX120" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY120" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ120" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA120" t="n">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BB120" t="n">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="BC120" t="n">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="BD120" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BE120" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BF120" t="n">
         <v>1.01</v>
@@ -23812,7 +23812,7 @@
       </c>
       <c r="BH120" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -23873,10 +23873,10 @@
         <v>1.46</v>
       </c>
       <c r="P121" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="Q121" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="R121" t="n">
         <v>1.23</v>
@@ -23885,16 +23885,16 @@
         <v>4.5</v>
       </c>
       <c r="T121" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="U121" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="V121" t="n">
         <v>1.72</v>
       </c>
       <c r="W121" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="X121" t="n">
         <v>10.5</v>
@@ -23939,13 +23939,13 @@
         <v>60</v>
       </c>
       <c r="AL121" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AM121" t="n">
         <v>180</v>
       </c>
       <c r="AN121" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AO121" t="n">
         <v>29</v>
@@ -23960,7 +23960,7 @@
         <v>12</v>
       </c>
       <c r="AS121" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AT121" t="n">
         <v>10</v>
@@ -23972,7 +23972,7 @@
         <v>10</v>
       </c>
       <c r="AW121" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX121" t="n">
         <v>17.5</v>
@@ -23981,13 +23981,13 @@
         <v>14</v>
       </c>
       <c r="AZ121" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BA121" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BB121" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BC121" t="n">
         <v>10</v>
@@ -23996,7 +23996,7 @@
         <v>10.5</v>
       </c>
       <c r="BE121" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BF121" t="n">
         <v>10.5</v>
@@ -24006,7 +24006,7 @@
       </c>
       <c r="BH121" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -24043,7 +24043,7 @@
         <v>3.7</v>
       </c>
       <c r="H122" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="I122" t="n">
         <v>2.34</v>
@@ -24055,7 +24055,7 @@
         <v>3.7</v>
       </c>
       <c r="L122" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="M122" t="n">
         <v>1.07</v>
@@ -24073,7 +24073,7 @@
         <v>1.95</v>
       </c>
       <c r="R122" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S122" t="n">
         <v>3.35</v>
@@ -24200,7 +24200,7 @@
       </c>
       <c r="BH122" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="BH123" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -24431,7 +24431,7 @@
         <v>2.64</v>
       </c>
       <c r="H124" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="I124" t="n">
         <v>3.55</v>
@@ -24440,7 +24440,7 @@
         <v>2.98</v>
       </c>
       <c r="K124" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="L124" t="n">
         <v>1.01</v>
@@ -24449,16 +24449,16 @@
         <v>1.13</v>
       </c>
       <c r="N124" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="O124" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="P124" t="n">
         <v>1.51</v>
       </c>
       <c r="Q124" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="R124" t="n">
         <v>1.18</v>
@@ -24494,13 +24494,13 @@
         <v>7.8</v>
       </c>
       <c r="AC124" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD124" t="n">
         <v>15.5</v>
       </c>
       <c r="AE124" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF124" t="n">
         <v>15</v>
@@ -24521,7 +24521,7 @@
         <v>40</v>
       </c>
       <c r="AL124" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AM124" t="n">
         <v>200</v>
@@ -24530,7 +24530,7 @@
         <v>44</v>
       </c>
       <c r="AO124" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AP124" t="n">
         <v>7.4</v>
@@ -24542,7 +24542,7 @@
         <v>19</v>
       </c>
       <c r="AS124" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AT124" t="n">
         <v>7</v>
@@ -24551,7 +24551,7 @@
         <v>6.4</v>
       </c>
       <c r="AV124" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AW124" t="n">
         <v>48</v>
@@ -24563,7 +24563,7 @@
         <v>11.5</v>
       </c>
       <c r="AZ124" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA124" t="n">
         <v>70</v>
@@ -24578,17 +24578,17 @@
         <v>60</v>
       </c>
       <c r="BE124" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="BF124" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BG124" t="n">
         <v>60</v>
       </c>
       <c r="BH124" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -24782,7 +24782,7 @@
       </c>
       <c r="BH125" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -24976,7 +24976,7 @@
       </c>
       <c r="BH126" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-22.xlsx
@@ -757,16 +757,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="H2" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="I2" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="J2" t="n">
         <v>3.6</v>
@@ -784,7 +784,7 @@
         <v>4</v>
       </c>
       <c r="O2" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P2" t="n">
         <v>2</v>
@@ -793,34 +793,34 @@
         <v>1.95</v>
       </c>
       <c r="R2" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S2" t="n">
         <v>3.45</v>
       </c>
       <c r="T2" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="U2" t="n">
         <v>2.22</v>
       </c>
       <c r="V2" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="W2" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="X2" t="n">
         <v>16</v>
       </c>
       <c r="Y2" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AA2" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AB2" t="n">
         <v>13.5</v>
@@ -874,7 +874,7 @@
         <v>14.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AT2" t="n">
         <v>10.5</v>
@@ -910,7 +910,7 @@
         <v>34</v>
       </c>
       <c r="BE2" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BF2" t="n">
         <v>21</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -951,16 +951,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="G3" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="H3" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="I3" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="J3" t="n">
         <v>4.2</v>
@@ -969,7 +969,7 @@
         <v>4.4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="M3" t="n">
         <v>1.02</v>
@@ -978,31 +978,31 @@
         <v>8.4</v>
       </c>
       <c r="O3" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="P3" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="R3" t="n">
         <v>2.06</v>
       </c>
       <c r="S3" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="T3" t="n">
         <v>1.38</v>
       </c>
       <c r="U3" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="V3" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W3" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="X3" t="n">
         <v>40</v>
@@ -1035,7 +1035,7 @@
         <v>13</v>
       </c>
       <c r="AH3" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AI3" t="n">
         <v>27</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
         <v>2.38</v>
       </c>
       <c r="J4" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K4" t="n">
         <v>13.5</v>
@@ -1187,7 +1187,7 @@
         <v>2.08</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="U4" t="n">
         <v>1.01</v>
@@ -1253,52 +1253,52 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF4" t="n">
         <v>1.01</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -1375,16 +1375,16 @@
         <v>1.38</v>
       </c>
       <c r="R5" t="n">
-        <v>1.84</v>
+        <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>2.02</v>
+        <v>1.93</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
       </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="V5" t="n">
         <v>2.08</v>
@@ -1447,52 +1447,52 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF5" t="n">
         <v>1.01</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
         <v>3.65</v>
       </c>
       <c r="K6" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
@@ -1566,19 +1566,19 @@
         <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R6" t="n">
         <v>1.39</v>
       </c>
       <c r="S6" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="T6" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="U6" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V6" t="n">
         <v>1.96</v>
@@ -1608,7 +1608,7 @@
         <v>11</v>
       </c>
       <c r="AE6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF6" t="n">
         <v>32</v>
@@ -1626,7 +1626,7 @@
         <v>100</v>
       </c>
       <c r="AK6" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AL6" t="n">
         <v>1000</v>
@@ -1635,7 +1635,7 @@
         <v>120</v>
       </c>
       <c r="AN6" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
         <v>14</v>
@@ -1674,19 +1674,19 @@
         <v>16</v>
       </c>
       <c r="BA6" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC6" t="n">
         <v>42</v>
       </c>
       <c r="BD6" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BE6" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BF6" t="n">
         <v>42</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -1835,52 +1835,52 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF7" t="n">
         <v>1.01</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1921,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="G8" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="H8" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="I8" t="n">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="J8" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="K8" t="n">
-        <v>4.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
@@ -1951,10 +1951,10 @@
         <v>1.22</v>
       </c>
       <c r="P8" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="R8" t="n">
         <v>1.45</v>
@@ -1969,10 +1969,10 @@
         <v>2.24</v>
       </c>
       <c r="V8" t="n">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="W8" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2029,52 +2029,52 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF8" t="n">
         <v>1.01</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -2124,13 +2124,13 @@
         <v>3.3</v>
       </c>
       <c r="I9" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="J9" t="n">
         <v>3.25</v>
       </c>
       <c r="K9" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
@@ -2163,7 +2163,7 @@
         <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W9" t="n">
         <v>1.68</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="G10" t="n">
         <v>1000</v>
       </c>
       <c r="H10" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="I10" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="J10" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K10" t="n">
-        <v>950</v>
+        <v>12</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2360,7 +2360,7 @@
         <v>2.66</v>
       </c>
       <c r="W10" t="n">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -2417,52 +2417,52 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF10" t="n">
         <v>1.01</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -2611,52 +2611,52 @@
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF11" t="n">
         <v>1.01</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -2700,19 +2700,19 @@
         <v>3.25</v>
       </c>
       <c r="G12" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="I12" t="n">
-        <v>2.24</v>
+        <v>2.44</v>
       </c>
       <c r="J12" t="n">
-        <v>3.95</v>
+        <v>2.84</v>
       </c>
       <c r="K12" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
@@ -2727,7 +2727,7 @@
         <v>1.12</v>
       </c>
       <c r="P12" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="Q12" t="n">
         <v>1.42</v>
@@ -2745,10 +2745,10 @@
         <v>2.48</v>
       </c>
       <c r="V12" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="W12" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -2891,19 +2891,19 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="G13" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="H13" t="n">
         <v>4.4</v>
       </c>
       <c r="I13" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J13" t="n">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="K13" t="n">
         <v>5</v>
@@ -2915,22 +2915,22 @@
         <v>1.02</v>
       </c>
       <c r="N13" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O13" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="P13" t="n">
-        <v>3.05</v>
+        <v>2.32</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="R13" t="n">
-        <v>1.84</v>
+        <v>1.74</v>
       </c>
       <c r="S13" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="T13" t="n">
         <v>1.5</v>
@@ -2942,7 +2942,7 @@
         <v>1.27</v>
       </c>
       <c r="W13" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="X13" t="n">
         <v>42</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -3088,43 +3088,43 @@
         <v>1.86</v>
       </c>
       <c r="G14" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I14" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="J14" t="n">
-        <v>3.4</v>
+        <v>2.78</v>
       </c>
       <c r="K14" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="N14" t="n">
-        <v>3.35</v>
+        <v>1.68</v>
       </c>
       <c r="O14" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="P14" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="R14" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="S14" t="n">
-        <v>3.85</v>
+        <v>3.15</v>
       </c>
       <c r="T14" t="n">
         <v>1.74</v>
@@ -3133,10 +3133,10 @@
         <v>1.97</v>
       </c>
       <c r="V14" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W14" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="X14" t="n">
         <v>12.5</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -3285,16 +3285,16 @@
         <v>5.2</v>
       </c>
       <c r="H15" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="I15" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="J15" t="n">
         <v>2.76</v>
       </c>
       <c r="K15" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="L15" t="n">
         <v>1.43</v>
@@ -3327,7 +3327,7 @@
         <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="W15" t="n">
         <v>1.24</v>
@@ -3387,52 +3387,52 @@
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF15" t="n">
         <v>1.01</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -3581,52 +3581,52 @@
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF16" t="n">
         <v>1.01</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -3667,10 +3667,10 @@
         </is>
       </c>
       <c r="F17" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="G17" t="n">
         <v>1.29</v>
-      </c>
-      <c r="G17" t="n">
-        <v>1.3</v>
       </c>
       <c r="H17" t="n">
         <v>14</v>
@@ -3679,25 +3679,25 @@
         <v>14.5</v>
       </c>
       <c r="J17" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="K17" t="n">
         <v>6.6</v>
       </c>
       <c r="L17" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="M17" t="n">
         <v>1.05</v>
       </c>
       <c r="N17" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O17" t="n">
         <v>1.26</v>
       </c>
       <c r="P17" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q17" t="n">
         <v>1.79</v>
@@ -3718,7 +3718,7 @@
         <v>1.07</v>
       </c>
       <c r="W17" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="X17" t="n">
         <v>20</v>
@@ -3766,25 +3766,25 @@
         <v>55</v>
       </c>
       <c r="AM17" t="n">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="AN17" t="n">
         <v>5.2</v>
       </c>
       <c r="AO17" t="n">
-        <v>490</v>
+        <v>480</v>
       </c>
       <c r="AP17" t="n">
         <v>18</v>
       </c>
       <c r="AQ17" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AR17" t="n">
         <v>20</v>
       </c>
       <c r="AS17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT17" t="n">
         <v>7.4</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -3969,52 +3969,52 @@
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF18" t="n">
         <v>1.01</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -4088,7 +4088,7 @@
         <v>2.02</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="R19" t="n">
         <v>1.39</v>
@@ -4109,7 +4109,7 @@
         <v>2.32</v>
       </c>
       <c r="X19" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Y19" t="n">
         <v>18.5</v>
@@ -4124,13 +4124,13 @@
         <v>8.6</v>
       </c>
       <c r="AC19" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD19" t="n">
         <v>20</v>
       </c>
       <c r="AE19" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AF19" t="n">
         <v>9.800000000000001</v>
@@ -4172,7 +4172,7 @@
         <v>38</v>
       </c>
       <c r="AS19" t="n">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="AT19" t="n">
         <v>8.199999999999999</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
         <v>1.74</v>
       </c>
       <c r="O20" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P20" t="n">
         <v>1.74</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -4452,7 +4452,7 @@
         <v>3</v>
       </c>
       <c r="I21" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="J21" t="n">
         <v>3.75</v>
@@ -4467,22 +4467,22 @@
         <v>1.05</v>
       </c>
       <c r="N21" t="n">
-        <v>4.8</v>
+        <v>2.16</v>
       </c>
       <c r="O21" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P21" t="n">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="R21" t="n">
         <v>1.53</v>
       </c>
       <c r="S21" t="n">
-        <v>2.76</v>
+        <v>2.62</v>
       </c>
       <c r="T21" t="n">
         <v>1.62</v>
@@ -4566,7 +4566,7 @@
         <v>11</v>
       </c>
       <c r="AU21" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV21" t="n">
         <v>11.5</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -4637,7 +4637,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="G22" t="n">
         <v>2.2</v>
@@ -4679,7 +4679,7 @@
         <v>2.86</v>
       </c>
       <c r="T22" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="U22" t="n">
         <v>2.4</v>
@@ -4796,11 +4796,11 @@
         <v>10</v>
       </c>
       <c r="BG22" t="n">
-        <v>25</v>
+        <v>10.5</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -4840,7 +4840,7 @@
         <v>2.48</v>
       </c>
       <c r="I23" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="J23" t="n">
         <v>3.7</v>
@@ -4855,22 +4855,22 @@
         <v>1.05</v>
       </c>
       <c r="N23" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="O23" t="n">
         <v>1.22</v>
       </c>
       <c r="P23" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="R23" t="n">
         <v>1.55</v>
       </c>
       <c r="S23" t="n">
-        <v>2.66</v>
+        <v>2.56</v>
       </c>
       <c r="T23" t="n">
         <v>1.58</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -5025,22 +5025,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="G24" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="H24" t="n">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="I24" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="J24" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="K24" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="L24" t="n">
         <v>1.27</v>
@@ -5049,16 +5049,16 @@
         <v>1.04</v>
       </c>
       <c r="N24" t="n">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="O24" t="n">
         <v>1.22</v>
       </c>
       <c r="P24" t="n">
-        <v>1.34</v>
+        <v>1.92</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.22</v>
+        <v>1.62</v>
       </c>
       <c r="R24" t="n">
         <v>1.34</v>
@@ -5067,128 +5067,128 @@
         <v>2.52</v>
       </c>
       <c r="T24" t="n">
-        <v>2.62</v>
+        <v>1.01</v>
       </c>
       <c r="U24" t="n">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="V24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W24" t="n">
-        <v>4.5</v>
+        <v>3.65</v>
       </c>
       <c r="X24" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="Y24" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="Z24" t="n">
-        <v>280</v>
+        <v>1000</v>
       </c>
       <c r="AA24" t="n">
         <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AC24" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AD24" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AE24" t="n">
         <v>1000</v>
       </c>
       <c r="AF24" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AG24" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AH24" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AI24" t="n">
         <v>1000</v>
       </c>
       <c r="AJ24" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AK24" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AL24" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM24" t="n">
         <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="AO24" t="n">
         <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>4.5</v>
+        <v>16</v>
       </c>
       <c r="AQ24" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="AR24" t="n">
+        <v>40</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>40</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>38</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>40</v>
+      </c>
+      <c r="AX24" t="n">
         <v>5.5</v>
       </c>
-      <c r="AS24" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>5.7</v>
-      </c>
       <c r="AY24" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AZ24" t="n">
-        <v>5.1</v>
+        <v>28</v>
       </c>
       <c r="BA24" t="n">
-        <v>5.5</v>
+        <v>40</v>
       </c>
       <c r="BB24" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BC24" t="n">
-        <v>4.3</v>
+        <v>11.5</v>
       </c>
       <c r="BD24" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BE24" t="n">
-        <v>5.5</v>
+        <v>40</v>
       </c>
       <c r="BF24" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BG24" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
         <v>2.1</v>
       </c>
       <c r="X25" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Y25" t="n">
         <v>22</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="G26" t="n">
         <v>2.06</v>
@@ -5461,7 +5461,7 @@
         <v>2.38</v>
       </c>
       <c r="V26" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W26" t="n">
         <v>1.94</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -5801,22 +5801,22 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="G28" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="H28" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="I28" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="J28" t="n">
         <v>3.8</v>
       </c>
       <c r="K28" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L28" t="n">
         <v>1.01</v>
@@ -5825,34 +5825,34 @@
         <v>1.04</v>
       </c>
       <c r="N28" t="n">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="O28" t="n">
         <v>1.2</v>
       </c>
       <c r="P28" t="n">
-        <v>2.24</v>
+        <v>2.42</v>
       </c>
       <c r="Q28" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="R28" t="n">
         <v>1.52</v>
       </c>
-      <c r="R28" t="n">
-        <v>1.51</v>
-      </c>
       <c r="S28" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="T28" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="U28" t="n">
         <v>2.38</v>
       </c>
       <c r="V28" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W28" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="X28" t="n">
         <v>1000</v>
@@ -5876,7 +5876,7 @@
         <v>19</v>
       </c>
       <c r="AE28" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AF28" t="n">
         <v>23</v>
@@ -5909,7 +5909,7 @@
         <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="AQ28" t="n">
         <v>2.48</v>
@@ -5918,19 +5918,19 @@
         <v>2.56</v>
       </c>
       <c r="AS28" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="AT28" t="n">
         <v>10</v>
       </c>
       <c r="AU28" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="AV28" t="n">
         <v>10</v>
       </c>
       <c r="AW28" t="n">
-        <v>2.6</v>
+        <v>21</v>
       </c>
       <c r="AX28" t="n">
         <v>12.5</v>
@@ -5945,7 +5945,7 @@
         <v>2.62</v>
       </c>
       <c r="BB28" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="BC28" t="n">
         <v>14.5</v>
@@ -5960,11 +5960,11 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BG28" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -6007,7 +6007,7 @@
         <v>5.6</v>
       </c>
       <c r="J29" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="K29" t="n">
         <v>4.8</v>
@@ -6022,7 +6022,7 @@
         <v>1.4</v>
       </c>
       <c r="O29" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P29" t="n">
         <v>1.4</v>
@@ -6046,7 +6046,7 @@
         <v>1.21</v>
       </c>
       <c r="W29" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="X29" t="n">
         <v>1000</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -6965,7 +6965,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="G34" t="n">
         <v>1.79</v>
@@ -7046,7 +7046,7 @@
         <v>12.5</v>
       </c>
       <c r="AG34" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH34" t="n">
         <v>17.5</v>
@@ -7064,25 +7064,25 @@
         <v>29</v>
       </c>
       <c r="AM34" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AN34" t="n">
         <v>9</v>
       </c>
       <c r="AO34" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP34" t="n">
-        <v>7.8</v>
+        <v>17</v>
       </c>
       <c r="AQ34" t="n">
         <v>19.5</v>
       </c>
       <c r="AR34" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AS34" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AT34" t="n">
         <v>9.4</v>
@@ -7094,7 +7094,7 @@
         <v>18</v>
       </c>
       <c r="AW34" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AX34" t="n">
         <v>10.5</v>
@@ -7106,7 +7106,7 @@
         <v>15.5</v>
       </c>
       <c r="BA34" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BB34" t="n">
         <v>16.5</v>
@@ -7118,17 +7118,17 @@
         <v>25</v>
       </c>
       <c r="BE34" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BF34" t="n">
         <v>8</v>
       </c>
       <c r="BG34" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -7159,7 +7159,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="G35" t="n">
         <v>2.12</v>
@@ -7168,7 +7168,7 @@
         <v>3.35</v>
       </c>
       <c r="I35" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J35" t="n">
         <v>4.2</v>
@@ -7189,22 +7189,22 @@
         <v>1.18</v>
       </c>
       <c r="P35" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="Q35" t="n">
         <v>1.56</v>
       </c>
       <c r="R35" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="S35" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="T35" t="n">
         <v>1.54</v>
       </c>
       <c r="U35" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="V35" t="n">
         <v>1.4</v>
@@ -7219,7 +7219,7 @@
         <v>21</v>
       </c>
       <c r="Z35" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA35" t="n">
         <v>70</v>
@@ -7249,7 +7249,7 @@
         <v>36</v>
       </c>
       <c r="AJ35" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AK35" t="n">
         <v>19.5</v>
@@ -7261,10 +7261,10 @@
         <v>55</v>
       </c>
       <c r="AN35" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO35" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AP35" t="n">
         <v>22</v>
@@ -7276,7 +7276,7 @@
         <v>25</v>
       </c>
       <c r="AS35" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AT35" t="n">
         <v>13.5</v>
@@ -7312,7 +7312,7 @@
         <v>23</v>
       </c>
       <c r="BE35" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BF35" t="n">
         <v>8.6</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -7371,7 +7371,7 @@
         <v>3.55</v>
       </c>
       <c r="L36" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="M36" t="n">
         <v>1.09</v>
@@ -7383,10 +7383,10 @@
         <v>1.38</v>
       </c>
       <c r="P36" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R36" t="n">
         <v>1.27</v>
@@ -7401,7 +7401,7 @@
         <v>1.98</v>
       </c>
       <c r="V36" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="W36" t="n">
         <v>1.39</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -7753,7 +7753,7 @@
         <v>1000</v>
       </c>
       <c r="J38" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K38" t="n">
         <v>1000</v>
@@ -7768,19 +7768,19 @@
         <v>1.03</v>
       </c>
       <c r="O38" t="n">
-        <v>1.02</v>
+        <v>1.43</v>
       </c>
       <c r="P38" t="n">
         <v>1.08</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="R38" t="n">
         <v>1.08</v>
       </c>
       <c r="S38" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T38" t="n">
         <v>1.01</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -8165,13 +8165,13 @@
         <v>1.78</v>
       </c>
       <c r="R40" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S40" t="n">
         <v>2.92</v>
       </c>
       <c r="T40" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="U40" t="n">
         <v>2.46</v>
@@ -8243,7 +8243,7 @@
         <v>12</v>
       </c>
       <c r="AR40" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AS40" t="n">
         <v>30</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -8332,7 +8332,7 @@
         <v>9.4</v>
       </c>
       <c r="I41" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="J41" t="n">
         <v>5</v>
@@ -8440,7 +8440,7 @@
         <v>75</v>
       </c>
       <c r="AS41" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AT41" t="n">
         <v>7</v>
@@ -8458,16 +8458,16 @@
         <v>7.4</v>
       </c>
       <c r="AY41" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ41" t="n">
         <v>26</v>
       </c>
       <c r="BA41" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BB41" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BC41" t="n">
         <v>14.5</v>
@@ -8476,17 +8476,17 @@
         <v>38</v>
       </c>
       <c r="BE41" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BF41" t="n">
         <v>6.6</v>
       </c>
       <c r="BG41" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -8523,7 +8523,7 @@
         <v>2.46</v>
       </c>
       <c r="H42" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I42" t="n">
         <v>3.65</v>
@@ -8535,7 +8535,7 @@
         <v>3.2</v>
       </c>
       <c r="L42" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="M42" t="n">
         <v>1.11</v>
@@ -8550,7 +8550,7 @@
         <v>1.7</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R42" t="n">
         <v>1.25</v>
@@ -8559,7 +8559,7 @@
         <v>4.6</v>
       </c>
       <c r="T42" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="U42" t="n">
         <v>1.96</v>
@@ -8571,7 +8571,7 @@
         <v>1.68</v>
       </c>
       <c r="X42" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="Y42" t="n">
         <v>11.5</v>
@@ -8583,7 +8583,7 @@
         <v>70</v>
       </c>
       <c r="AB42" t="n">
-        <v>8.6</v>
+        <v>14</v>
       </c>
       <c r="AC42" t="n">
         <v>7</v>
@@ -8601,13 +8601,13 @@
         <v>12</v>
       </c>
       <c r="AH42" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI42" t="n">
         <v>75</v>
       </c>
       <c r="AJ42" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK42" t="n">
         <v>32</v>
@@ -8625,13 +8625,13 @@
         <v>65</v>
       </c>
       <c r="AP42" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ42" t="n">
         <v>10.5</v>
       </c>
       <c r="AR42" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AS42" t="n">
         <v>32</v>
@@ -8646,41 +8646,41 @@
         <v>14</v>
       </c>
       <c r="AW42" t="n">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="AX42" t="n">
         <v>12.5</v>
       </c>
       <c r="AY42" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ42" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BA42" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BB42" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD42" t="n">
+        <v>29</v>
+      </c>
+      <c r="BE42" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BF42" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BG42" t="n">
         <v>30</v>
       </c>
-      <c r="BC42" t="n">
-        <v>26</v>
-      </c>
-      <c r="BD42" t="n">
-        <v>48</v>
-      </c>
-      <c r="BE42" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BF42" t="n">
-        <v>25</v>
-      </c>
-      <c r="BG42" t="n">
-        <v>50</v>
-      </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="G43" t="n">
         <v>3.2</v>
@@ -8723,40 +8723,40 @@
         <v>2.66</v>
       </c>
       <c r="J43" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="K43" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L43" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="M43" t="n">
         <v>1.07</v>
       </c>
       <c r="N43" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="O43" t="n">
         <v>1.31</v>
       </c>
       <c r="P43" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.96</v>
+        <v>1.81</v>
       </c>
       <c r="R43" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S43" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="T43" t="n">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="U43" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="V43" t="n">
         <v>1.6</v>
@@ -8780,7 +8780,7 @@
         <v>14.5</v>
       </c>
       <c r="AC43" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD43" t="n">
         <v>12.5</v>
@@ -8822,13 +8822,13 @@
         <v>12.5</v>
       </c>
       <c r="AQ43" t="n">
-        <v>5.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR43" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="AS43" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="AT43" t="n">
         <v>10.5</v>
@@ -8837,44 +8837,44 @@
         <v>7</v>
       </c>
       <c r="AV43" t="n">
-        <v>5.3</v>
+        <v>10.5</v>
       </c>
       <c r="AW43" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BB43" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC43" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BD43" t="n">
         <v>7</v>
       </c>
-      <c r="AX43" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AY43" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AZ43" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA43" t="n">
+      <c r="BE43" t="n">
         <v>7.4</v>
       </c>
-      <c r="BB43" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BC43" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BD43" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BE43" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BF43" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BG43" t="n">
         <v>17</v>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -8905,22 +8905,22 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="G44" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="H44" t="n">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="I44" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="J44" t="n">
-        <v>2.96</v>
+        <v>2.7</v>
       </c>
       <c r="K44" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L44" t="n">
         <v>1.01</v>
@@ -8929,34 +8929,34 @@
         <v>1.09</v>
       </c>
       <c r="N44" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="O44" t="n">
         <v>1.36</v>
       </c>
       <c r="P44" t="n">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="R44" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="S44" t="n">
-        <v>3.85</v>
+        <v>3.35</v>
       </c>
       <c r="T44" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="U44" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="V44" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="W44" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="X44" t="n">
         <v>12</v>
@@ -8974,7 +8974,7 @@
         <v>12.5</v>
       </c>
       <c r="AC44" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AD44" t="n">
         <v>13</v>
@@ -9016,7 +9016,7 @@
         <v>10</v>
       </c>
       <c r="AQ44" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR44" t="n">
         <v>16</v>
@@ -9025,7 +9025,7 @@
         <v>8.4</v>
       </c>
       <c r="AT44" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AU44" t="n">
         <v>6</v>
@@ -9034,10 +9034,10 @@
         <v>11</v>
       </c>
       <c r="AW44" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="AX44" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AY44" t="n">
         <v>11.5</v>
@@ -9046,29 +9046,29 @@
         <v>14</v>
       </c>
       <c r="BA44" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BB44" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC44" t="n">
-        <v>8.4</v>
+        <v>26</v>
       </c>
       <c r="BD44" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE44" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF44" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG44" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -9201,7 +9201,7 @@
         <v>85</v>
       </c>
       <c r="AN45" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO45" t="n">
         <v>40</v>
@@ -9213,10 +9213,10 @@
         <v>13.5</v>
       </c>
       <c r="AR45" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AS45" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT45" t="n">
         <v>9.4</v>
@@ -9228,7 +9228,7 @@
         <v>13.5</v>
       </c>
       <c r="AW45" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="AX45" t="n">
         <v>12.5</v>
@@ -9240,29 +9240,29 @@
         <v>14.5</v>
       </c>
       <c r="BA45" t="n">
-        <v>9.199999999999999</v>
+        <v>40</v>
       </c>
       <c r="BB45" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC45" t="n">
         <v>18.5</v>
       </c>
       <c r="BD45" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BE45" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF45" t="n">
         <v>12.5</v>
       </c>
       <c r="BG45" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -9293,64 +9293,64 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2.28</v>
+        <v>2.48</v>
       </c>
       <c r="G46" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="H46" t="n">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="I46" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="J46" t="n">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="K46" t="n">
-        <v>5.1</v>
+        <v>3.45</v>
       </c>
       <c r="L46" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="M46" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N46" t="n">
-        <v>1.53</v>
+        <v>2.9</v>
       </c>
       <c r="O46" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="P46" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="R46" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="S46" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="T46" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="U46" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="V46" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="W46" t="n">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="X46" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y46" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z46" t="n">
         <v>1000</v>
@@ -9359,22 +9359,22 @@
         <v>1000</v>
       </c>
       <c r="AB46" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC46" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD46" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AE46" t="n">
         <v>1000</v>
       </c>
       <c r="AF46" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AG46" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH46" t="n">
         <v>1000</v>
@@ -9401,62 +9401,62 @@
         <v>1000</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AR46" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AS46" t="n">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="AT46" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AU46" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AV46" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AW46" t="n">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="AX46" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AY46" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AZ46" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BA46" t="n">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="BB46" t="n">
-        <v>1.01</v>
+        <v>29</v>
       </c>
       <c r="BC46" t="n">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BD46" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BE46" t="n">
-        <v>1.01</v>
+        <v>90</v>
       </c>
       <c r="BF46" t="n">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BG46" t="n">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -9505,7 +9505,7 @@
         <v>3.55</v>
       </c>
       <c r="L47" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M47" t="n">
         <v>1.07</v>
@@ -9595,7 +9595,7 @@
         <v>34</v>
       </c>
       <c r="AP47" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AQ47" t="n">
         <v>12.5</v>
@@ -9646,11 +9646,11 @@
         <v>16.5</v>
       </c>
       <c r="BG47" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -9681,10 +9681,10 @@
         </is>
       </c>
       <c r="F48" t="n">
+        <v>2</v>
+      </c>
+      <c r="G48" t="n">
         <v>2.02</v>
-      </c>
-      <c r="G48" t="n">
-        <v>2.04</v>
       </c>
       <c r="H48" t="n">
         <v>4</v>
@@ -9732,10 +9732,10 @@
         <v>1.32</v>
       </c>
       <c r="W48" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="X48" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Y48" t="n">
         <v>16.5</v>
@@ -9783,13 +9783,13 @@
         <v>85</v>
       </c>
       <c r="AN48" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AO48" t="n">
         <v>42</v>
       </c>
       <c r="AP48" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AQ48" t="n">
         <v>15.5</v>
@@ -9816,7 +9816,7 @@
         <v>12</v>
       </c>
       <c r="AY48" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ48" t="n">
         <v>16.5</v>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -9875,7 +9875,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G49" t="n">
         <v>2.26</v>
@@ -9884,13 +9884,13 @@
         <v>3.45</v>
       </c>
       <c r="I49" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J49" t="n">
         <v>3.7</v>
       </c>
       <c r="K49" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L49" t="n">
         <v>1.36</v>
@@ -9920,7 +9920,7 @@
         <v>1.68</v>
       </c>
       <c r="U49" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V49" t="n">
         <v>1.4</v>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -10072,67 +10072,67 @@
         <v>1.75</v>
       </c>
       <c r="G50" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="H50" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="I50" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J50" t="n">
-        <v>3.55</v>
+        <v>3</v>
       </c>
       <c r="K50" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="L50" t="n">
         <v>1.35</v>
       </c>
       <c r="M50" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="N50" t="n">
-        <v>3.3</v>
+        <v>1.65</v>
       </c>
       <c r="O50" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="P50" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.94</v>
+        <v>1.33</v>
       </c>
       <c r="R50" t="n">
-        <v>1.29</v>
+        <v>1.09</v>
       </c>
       <c r="S50" t="n">
-        <v>3.7</v>
+        <v>1.33</v>
       </c>
       <c r="T50" t="n">
-        <v>1.93</v>
+        <v>1.01</v>
       </c>
       <c r="U50" t="n">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="V50" t="n">
         <v>1.22</v>
       </c>
       <c r="W50" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="X50" t="n">
         <v>15</v>
       </c>
       <c r="Y50" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Z50" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AA50" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AB50" t="n">
         <v>8.800000000000001</v>
@@ -10141,10 +10141,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD50" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AE50" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AF50" t="n">
         <v>12</v>
@@ -10153,10 +10153,10 @@
         <v>12</v>
       </c>
       <c r="AH50" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI50" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AJ50" t="n">
         <v>22</v>
@@ -10168,19 +10168,19 @@
         <v>48</v>
       </c>
       <c r="AM50" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AN50" t="n">
         <v>15.5</v>
       </c>
       <c r="AO50" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AP50" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ50" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AR50" t="n">
         <v>32</v>
@@ -10189,7 +10189,7 @@
         <v>110</v>
       </c>
       <c r="AT50" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AU50" t="n">
         <v>6.6</v>
@@ -10201,10 +10201,10 @@
         <v>60</v>
       </c>
       <c r="AX50" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY50" t="n">
         <v>8</v>
-      </c>
-      <c r="AY50" t="n">
-        <v>7.8</v>
       </c>
       <c r="AZ50" t="n">
         <v>16.5</v>
@@ -10225,14 +10225,14 @@
         <v>100</v>
       </c>
       <c r="BF50" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BG50" t="n">
         <v>85</v>
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -10281,7 +10281,7 @@
         <v>4.1</v>
       </c>
       <c r="L51" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="M51" t="n">
         <v>1.07</v>
@@ -10317,116 +10317,116 @@
         <v>2</v>
       </c>
       <c r="X51" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Y51" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Z51" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AA51" t="n">
         <v>1000</v>
       </c>
       <c r="AB51" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC51" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD51" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE51" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF51" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG51" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH51" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI51" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ51" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AK51" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL51" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM51" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN51" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AO51" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AR51" t="n">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="AS51" t="n">
-        <v>1.01</v>
+        <v>75</v>
       </c>
       <c r="AT51" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AU51" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV51" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AW51" t="n">
-        <v>1.01</v>
+        <v>44</v>
       </c>
       <c r="AX51" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AY51" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AZ51" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BA51" t="n">
-        <v>1.01</v>
+        <v>46</v>
       </c>
       <c r="BB51" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BC51" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BD51" t="n">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="BE51" t="n">
-        <v>1.01</v>
+        <v>75</v>
       </c>
       <c r="BF51" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BG51" t="n">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -10460,13 +10460,13 @@
         <v>1.41</v>
       </c>
       <c r="G52" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="H52" t="n">
         <v>7.2</v>
       </c>
       <c r="I52" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J52" t="n">
         <v>5.4</v>
@@ -10481,22 +10481,22 @@
         <v>1.02</v>
       </c>
       <c r="N52" t="n">
-        <v>6.6</v>
+        <v>1.05</v>
       </c>
       <c r="O52" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="P52" t="n">
-        <v>2.96</v>
+        <v>1.67</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.45</v>
+        <v>1.12</v>
       </c>
       <c r="R52" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="S52" t="n">
-        <v>2.08</v>
+        <v>1.42</v>
       </c>
       <c r="T52" t="n">
         <v>1.58</v>
@@ -10505,7 +10505,7 @@
         <v>2.22</v>
       </c>
       <c r="V52" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W52" t="n">
         <v>3.15</v>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -10651,22 +10651,22 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>2.58</v>
+        <v>1.61</v>
       </c>
       <c r="G53" t="n">
-        <v>2.78</v>
+        <v>1000</v>
       </c>
       <c r="H53" t="n">
-        <v>3.8</v>
+        <v>1.61</v>
       </c>
       <c r="I53" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="J53" t="n">
-        <v>2.52</v>
+        <v>1.03</v>
       </c>
       <c r="K53" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="L53" t="n">
         <v>1.01</v>
@@ -10684,7 +10684,7 @@
         <v>1.25</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="R53" t="n">
         <v>1.08</v>
@@ -10699,10 +10699,10 @@
         <v>1.01</v>
       </c>
       <c r="V53" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="W53" t="n">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="X53" t="n">
         <v>7</v>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -11039,7 +11039,7 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="G55" t="n">
         <v>2.6</v>
@@ -11048,13 +11048,13 @@
         <v>3.1</v>
       </c>
       <c r="I55" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="J55" t="n">
         <v>3.15</v>
       </c>
       <c r="K55" t="n">
-        <v>410</v>
+        <v>5.2</v>
       </c>
       <c r="L55" t="n">
         <v>1.29</v>
@@ -11066,7 +11066,7 @@
         <v>1.87</v>
       </c>
       <c r="O55" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P55" t="n">
         <v>1.87</v>
@@ -11075,19 +11075,19 @@
         <v>1.74</v>
       </c>
       <c r="R55" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="S55" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="T55" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="U55" t="n">
         <v>1.01</v>
       </c>
       <c r="V55" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W55" t="n">
         <v>1.62</v>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -11236,7 +11236,7 @@
         <v>1.79</v>
       </c>
       <c r="G56" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="H56" t="n">
         <v>4.7</v>
@@ -11248,34 +11248,34 @@
         <v>4</v>
       </c>
       <c r="K56" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L56" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M56" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N56" t="n">
-        <v>4.5</v>
+        <v>2.12</v>
       </c>
       <c r="O56" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="P56" t="n">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="Q56" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="R56" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="S56" t="n">
-        <v>2.72</v>
+        <v>2.62</v>
       </c>
       <c r="T56" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="U56" t="n">
         <v>2.24</v>
@@ -11317,7 +11317,7 @@
         <v>11</v>
       </c>
       <c r="AH56" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AI56" t="n">
         <v>65</v>
@@ -11350,7 +11350,7 @@
         <v>30</v>
       </c>
       <c r="AS56" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AT56" t="n">
         <v>9.199999999999999</v>
@@ -11362,7 +11362,7 @@
         <v>16</v>
       </c>
       <c r="AW56" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX56" t="n">
         <v>10.5</v>
@@ -11374,7 +11374,7 @@
         <v>14.5</v>
       </c>
       <c r="BA56" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BB56" t="n">
         <v>16.5</v>
@@ -11386,17 +11386,17 @@
         <v>22</v>
       </c>
       <c r="BE56" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF56" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BG56" t="n">
         <v>6.8</v>
       </c>
-      <c r="BF56" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BG56" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -11454,7 +11454,7 @@
         <v>1.57</v>
       </c>
       <c r="O57" t="n">
-        <v>1.02</v>
+        <v>1.39</v>
       </c>
       <c r="P57" t="n">
         <v>1.57</v>
@@ -11590,7 +11590,7 @@
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -11624,19 +11624,19 @@
         <v>4.4</v>
       </c>
       <c r="G58" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="H58" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="I58" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="J58" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="K58" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="L58" t="n">
         <v>1.01</v>
@@ -11645,22 +11645,22 @@
         <v>1.02</v>
       </c>
       <c r="N58" t="n">
-        <v>6.4</v>
+        <v>2.7</v>
       </c>
       <c r="O58" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="P58" t="n">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="Q58" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="R58" t="n">
-        <v>1.85</v>
+        <v>1.38</v>
       </c>
       <c r="S58" t="n">
-        <v>1.98</v>
+        <v>1.84</v>
       </c>
       <c r="T58" t="n">
         <v>1.44</v>
@@ -11669,13 +11669,13 @@
         <v>2.7</v>
       </c>
       <c r="V58" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="W58" t="n">
         <v>1.24</v>
       </c>
       <c r="X58" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="Y58" t="n">
         <v>17</v>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -11845,13 +11845,13 @@
         <v>1.21</v>
       </c>
       <c r="P59" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="Q59" t="n">
         <v>1.58</v>
       </c>
       <c r="R59" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="S59" t="n">
         <v>2.58</v>
@@ -11978,7 +11978,7 @@
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -12015,7 +12015,7 @@
         <v>7.2</v>
       </c>
       <c r="H60" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="I60" t="n">
         <v>1.48</v>
@@ -12027,7 +12027,7 @@
         <v>6.2</v>
       </c>
       <c r="L60" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="M60" t="n">
         <v>1.02</v>
@@ -12060,7 +12060,7 @@
         <v>3.05</v>
       </c>
       <c r="W60" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X60" t="n">
         <v>48</v>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -12366,7 +12366,7 @@
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -12400,13 +12400,13 @@
         <v>2.56</v>
       </c>
       <c r="G62" t="n">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="H62" t="n">
         <v>2.86</v>
       </c>
       <c r="I62" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="J62" t="n">
         <v>2.82</v>
@@ -12418,13 +12418,13 @@
         <v>1.01</v>
       </c>
       <c r="M62" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N62" t="n">
-        <v>1.76</v>
+        <v>3.2</v>
       </c>
       <c r="O62" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="P62" t="n">
         <v>1.76</v>
@@ -12433,55 +12433,55 @@
         <v>1.94</v>
       </c>
       <c r="R62" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="S62" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="T62" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="U62" t="n">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="V62" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="W62" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="X62" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y62" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z62" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AA62" t="n">
         <v>1000</v>
       </c>
       <c r="AB62" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC62" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD62" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE62" t="n">
         <v>1000</v>
       </c>
       <c r="AF62" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG62" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH62" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI62" t="n">
         <v>1000</v>
@@ -12505,62 +12505,62 @@
         <v>1000</v>
       </c>
       <c r="AP62" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ62" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AR62" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AS62" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="AT62" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AU62" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AV62" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW62" t="n">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="AX62" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AY62" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AZ62" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BA62" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BB62" t="n">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BC62" t="n">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="BD62" t="n">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BE62" t="n">
-        <v>1.01</v>
+        <v>75</v>
       </c>
       <c r="BF62" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BG62" t="n">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -12591,49 +12591,49 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="G63" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="H63" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="I63" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J63" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K63" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="L63" t="n">
         <v>1.37</v>
       </c>
       <c r="M63" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N63" t="n">
-        <v>3.35</v>
+        <v>1.83</v>
       </c>
       <c r="O63" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="P63" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="Q63" t="n">
         <v>2.16</v>
       </c>
       <c r="R63" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="S63" t="n">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="T63" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="U63" t="n">
         <v>2.08</v>
@@ -12660,7 +12660,7 @@
         <v>9.6</v>
       </c>
       <c r="AC63" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AD63" t="n">
         <v>14</v>
@@ -12708,7 +12708,7 @@
         <v>20</v>
       </c>
       <c r="AS63" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AT63" t="n">
         <v>8.6</v>
@@ -12720,7 +12720,7 @@
         <v>12</v>
       </c>
       <c r="AW63" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AX63" t="n">
         <v>14</v>
@@ -12732,29 +12732,29 @@
         <v>15.5</v>
       </c>
       <c r="BA63" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BB63" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BC63" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="BD63" t="n">
         <v>36</v>
       </c>
       <c r="BE63" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BF63" t="n">
         <v>18.5</v>
       </c>
       <c r="BG63" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -12785,7 +12785,7 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="G64" t="n">
         <v>2.24</v>
@@ -12794,16 +12794,16 @@
         <v>3.4</v>
       </c>
       <c r="I64" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="J64" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K64" t="n">
         <v>4</v>
       </c>
       <c r="L64" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M64" t="n">
         <v>1.05</v>
@@ -12812,28 +12812,28 @@
         <v>4.3</v>
       </c>
       <c r="O64" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P64" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q64" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="R64" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S64" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="T64" t="n">
         <v>1.68</v>
       </c>
       <c r="U64" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V64" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W64" t="n">
         <v>1.8</v>
@@ -12842,10 +12842,10 @@
         <v>22</v>
       </c>
       <c r="Y64" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="Z64" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AA64" t="n">
         <v>75</v>
@@ -12854,13 +12854,13 @@
         <v>11.5</v>
       </c>
       <c r="AC64" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD64" t="n">
         <v>15</v>
       </c>
       <c r="AE64" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="AF64" t="n">
         <v>15.5</v>
@@ -12872,7 +12872,7 @@
         <v>20</v>
       </c>
       <c r="AI64" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AJ64" t="n">
         <v>28</v>
@@ -12893,62 +12893,62 @@
         <v>40</v>
       </c>
       <c r="AP64" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AQ64" t="n">
         <v>13.5</v>
       </c>
       <c r="AR64" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AS64" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AT64" t="n">
         <v>10</v>
       </c>
       <c r="AU64" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV64" t="n">
         <v>13</v>
       </c>
       <c r="AW64" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AX64" t="n">
         <v>13</v>
       </c>
       <c r="AY64" t="n">
-        <v>4.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ64" t="n">
         <v>14</v>
       </c>
       <c r="BA64" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB64" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC64" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BD64" t="n">
         <v>6.4</v>
       </c>
-      <c r="BB64" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BC64" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BD64" t="n">
-        <v>6</v>
-      </c>
       <c r="BE64" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BF64" t="n">
         <v>10</v>
       </c>
       <c r="BG64" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -12979,7 +12979,7 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="G65" t="n">
         <v>2.2</v>
@@ -12988,10 +12988,10 @@
         <v>3.2</v>
       </c>
       <c r="I65" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J65" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K65" t="n">
         <v>4.5</v>
@@ -13003,13 +13003,13 @@
         <v>1.03</v>
       </c>
       <c r="N65" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="O65" t="n">
         <v>1.13</v>
       </c>
       <c r="P65" t="n">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="Q65" t="n">
         <v>1.43</v>
@@ -13142,7 +13142,7 @@
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -13197,19 +13197,19 @@
         <v>1.07</v>
       </c>
       <c r="N66" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O66" t="n">
         <v>1.33</v>
       </c>
       <c r="P66" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="Q66" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="R66" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S66" t="n">
         <v>3.5</v>
@@ -13336,7 +13336,7 @@
       </c>
       <c r="BH66" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -13376,7 +13376,7 @@
         <v>4.4</v>
       </c>
       <c r="I67" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J67" t="n">
         <v>3.25</v>
@@ -13397,7 +13397,7 @@
         <v>1.41</v>
       </c>
       <c r="P67" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="Q67" t="n">
         <v>2.22</v>
@@ -13484,7 +13484,7 @@
         <v>26</v>
       </c>
       <c r="AS67" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AT67" t="n">
         <v>7.8</v>
@@ -13508,7 +13508,7 @@
         <v>17.5</v>
       </c>
       <c r="BA67" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="BB67" t="n">
         <v>22</v>
@@ -13530,7 +13530,7 @@
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -13561,22 +13561,22 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="G68" t="n">
         <v>1.39</v>
       </c>
       <c r="H68" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I68" t="n">
         <v>10.5</v>
       </c>
       <c r="J68" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="K68" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="L68" t="n">
         <v>1.01</v>
@@ -13639,7 +13639,7 @@
         <v>140</v>
       </c>
       <c r="AF68" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG68" t="n">
         <v>10.5</v>
@@ -13648,7 +13648,7 @@
         <v>26</v>
       </c>
       <c r="AI68" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ68" t="n">
         <v>11.5</v>
@@ -13678,7 +13678,7 @@
         <v>50</v>
       </c>
       <c r="AS68" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AT68" t="n">
         <v>9.4</v>
@@ -13724,7 +13724,7 @@
       </c>
       <c r="BH68" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -13755,7 +13755,7 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="G69" t="n">
         <v>1.98</v>
@@ -13782,7 +13782,7 @@
         <v>4.2</v>
       </c>
       <c r="O69" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P69" t="n">
         <v>2.12</v>
@@ -13797,7 +13797,7 @@
         <v>3.15</v>
       </c>
       <c r="T69" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="U69" t="n">
         <v>2.22</v>
@@ -13818,7 +13818,7 @@
         <v>32</v>
       </c>
       <c r="AA69" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AB69" t="n">
         <v>10.5</v>
@@ -13899,7 +13899,7 @@
         <v>40</v>
       </c>
       <c r="BB69" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC69" t="n">
         <v>17.5</v>
@@ -13914,11 +13914,11 @@
         <v>11</v>
       </c>
       <c r="BG69" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -13949,19 +13949,19 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>1.45</v>
+        <v>1.98</v>
       </c>
       <c r="G70" t="n">
-        <v>1000</v>
+        <v>2.36</v>
       </c>
       <c r="H70" t="n">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="I70" t="n">
         <v>1000</v>
       </c>
       <c r="J70" t="n">
-        <v>1.03</v>
+        <v>2.72</v>
       </c>
       <c r="K70" t="n">
         <v>3.4</v>
@@ -13970,16 +13970,16 @@
         <v>1.01</v>
       </c>
       <c r="M70" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N70" t="n">
-        <v>1.09</v>
+        <v>2.96</v>
       </c>
       <c r="O70" t="n">
         <v>1.44</v>
       </c>
       <c r="P70" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="Q70" t="n">
         <v>1.44</v>
@@ -13988,7 +13988,7 @@
         <v>1.08</v>
       </c>
       <c r="S70" t="n">
-        <v>1.44</v>
+        <v>2.22</v>
       </c>
       <c r="T70" t="n">
         <v>1.01</v>
@@ -13997,10 +13997,10 @@
         <v>1.01</v>
       </c>
       <c r="V70" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="W70" t="n">
-        <v>1.02</v>
+        <v>1.73</v>
       </c>
       <c r="X70" t="n">
         <v>1000</v>
@@ -14112,7 +14112,7 @@
       </c>
       <c r="BH70" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -14143,16 +14143,16 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="G71" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="H71" t="n">
         <v>2.92</v>
       </c>
       <c r="I71" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="J71" t="n">
         <v>3.2</v>
@@ -14170,19 +14170,19 @@
         <v>3.15</v>
       </c>
       <c r="O71" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="P71" t="n">
         <v>1.7</v>
       </c>
       <c r="Q71" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="R71" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S71" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="T71" t="n">
         <v>1.97</v>
@@ -14278,7 +14278,7 @@
         <v>15.5</v>
       </c>
       <c r="AY71" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ71" t="n">
         <v>18</v>
@@ -14299,14 +14299,14 @@
         <v>19.5</v>
       </c>
       <c r="BF71" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BG71" t="n">
         <v>34</v>
       </c>
       <c r="BH71" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -14500,7 +14500,7 @@
       </c>
       <c r="BH72" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -14558,7 +14558,7 @@
         <v>1.48</v>
       </c>
       <c r="O73" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P73" t="n">
         <v>1.48</v>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -14888,7 +14888,7 @@
       </c>
       <c r="BH74" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -14934,7 +14934,7 @@
         <v>3.15</v>
       </c>
       <c r="K75" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L75" t="n">
         <v>1.01</v>
@@ -14943,16 +14943,16 @@
         <v>1.01</v>
       </c>
       <c r="N75" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="O75" t="n">
         <v>1.42</v>
       </c>
       <c r="P75" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="Q75" t="n">
-        <v>2.26</v>
+        <v>2.06</v>
       </c>
       <c r="R75" t="n">
         <v>1.19</v>
@@ -14973,116 +14973,116 @@
         <v>1.58</v>
       </c>
       <c r="X75" t="n">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y75" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD75" t="n">
         <v>15</v>
       </c>
-      <c r="Z75" t="n">
-        <v>30</v>
-      </c>
-      <c r="AA75" t="n">
-        <v>85</v>
-      </c>
-      <c r="AB75" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC75" t="n">
+      <c r="AE75" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ75" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK75" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO75" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP75" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ75" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR75" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS75" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT75" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU75" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV75" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW75" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX75" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY75" t="n">
         <v>10</v>
       </c>
-      <c r="AD75" t="n">
-        <v>20</v>
-      </c>
-      <c r="AE75" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF75" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG75" t="n">
+      <c r="AZ75" t="n">
         <v>17</v>
       </c>
-      <c r="AH75" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI75" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ75" t="n">
-        <v>50</v>
-      </c>
-      <c r="AK75" t="n">
-        <v>46</v>
-      </c>
-      <c r="AL75" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM75" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN75" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO75" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP75" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AQ75" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AR75" t="n">
-        <v>15</v>
-      </c>
-      <c r="AS75" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AT75" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AU75" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AV75" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AW75" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AX75" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY75" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AZ75" t="n">
-        <v>2.52</v>
-      </c>
       <c r="BA75" t="n">
-        <v>2.68</v>
+        <v>7.4</v>
       </c>
       <c r="BB75" t="n">
-        <v>2.64</v>
+        <v>7</v>
       </c>
       <c r="BC75" t="n">
-        <v>2.62</v>
+        <v>6.6</v>
       </c>
       <c r="BD75" t="n">
-        <v>2.68</v>
+        <v>7.2</v>
       </c>
       <c r="BE75" t="n">
-        <v>2.78</v>
+        <v>7.8</v>
       </c>
       <c r="BF75" t="n">
-        <v>2.74</v>
+        <v>6.8</v>
       </c>
       <c r="BG75" t="n">
-        <v>2.74</v>
+        <v>7.2</v>
       </c>
       <c r="BH75" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -15131,28 +15131,28 @@
         <v>4.3</v>
       </c>
       <c r="L76" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="M76" t="n">
         <v>1.08</v>
       </c>
       <c r="N76" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O76" t="n">
         <v>1.38</v>
       </c>
       <c r="P76" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="Q76" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R76" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S76" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T76" t="n">
         <v>2.34</v>
@@ -15185,7 +15185,7 @@
         <v>10</v>
       </c>
       <c r="AD76" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AE76" t="n">
         <v>170</v>
@@ -15242,7 +15242,7 @@
         <v>29</v>
       </c>
       <c r="AW76" t="n">
-        <v>17.5</v>
+        <v>44</v>
       </c>
       <c r="AX76" t="n">
         <v>7</v>
@@ -15254,7 +15254,7 @@
         <v>27</v>
       </c>
       <c r="BA76" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BB76" t="n">
         <v>11.5</v>
@@ -15263,7 +15263,7 @@
         <v>16.5</v>
       </c>
       <c r="BD76" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="BE76" t="n">
         <v>17.5</v>
@@ -15276,7 +15276,7 @@
       </c>
       <c r="BH76" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -15307,7 +15307,7 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="G77" t="n">
         <v>1.2</v>
@@ -15316,13 +15316,13 @@
         <v>23</v>
       </c>
       <c r="I77" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J77" t="n">
         <v>7.6</v>
       </c>
       <c r="K77" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L77" t="n">
         <v>1.01</v>
@@ -15427,7 +15427,7 @@
         <v>2.18</v>
       </c>
       <c r="AT77" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AU77" t="n">
         <v>14.5</v>
@@ -15470,7 +15470,7 @@
       </c>
       <c r="BH77" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -15516,10 +15516,10 @@
         <v>3.7</v>
       </c>
       <c r="K78" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L78" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M78" t="n">
         <v>1.08</v>
@@ -15664,7 +15664,7 @@
       </c>
       <c r="BH78" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -15701,19 +15701,19 @@
         <v>6.4</v>
       </c>
       <c r="H79" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="I79" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="J79" t="n">
         <v>3.35</v>
       </c>
       <c r="K79" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L79" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="M79" t="n">
         <v>1.07</v>
@@ -15743,7 +15743,7 @@
         <v>1.01</v>
       </c>
       <c r="V79" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="W79" t="n">
         <v>1.19</v>
@@ -15858,7 +15858,7 @@
       </c>
       <c r="BH79" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -15910,7 +15910,7 @@
         <v>1.01</v>
       </c>
       <c r="M80" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N80" t="n">
         <v>1.76</v>
@@ -15940,7 +15940,7 @@
         <v>1.32</v>
       </c>
       <c r="W80" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="X80" t="n">
         <v>15</v>
@@ -16052,7 +16052,7 @@
       </c>
       <c r="BH80" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -16083,22 +16083,22 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="G81" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="H81" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="I81" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="J81" t="n">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="K81" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="L81" t="n">
         <v>1.01</v>
@@ -16131,10 +16131,10 @@
         <v>1.01</v>
       </c>
       <c r="V81" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W81" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="X81" t="n">
         <v>13.5</v>
@@ -16246,7 +16246,7 @@
       </c>
       <c r="BH81" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -16304,7 +16304,7 @@
         <v>5.4</v>
       </c>
       <c r="O82" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P82" t="n">
         <v>2.5</v>
@@ -16316,13 +16316,13 @@
         <v>1.6</v>
       </c>
       <c r="S82" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="T82" t="n">
         <v>2.52</v>
       </c>
       <c r="U82" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="V82" t="n">
         <v>1.03</v>
@@ -16331,7 +16331,7 @@
         <v>6.2</v>
       </c>
       <c r="X82" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="Y82" t="n">
         <v>65</v>
@@ -16343,13 +16343,13 @@
         <v>1000</v>
       </c>
       <c r="AB82" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC82" t="n">
         <v>21</v>
       </c>
       <c r="AD82" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AE82" t="n">
         <v>1000</v>
@@ -16379,22 +16379,22 @@
         <v>420</v>
       </c>
       <c r="AN82" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="AO82" t="n">
         <v>1000</v>
       </c>
       <c r="AP82" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AQ82" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AR82" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AS82" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AT82" t="n">
         <v>8</v>
@@ -16403,10 +16403,10 @@
         <v>16.5</v>
       </c>
       <c r="AV82" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AW82" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AX82" t="n">
         <v>6.2</v>
@@ -16415,10 +16415,10 @@
         <v>11</v>
       </c>
       <c r="AZ82" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BA82" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BB82" t="n">
         <v>7</v>
@@ -16427,20 +16427,20 @@
         <v>13</v>
       </c>
       <c r="BD82" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE82" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BF82" t="n">
         <v>3.25</v>
       </c>
       <c r="BG82" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BH82" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -16501,28 +16501,28 @@
         <v>1.28</v>
       </c>
       <c r="P83" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q83" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="R83" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S83" t="n">
         <v>3.05</v>
       </c>
       <c r="T83" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="U83" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="V83" t="n">
         <v>1.23</v>
       </c>
       <c r="W83" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="X83" t="n">
         <v>16.5</v>
@@ -16546,7 +16546,7 @@
         <v>20</v>
       </c>
       <c r="AE83" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AF83" t="n">
         <v>11.5</v>
@@ -16576,7 +16576,7 @@
         <v>11</v>
       </c>
       <c r="AO83" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AP83" t="n">
         <v>14.5</v>
@@ -16591,7 +16591,7 @@
         <v>11.5</v>
       </c>
       <c r="AT83" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AU83" t="n">
         <v>8</v>
@@ -16634,7 +16634,7 @@
       </c>
       <c r="BH83" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -16665,22 +16665,22 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="G84" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="H84" t="n">
         <v>3</v>
       </c>
       <c r="I84" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J84" t="n">
         <v>3</v>
       </c>
       <c r="K84" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="L84" t="n">
         <v>1.35</v>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="BH84" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -16865,7 +16865,7 @@
         <v>17</v>
       </c>
       <c r="H85" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="I85" t="n">
         <v>1.3</v>
@@ -16880,7 +16880,7 @@
         <v>1.01</v>
       </c>
       <c r="M85" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N85" t="n">
         <v>4</v>
@@ -16889,13 +16889,13 @@
         <v>1.28</v>
       </c>
       <c r="P85" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q85" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R85" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S85" t="n">
         <v>3.15</v>
@@ -16904,7 +16904,7 @@
         <v>2.5</v>
       </c>
       <c r="U85" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="V85" t="n">
         <v>4.3</v>
@@ -16934,7 +16934,7 @@
         <v>12</v>
       </c>
       <c r="AE85" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AF85" t="n">
         <v>180</v>
@@ -16964,7 +16964,7 @@
         <v>1000</v>
       </c>
       <c r="AO85" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AP85" t="n">
         <v>14.5</v>
@@ -16979,7 +16979,7 @@
         <v>8</v>
       </c>
       <c r="AT85" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AU85" t="n">
         <v>12</v>
@@ -16991,38 +16991,38 @@
         <v>14</v>
       </c>
       <c r="AX85" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AY85" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ85" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AZ85" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BA85" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BB85" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BC85" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD85" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE85" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF85" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BG85" t="n">
         <v>5</v>
       </c>
       <c r="BH85" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -17065,7 +17065,7 @@
         <v>1.8</v>
       </c>
       <c r="J86" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K86" t="n">
         <v>4.3</v>
@@ -17077,10 +17077,10 @@
         <v>1.01</v>
       </c>
       <c r="N86" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="O86" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P86" t="n">
         <v>1.65</v>
@@ -17216,7 +17216,7 @@
       </c>
       <c r="BH86" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -17410,7 +17410,7 @@
       </c>
       <c r="BH87" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -17456,7 +17456,7 @@
         <v>2.82</v>
       </c>
       <c r="K88" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L88" t="n">
         <v>1.65</v>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="BH88" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -17677,7 +17677,7 @@
         <v>2.72</v>
       </c>
       <c r="T89" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="U89" t="n">
         <v>1.73</v>
@@ -17798,7 +17798,7 @@
       </c>
       <c r="BH89" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -17992,7 +17992,7 @@
       </c>
       <c r="BH90" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -18023,46 +18023,46 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="G91" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="H91" t="n">
         <v>1.62</v>
       </c>
       <c r="I91" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="J91" t="n">
         <v>4</v>
       </c>
       <c r="K91" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L91" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="M91" t="n">
         <v>1.01</v>
       </c>
       <c r="N91" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="O91" t="n">
         <v>1.25</v>
       </c>
       <c r="P91" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q91" t="n">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="R91" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S91" t="n">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="T91" t="n">
         <v>1.01</v>
@@ -18071,7 +18071,7 @@
         <v>1.01</v>
       </c>
       <c r="V91" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="W91" t="n">
         <v>1.16</v>
@@ -18186,7 +18186,7 @@
       </c>
       <c r="BH91" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -18226,7 +18226,7 @@
         <v>2.08</v>
       </c>
       <c r="I92" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="J92" t="n">
         <v>4</v>
@@ -18235,28 +18235,28 @@
         <v>4.1</v>
       </c>
       <c r="L92" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="M92" t="n">
         <v>1.04</v>
       </c>
       <c r="N92" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="O92" t="n">
         <v>1.21</v>
       </c>
       <c r="P92" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="Q92" t="n">
         <v>1.65</v>
       </c>
       <c r="R92" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="S92" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="T92" t="n">
         <v>1.59</v>
@@ -18380,7 +18380,7 @@
       </c>
       <c r="BH92" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -18423,10 +18423,10 @@
         <v>5</v>
       </c>
       <c r="J93" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K93" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L93" t="n">
         <v>1.43</v>
@@ -18438,7 +18438,7 @@
         <v>2.82</v>
       </c>
       <c r="O93" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P93" t="n">
         <v>1.61</v>
@@ -18574,7 +18574,7 @@
       </c>
       <c r="BH93" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -18768,7 +18768,7 @@
       </c>
       <c r="BH94" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -18962,7 +18962,7 @@
       </c>
       <c r="BH95" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -19005,7 +19005,7 @@
         <v>1000</v>
       </c>
       <c r="J96" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K96" t="n">
         <v>1000</v>
@@ -19156,7 +19156,7 @@
       </c>
       <c r="BH96" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -19187,10 +19187,10 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="G97" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="H97" t="n">
         <v>2.04</v>
@@ -19202,13 +19202,13 @@
         <v>3.4</v>
       </c>
       <c r="K97" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L97" t="n">
         <v>1.01</v>
       </c>
       <c r="M97" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N97" t="n">
         <v>3.9</v>
@@ -19217,43 +19217,43 @@
         <v>1.29</v>
       </c>
       <c r="P97" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="Q97" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="R97" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S97" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T97" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="U97" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V97" t="n">
         <v>1.84</v>
       </c>
       <c r="W97" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="X97" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Y97" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Z97" t="n">
         <v>14.5</v>
       </c>
       <c r="AA97" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AB97" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AC97" t="n">
         <v>8.4</v>
@@ -19262,7 +19262,7 @@
         <v>11.5</v>
       </c>
       <c r="AE97" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AF97" t="n">
         <v>32</v>
@@ -19271,7 +19271,7 @@
         <v>17.5</v>
       </c>
       <c r="AH97" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AI97" t="n">
         <v>36</v>
@@ -19292,7 +19292,7 @@
         <v>48</v>
       </c>
       <c r="AO97" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AP97" t="n">
         <v>13</v>
@@ -19304,10 +19304,10 @@
         <v>11.5</v>
       </c>
       <c r="AS97" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AT97" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AU97" t="n">
         <v>7</v>
@@ -19316,7 +19316,7 @@
         <v>9</v>
       </c>
       <c r="AW97" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AX97" t="n">
         <v>19</v>
@@ -19328,29 +19328,29 @@
         <v>14.5</v>
       </c>
       <c r="BA97" t="n">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="BB97" t="n">
-        <v>8</v>
+        <v>6.6</v>
       </c>
       <c r="BC97" t="n">
-        <v>38</v>
+        <v>6.2</v>
       </c>
       <c r="BD97" t="n">
-        <v>36</v>
+        <v>6.4</v>
       </c>
       <c r="BE97" t="n">
-        <v>8.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="BF97" t="n">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="BG97" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BH97" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -19381,22 +19381,22 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>1.96</v>
+        <v>1.79</v>
       </c>
       <c r="G98" t="n">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="H98" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="I98" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="J98" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="K98" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="L98" t="n">
         <v>1.01</v>
@@ -19405,22 +19405,22 @@
         <v>1.07</v>
       </c>
       <c r="N98" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="O98" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P98" t="n">
         <v>1.32</v>
       </c>
       <c r="Q98" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="R98" t="n">
         <v>1.31</v>
       </c>
       <c r="S98" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="T98" t="n">
         <v>1.01</v>
@@ -19429,10 +19429,10 @@
         <v>1.01</v>
       </c>
       <c r="V98" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="W98" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="X98" t="n">
         <v>1000</v>
@@ -19495,7 +19495,7 @@
         <v>10.5</v>
       </c>
       <c r="AR98" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AS98" t="n">
         <v>2.26</v>
@@ -19507,7 +19507,7 @@
         <v>1.89</v>
       </c>
       <c r="AV98" t="n">
-        <v>12</v>
+        <v>2.08</v>
       </c>
       <c r="AW98" t="n">
         <v>2.2</v>
@@ -19544,7 +19544,7 @@
       </c>
       <c r="BH98" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -19578,10 +19578,10 @@
         <v>2.02</v>
       </c>
       <c r="G99" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H99" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I99" t="n">
         <v>4.7</v>
@@ -19590,22 +19590,22 @@
         <v>3.25</v>
       </c>
       <c r="K99" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L99" t="n">
         <v>1.01</v>
       </c>
       <c r="M99" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="N99" t="n">
         <v>3</v>
       </c>
       <c r="O99" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P99" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q99" t="n">
         <v>2.34</v>
@@ -19620,19 +19620,19 @@
         <v>2.02</v>
       </c>
       <c r="U99" t="n">
-        <v>1.72</v>
+        <v>1.88</v>
       </c>
       <c r="V99" t="n">
         <v>1.27</v>
       </c>
       <c r="W99" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="X99" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Y99" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="Z99" t="n">
         <v>38</v>
@@ -19641,70 +19641,70 @@
         <v>140</v>
       </c>
       <c r="AB99" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AC99" t="n">
         <v>8.4</v>
       </c>
       <c r="AD99" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AE99" t="n">
         <v>85</v>
       </c>
       <c r="AF99" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AG99" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AH99" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI99" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ99" t="n">
         <v>27</v>
       </c>
-      <c r="AI99" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ99" t="n">
-        <v>32</v>
-      </c>
       <c r="AK99" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AL99" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AM99" t="n">
         <v>180</v>
       </c>
       <c r="AN99" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AO99" t="n">
         <v>120</v>
       </c>
       <c r="AP99" t="n">
-        <v>4</v>
+        <v>9.4</v>
       </c>
       <c r="AQ99" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR99" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS99" t="n">
         <v>9.6</v>
-      </c>
-      <c r="AR99" t="n">
-        <v>5</v>
-      </c>
-      <c r="AS99" t="n">
-        <v>5.6</v>
       </c>
       <c r="AT99" t="n">
         <v>6.6</v>
       </c>
       <c r="AU99" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV99" t="n">
-        <v>4.5</v>
+        <v>16.5</v>
       </c>
       <c r="AW99" t="n">
-        <v>5.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX99" t="n">
         <v>10</v>
@@ -19713,32 +19713,32 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ99" t="n">
-        <v>4.7</v>
+        <v>17.5</v>
       </c>
       <c r="BA99" t="n">
-        <v>5.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB99" t="n">
-        <v>4.8</v>
+        <v>7.4</v>
       </c>
       <c r="BC99" t="n">
-        <v>4.9</v>
+        <v>18.5</v>
       </c>
       <c r="BD99" t="n">
-        <v>5.2</v>
+        <v>8.4</v>
       </c>
       <c r="BE99" t="n">
-        <v>5.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF99" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BG99" t="n">
-        <v>5.6</v>
+        <v>9.4</v>
       </c>
       <c r="BH99" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -19769,7 +19769,7 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="G100" t="n">
         <v>1.95</v>
@@ -19781,10 +19781,10 @@
         <v>4.9</v>
       </c>
       <c r="J100" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K100" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L100" t="n">
         <v>1.01</v>
@@ -19811,10 +19811,10 @@
         <v>3.55</v>
       </c>
       <c r="T100" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="U100" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V100" t="n">
         <v>1.25</v>
@@ -19868,7 +19868,7 @@
         <v>40</v>
       </c>
       <c r="AM100" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN100" t="n">
         <v>14.5</v>
@@ -19932,7 +19932,7 @@
       </c>
       <c r="BH100" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -19963,16 +19963,16 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="G101" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H101" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="I101" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="J101" t="n">
         <v>3.05</v>
@@ -20002,7 +20002,7 @@
         <v>1.17</v>
       </c>
       <c r="S101" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T101" t="n">
         <v>1.01</v>
@@ -20011,28 +20011,28 @@
         <v>1.01</v>
       </c>
       <c r="V101" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W101" t="n">
         <v>1.74</v>
       </c>
       <c r="X101" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="Y101" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Z101" t="n">
         <v>34</v>
       </c>
       <c r="AA101" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AB101" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC101" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD101" t="n">
         <v>22</v>
@@ -20041,7 +20041,7 @@
         <v>80</v>
       </c>
       <c r="AF101" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AG101" t="n">
         <v>14</v>
@@ -20053,10 +20053,10 @@
         <v>110</v>
       </c>
       <c r="AJ101" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AK101" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AL101" t="n">
         <v>70</v>
@@ -20065,10 +20065,10 @@
         <v>210</v>
       </c>
       <c r="AN101" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AO101" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AP101" t="n">
         <v>8.199999999999999</v>
@@ -20077,10 +20077,10 @@
         <v>10</v>
       </c>
       <c r="AR101" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AS101" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AT101" t="n">
         <v>6.4</v>
@@ -20089,22 +20089,22 @@
         <v>6.4</v>
       </c>
       <c r="AV101" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AW101" t="n">
         <v>4.5</v>
       </c>
       <c r="AX101" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY101" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ101" t="n">
         <v>19.5</v>
       </c>
       <c r="BA101" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BB101" t="n">
         <v>4.2</v>
@@ -20113,20 +20113,20 @@
         <v>4.2</v>
       </c>
       <c r="BD101" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE101" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BF101" t="n">
+        <v>21</v>
+      </c>
+      <c r="BG101" t="n">
         <v>4.5</v>
       </c>
-      <c r="BE101" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BF101" t="n">
-        <v>20</v>
-      </c>
-      <c r="BG101" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BH101" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -20160,16 +20160,16 @@
         <v>3.3</v>
       </c>
       <c r="G102" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="H102" t="n">
         <v>2.12</v>
       </c>
       <c r="I102" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="J102" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K102" t="n">
         <v>4.2</v>
@@ -20181,7 +20181,7 @@
         <v>1.04</v>
       </c>
       <c r="N102" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="O102" t="n">
         <v>1.24</v>
@@ -20205,10 +20205,10 @@
         <v>2.44</v>
       </c>
       <c r="V102" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="W102" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="X102" t="n">
         <v>25</v>
@@ -20226,7 +20226,7 @@
         <v>17.5</v>
       </c>
       <c r="AC102" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AD102" t="n">
         <v>260</v>
@@ -20262,7 +20262,7 @@
         <v>26</v>
       </c>
       <c r="AO102" t="n">
-        <v>340</v>
+        <v>240</v>
       </c>
       <c r="AP102" t="n">
         <v>8</v>
@@ -20320,7 +20320,7 @@
       </c>
       <c r="BH102" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -20354,19 +20354,19 @@
         <v>2.52</v>
       </c>
       <c r="G103" t="n">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="H103" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="I103" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="J103" t="n">
-        <v>2.72</v>
+        <v>1.09</v>
       </c>
       <c r="K103" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L103" t="n">
         <v>1.01</v>
@@ -20375,19 +20375,19 @@
         <v>1.1</v>
       </c>
       <c r="N103" t="n">
-        <v>1.98</v>
+        <v>1.03</v>
       </c>
       <c r="O103" t="n">
         <v>1.36</v>
       </c>
       <c r="P103" t="n">
-        <v>1.68</v>
+        <v>1.25</v>
       </c>
       <c r="Q103" t="n">
         <v>2.06</v>
       </c>
       <c r="R103" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="S103" t="n">
         <v>3.3</v>
@@ -20399,13 +20399,13 @@
         <v>1.01</v>
       </c>
       <c r="V103" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W103" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="X103" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y103" t="n">
         <v>1000</v>
@@ -20462,40 +20462,40 @@
         <v>4.8</v>
       </c>
       <c r="AQ103" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AR103" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AS103" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AT103" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AU103" t="n">
         <v>6.4</v>
       </c>
       <c r="AV103" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AW103" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AX103" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AY103" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AZ103" t="n">
         <v>6.2</v>
       </c>
       <c r="BA103" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB103" t="n">
         <v>7.8</v>
-      </c>
-      <c r="BB103" t="n">
-        <v>7.6</v>
       </c>
       <c r="BC103" t="n">
         <v>7.4</v>
@@ -20504,17 +20504,17 @@
         <v>7.8</v>
       </c>
       <c r="BE103" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="BF103" t="n">
         <v>7</v>
       </c>
       <c r="BG103" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH103" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -20545,7 +20545,7 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="G104" t="n">
         <v>2.74</v>
@@ -20554,13 +20554,13 @@
         <v>3.1</v>
       </c>
       <c r="I104" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="J104" t="n">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="K104" t="n">
-        <v>950</v>
+        <v>5.7</v>
       </c>
       <c r="L104" t="n">
         <v>1.01</v>
@@ -20587,10 +20587,10 @@
         <v>3.25</v>
       </c>
       <c r="T104" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="U104" t="n">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="V104" t="n">
         <v>1.28</v>
@@ -20708,7 +20708,7 @@
       </c>
       <c r="BH104" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -20763,16 +20763,16 @@
         <v>1.08</v>
       </c>
       <c r="N105" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O105" t="n">
         <v>1.35</v>
       </c>
       <c r="P105" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="Q105" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R105" t="n">
         <v>1.34</v>
@@ -20781,7 +20781,7 @@
         <v>3.65</v>
       </c>
       <c r="T105" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U105" t="n">
         <v>2.08</v>
@@ -20799,10 +20799,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="Z105" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AA105" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AB105" t="n">
         <v>14</v>
@@ -20817,7 +20817,7 @@
         <v>24</v>
       </c>
       <c r="AF105" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AG105" t="n">
         <v>16.5</v>
@@ -20832,7 +20832,7 @@
         <v>1000</v>
       </c>
       <c r="AK105" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AL105" t="n">
         <v>60</v>
@@ -20847,7 +20847,7 @@
         <v>17</v>
       </c>
       <c r="AP105" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AQ105" t="n">
         <v>8.4</v>
@@ -20865,7 +20865,7 @@
         <v>7.4</v>
       </c>
       <c r="AV105" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW105" t="n">
         <v>19.5</v>
@@ -20877,32 +20877,32 @@
         <v>14</v>
       </c>
       <c r="AZ105" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA105" t="n">
-        <v>9.199999999999999</v>
+        <v>30</v>
       </c>
       <c r="BB105" t="n">
-        <v>10.5</v>
+        <v>48</v>
       </c>
       <c r="BC105" t="n">
-        <v>9.6</v>
+        <v>40</v>
       </c>
       <c r="BD105" t="n">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="BE105" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="BF105" t="n">
-        <v>9.800000000000001</v>
+        <v>27</v>
       </c>
       <c r="BG105" t="n">
         <v>14.5</v>
       </c>
       <c r="BH105" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -20939,31 +20939,31 @@
         <v>5.4</v>
       </c>
       <c r="H106" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="I106" t="n">
         <v>1.73</v>
       </c>
       <c r="J106" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K106" t="n">
         <v>4.4</v>
       </c>
       <c r="L106" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="M106" t="n">
         <v>1.06</v>
       </c>
       <c r="N106" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O106" t="n">
         <v>1.27</v>
       </c>
       <c r="P106" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q106" t="n">
         <v>1.81</v>
@@ -20975,7 +20975,7 @@
         <v>3.05</v>
       </c>
       <c r="T106" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="U106" t="n">
         <v>2.12</v>
@@ -20987,13 +20987,13 @@
         <v>1.22</v>
       </c>
       <c r="X106" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="Y106" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="Z106" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AA106" t="n">
         <v>17</v>
@@ -21008,7 +21008,7 @@
         <v>10</v>
       </c>
       <c r="AE106" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AF106" t="n">
         <v>42</v>
@@ -21017,22 +21017,22 @@
         <v>21</v>
       </c>
       <c r="AH106" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AI106" t="n">
         <v>32</v>
       </c>
       <c r="AJ106" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AK106" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AL106" t="n">
         <v>70</v>
       </c>
       <c r="AM106" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AN106" t="n">
         <v>75</v>
@@ -21041,7 +21041,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AP106" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AQ106" t="n">
         <v>9</v>
@@ -21068,7 +21068,7 @@
         <v>38</v>
       </c>
       <c r="AY106" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AZ106" t="n">
         <v>18</v>
@@ -21077,26 +21077,26 @@
         <v>29</v>
       </c>
       <c r="BB106" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="BC106" t="n">
         <v>32</v>
       </c>
       <c r="BD106" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="BE106" t="n">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="BF106" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="BG106" t="n">
         <v>8.4</v>
       </c>
       <c r="BH106" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -21127,7 +21127,7 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="G107" t="n">
         <v>2.5</v>
@@ -21290,7 +21290,7 @@
       </c>
       <c r="BH107" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -21330,7 +21330,7 @@
         <v>2.3</v>
       </c>
       <c r="I108" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="J108" t="n">
         <v>3.2</v>
@@ -21339,7 +21339,7 @@
         <v>3.3</v>
       </c>
       <c r="L108" t="n">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="M108" t="n">
         <v>1.1</v>
@@ -21351,7 +21351,7 @@
         <v>1.45</v>
       </c>
       <c r="P108" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q108" t="n">
         <v>2.32</v>
@@ -21363,16 +21363,16 @@
         <v>4.5</v>
       </c>
       <c r="T108" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="U108" t="n">
         <v>1.9</v>
       </c>
       <c r="V108" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="W108" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="X108" t="n">
         <v>10.5</v>
@@ -21402,7 +21402,7 @@
         <v>24</v>
       </c>
       <c r="AG108" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AH108" t="n">
         <v>23</v>
@@ -21423,7 +21423,7 @@
         <v>160</v>
       </c>
       <c r="AN108" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AO108" t="n">
         <v>29</v>
@@ -21468,7 +21468,7 @@
         <v>12.5</v>
       </c>
       <c r="BC108" t="n">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="BD108" t="n">
         <v>44</v>
@@ -21477,14 +21477,14 @@
         <v>11.5</v>
       </c>
       <c r="BF108" t="n">
-        <v>10.5</v>
+        <v>50</v>
       </c>
       <c r="BG108" t="n">
         <v>22</v>
       </c>
       <c r="BH108" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -21518,7 +21518,7 @@
         <v>5.7</v>
       </c>
       <c r="G109" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H109" t="n">
         <v>1.52</v>
@@ -21548,7 +21548,7 @@
         <v>1.25</v>
       </c>
       <c r="Q109" t="n">
-        <v>1.46</v>
+        <v>2.38</v>
       </c>
       <c r="R109" t="n">
         <v>1.18</v>
@@ -21566,7 +21566,7 @@
         <v>2.14</v>
       </c>
       <c r="W109" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X109" t="n">
         <v>1000</v>
@@ -21678,7 +21678,7 @@
       </c>
       <c r="BH109" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -21718,7 +21718,7 @@
         <v>2.48</v>
       </c>
       <c r="I110" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="J110" t="n">
         <v>3.1</v>
@@ -21872,7 +21872,7 @@
       </c>
       <c r="BH110" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -21924,7 +21924,7 @@
         <v>1.01</v>
       </c>
       <c r="M111" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="N111" t="n">
         <v>2.74</v>
@@ -22066,7 +22066,7 @@
       </c>
       <c r="BH111" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -22260,7 +22260,7 @@
       </c>
       <c r="BH112" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -22315,19 +22315,19 @@
         <v>1.01</v>
       </c>
       <c r="N113" t="n">
-        <v>3.15</v>
+        <v>1.27</v>
       </c>
       <c r="O113" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="P113" t="n">
-        <v>1.74</v>
+        <v>1.26</v>
       </c>
       <c r="Q113" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="R113" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="S113" t="n">
         <v>3.55</v>
@@ -22454,7 +22454,7 @@
       </c>
       <c r="BH113" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -22491,7 +22491,7 @@
         <v>1.53</v>
       </c>
       <c r="H114" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="I114" t="n">
         <v>9.6</v>
@@ -22527,10 +22527,10 @@
         <v>3</v>
       </c>
       <c r="T114" t="n">
-        <v>1.96</v>
+        <v>1.82</v>
       </c>
       <c r="U114" t="n">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="V114" t="n">
         <v>1.12</v>
@@ -22648,7 +22648,7 @@
       </c>
       <c r="BH114" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -22842,7 +22842,7 @@
       </c>
       <c r="BH115" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -22894,25 +22894,25 @@
         <v>1.01</v>
       </c>
       <c r="M116" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="N116" t="n">
-        <v>2.54</v>
+        <v>2.36</v>
       </c>
       <c r="O116" t="n">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="P116" t="n">
-        <v>1.51</v>
+        <v>1.25</v>
       </c>
       <c r="Q116" t="n">
-        <v>2.72</v>
+        <v>1.02</v>
       </c>
       <c r="R116" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="S116" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="T116" t="n">
         <v>2.34</v>
@@ -22933,7 +22933,7 @@
         <v>14.5</v>
       </c>
       <c r="Z116" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AA116" t="n">
         <v>260</v>
@@ -23036,7 +23036,7 @@
       </c>
       <c r="BH116" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -23067,10 +23067,10 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="G117" t="n">
-        <v>1.97</v>
+        <v>970</v>
       </c>
       <c r="H117" t="n">
         <v>5.7</v>
@@ -23079,10 +23079,10 @@
         <v>7.8</v>
       </c>
       <c r="J117" t="n">
-        <v>2.76</v>
+        <v>2.64</v>
       </c>
       <c r="K117" t="n">
-        <v>110</v>
+        <v>5.6</v>
       </c>
       <c r="L117" t="n">
         <v>1.01</v>
@@ -23230,7 +23230,7 @@
       </c>
       <c r="BH117" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -23424,7 +23424,7 @@
       </c>
       <c r="BH118" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -23455,7 +23455,7 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>1.04</v>
+        <v>2.28</v>
       </c>
       <c r="G119" t="n">
         <v>2.96</v>
@@ -23464,7 +23464,7 @@
         <v>2.58</v>
       </c>
       <c r="I119" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="J119" t="n">
         <v>2.22</v>
@@ -23473,7 +23473,7 @@
         <v>4.5</v>
       </c>
       <c r="L119" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="M119" t="n">
         <v>1.01</v>
@@ -23618,7 +23618,7 @@
       </c>
       <c r="BH119" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -23655,10 +23655,10 @@
         <v>3.2</v>
       </c>
       <c r="H120" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="I120" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="J120" t="n">
         <v>2.66</v>
@@ -23812,7 +23812,7 @@
       </c>
       <c r="BH120" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -23843,46 +23843,46 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="G121" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="H121" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="I121" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="J121" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="K121" t="n">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="L121" t="n">
         <v>1.01</v>
       </c>
       <c r="M121" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="N121" t="n">
-        <v>2.86</v>
+        <v>1.03</v>
       </c>
       <c r="O121" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="P121" t="n">
-        <v>1.64</v>
+        <v>1.25</v>
       </c>
       <c r="Q121" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="R121" t="n">
-        <v>1.23</v>
+        <v>1.09</v>
       </c>
       <c r="S121" t="n">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="T121" t="n">
         <v>1.98</v>
@@ -23891,10 +23891,10 @@
         <v>1.89</v>
       </c>
       <c r="V121" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="W121" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="X121" t="n">
         <v>10.5</v>
@@ -24006,7 +24006,7 @@
       </c>
       <c r="BH121" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -24200,7 +24200,7 @@
       </c>
       <c r="BH122" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -24255,16 +24255,16 @@
         <v>1.11</v>
       </c>
       <c r="N123" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="O123" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="P123" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="Q123" t="n">
-        <v>2.84</v>
+        <v>2.52</v>
       </c>
       <c r="R123" t="n">
         <v>1.13</v>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="BH123" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -24440,31 +24440,31 @@
         <v>2.98</v>
       </c>
       <c r="K124" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="L124" t="n">
         <v>1.01</v>
       </c>
       <c r="M124" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="N124" t="n">
-        <v>2.56</v>
+        <v>2.36</v>
       </c>
       <c r="O124" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="P124" t="n">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="Q124" t="n">
-        <v>2.72</v>
+        <v>2.48</v>
       </c>
       <c r="R124" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="S124" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="T124" t="n">
         <v>1.99</v>
@@ -24479,7 +24479,7 @@
         <v>1.6</v>
       </c>
       <c r="X124" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="Y124" t="n">
         <v>9.4</v>
@@ -24488,7 +24488,7 @@
         <v>21</v>
       </c>
       <c r="AA124" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AB124" t="n">
         <v>7.8</v>
@@ -24512,16 +24512,16 @@
         <v>24</v>
       </c>
       <c r="AI124" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AJ124" t="n">
         <v>42</v>
       </c>
       <c r="AK124" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AL124" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AM124" t="n">
         <v>200</v>
@@ -24536,7 +24536,7 @@
         <v>7.4</v>
       </c>
       <c r="AQ124" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR124" t="n">
         <v>19</v>
@@ -24545,7 +24545,7 @@
         <v>55</v>
       </c>
       <c r="AT124" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AU124" t="n">
         <v>6.4</v>
@@ -24581,14 +24581,14 @@
         <v>160</v>
       </c>
       <c r="BF124" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BG124" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BH124" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -24782,7 +24782,7 @@
       </c>
       <c r="BH125" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -24976,7 +24976,7 @@
       </c>
       <c r="BH126" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
